--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +152,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +233,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -35269,4 +35461,7305 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1558呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 384呎 (1房)
+$858万
+$22,341/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 384呎 (1房)
+$858万
+$22,341/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$584万
+$23,361/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 392呎 (1房)
+$895万
+$22,836/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 391呎 (1房)
+$881万
+$22,535/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$2028万
+$33,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$834万
+$21,710/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$848万
+$22,072/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$568万
+$22,702/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$855万
+$21,809/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$869万
+$22,386/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1108万
+$23,270/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1979万
+$32,500/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$827万
+$21,525/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$827万
+$21,525/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$585万
+$23,386/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$848万
+$21,621/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$842万
+$21,709/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1098万
+$23,071/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3373万
+$36,038/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$824万
+$21,464/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$824万
+$21,464/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$561万
+$22,450/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$859万
+$21,916/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$840万
+$21,644/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1095万
+$23,003/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3288万
+$35,128/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$822万
+$21,401/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$822万
+$21,401/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$566万
+$22,633/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$866万
+$22,091/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$837万
+$21,581/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1092万
+$22,937/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3280万
+$35,037/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1973万
+$32,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$819万
+$21,340/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$819万
+$21,340/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$564万
+$22,568/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$840万
+$21,430/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$835万
+$21,519/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1107万
+$23,252/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3293万
+$35,185/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$817万
+$21,277/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$817万
+$21,277/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$556万
+$22,259/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$838万
+$21,368/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$856万
+$22,050/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1116万
+$23,438/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3280万
+$35,037/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$812万
+$21,155/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$767万
+$19,979/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$563万
+$22,502/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$833万
+$21,242/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$841万
+$21,684/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1097万
+$23,050/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3213万
+$34,327/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$810万
+$21,091/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$810万
+$21,091/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$552万
+$22,068/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$844万
+$21,533/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$825万
+$21,264/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1076万
+$22,604/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3195万
+$34,136/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$808万
+$21,030/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$808万
+$21,030/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$550万
+$22,007/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$828万
+$21,118/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$823万
+$21,201/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1073万
+$22,538/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3176万
+$33,932/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$805万
+$20,967/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$805万
+$20,967/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$549万
+$21,942/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$825万
+$21,054/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$820万
+$21,138/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1082万
+$22,721/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3167万
+$33,836/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$803万
+$20,906/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$803万
+$20,906/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$559万
+$22,363/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$823万
+$20,992/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$818万
+$21,073/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1078万
+$22,654/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 936呎 (3房)
+$3205万
+$34,237/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$800万
+$20,845/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$800万
+$20,845/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$545万
+$21,816/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$820万
+$20,930/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$815万
+$21,011/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1087万
+$22,836/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3195万
+$34,100/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$798万
+$20,782/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$798万
+$20,782/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$550万
+$21,993/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$818万
+$20,865/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$813万
+$20,948/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1078万
+$22,642/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3160万
+$33,725/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$796万
+$20,721/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$796万
+$20,721/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$548万
+$21,931/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$815万
+$20,803/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$810万
+$20,883/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1057万
+$22,205/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3184万
+$33,979/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$796万
+$20,721/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$805万
+$20,951/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$557万
+$22,292/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$815万
+$20,803/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$810万
+$20,883/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1057万
+$22,205/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3176万
+$33,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$793万
+$20,660/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$793万
+$20,660/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$547万
+$21,865/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$813万
+$20,739/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$808万
+$20,821/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1054万
+$22,139/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3167万
+$33,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$804万
+$20,940/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$813万
+$21,169/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$539万
+$21,560/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$811万
+$20,677/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$805万
+$20,756/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1051万
+$22,073/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+$3158万
+$33,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$789万
+$20,536/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$797万
+$20,764/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$543万
+$21,738/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$808万
+$20,615/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$812万
+$20,923/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1048万
+$22,007/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$786万
+$20,473/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$799万
+$20,814/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$545万
+$21,792/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$819万
+$20,893/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$800万
+$20,630/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1044万
+$21,940/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$797万
+$20,752/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$784万
+$20,412/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$534万
+$21,373/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$821万
+$20,944/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$807万
+$20,794/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1041万
+$21,872/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$790万
+$20,577/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$781万
+$20,351/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$548万
+$21,900/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$801万
+$20,427/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$809万
+$20,844/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1050万
+$22,048/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$779万
+$20,288/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$779万
+$20,288/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$531万
+$21,244/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$798万
+$20,362/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$793万
+$20,440/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1035万
+$21,740/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$779万
+$20,288/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$779万
+$20,288/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$531万
+$21,240/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$798万
+$20,362/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$793万
+$20,440/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1035万
+$21,740/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$790万
+$20,564/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$777万
+$20,227/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$530万
+$21,182/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$809万
+$20,639/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$791万
+$20,375/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1072万
+$22,517/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$774万
+$20,163/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$791万
+$20,611/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$528万
+$21,118/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$793万
+$20,239/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$788万
+$20,313/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1046万
+$21,968/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$772万
+$20,102/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$772万
+$20,102/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$526万
+$21,056/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$791万
+$20,174/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$794万
+$20,475/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1025万
+$21,539/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$767万
+$19,978/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$767万
+$19,978/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$523万
+$20,927/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$786万
+$20,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$737万
+$19,004/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1019万
+$21,407/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 937呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 424呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 384呎 (1房)
+$760万
+$19,788/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 384呎 (1房)
+$781万
+$20,343/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 250呎 (开放式)
+$518万
+$20,729/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>J | 392呎 (1房)
+$735万
+$18,756/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>K | 388呎 (1房)
+$730万
+$18,825/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>L | 476呎 (2房)
+$1010万
+$21,209/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1204呎 (3房)
+$5422万
+$45,037/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>B | 611呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 416呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 250呎 (开放式)
+$582万
+$23,280/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 390呎 (1房)
+$856万
+$21,939/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 395呎 (1房)
+$867万
+$21,941/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$590万
+$23,604/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 384呎 (1房)
+$852万
+$22,175/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 604呎 (2房)
+$1380万
+$22,856/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+      <c r="M5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1870万
+$30,700/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1476万
+$35,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1747万
+$30,975/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$595万
+$23,782/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$832万
+$21,321/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$805万
+$20,372/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$563万
+$22,540/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$828万
+$21,551/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1311万
+$21,703/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2271万
+$33,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1849万
+$30,356/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1460万
+$35,089/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1727万
+$30,629/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$590万
+$23,581/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$824万
+$21,138/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$798万
+$20,200/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$568万
+$22,721/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$820万
+$21,366/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1300万
+$21,518/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2258万
+$33,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1859万
+$30,519/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1451万
+$34,889/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1746万
+$30,964/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$588万
+$23,515/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$838万
+$21,498/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$833万
+$21,078/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$566万
+$22,659/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$818万
+$21,302/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1296万
+$21,455/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2281万
+$33,650/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (1房)
+$1472万
+$31,053/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1828万
+$30,012/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1443万
+$34,690/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1708万
+$30,284/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$586万
+$23,450/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$820万
+$21,016/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$830万
+$21,019/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$556万
+$22,223/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$816万
+$21,241/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1292万
+$21,394/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2195万
+$32,379/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (1房)
+$1447万
+$30,534/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1817万
+$29,839/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1435万
+$34,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1717万
+$30,446/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$585万
+$23,384/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$831万
+$21,303/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$828万
+$20,960/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$563万
+$22,531/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$813万
+$21,178/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1288万
+$21,367/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2183万
+$32,193/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (1房)
+$1439万
+$30,357/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1807万
+$29,667/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1426万
+$34,291/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1717万
+$30,438/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$583万
+$23,310/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$837万
+$21,474/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$825万
+$20,898/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$562万
+$22,465/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$811万
+$21,117/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1299万
+$21,505/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2170万
+$32,007/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1589万
+$33,603/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1796万
+$29,496/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1418万
+$34,091/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1679万
+$29,767/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$560万
+$22,417/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$819万
+$21,002/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$834万
+$21,124/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$549万
+$21,971/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$806万
+$20,993/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1327万
+$22,004/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2157万
+$31,821/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1580万
+$33,404/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1786万
+$29,323/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1410万
+$33,889/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1669万
+$29,593/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$559万
+$22,355/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$821万
+$21,057/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$827万
+$20,948/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$557万
+$22,271/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$804万
+$20,932/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1274万
+$21,084/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2145万
+$31,635/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1571万
+$33,207/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1775万
+$29,152/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1402万
+$33,690/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1659万
+$29,421/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$568万
+$22,736/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$805万
+$20,649/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$830万
+$21,003/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$555万
+$22,209/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$801万
+$20,869/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1291万
+$21,372/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1765万
+$28,979/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1393万
+$33,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1650万
+$29,248/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$567万
+$22,666/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$803万
+$20,589/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$814万
+$20,597/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$554万
+$22,143/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$799万
+$20,808/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1266万
+$20,996/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1760万
+$28,893/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1389万
+$33,389/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1645万
+$29,162/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$554万
+$22,161/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$801万
+$20,529/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$811万
+$20,538/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$552万
+$22,077/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$797万
+$20,747/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1262万
+$20,898/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1754万
+$28,807/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1385万
+$33,291/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1640万
+$29,076/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$543万
+$21,733/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$798万
+$20,467/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$809万
+$20,479/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$541万
+$21,654/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$794万
+$20,684/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1273万
+$21,069/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1749万
+$28,720/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1381万
+$33,190/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1635万
+$28,990/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$542万
+$21,672/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$796万
+$20,407/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$820万
+$20,758/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$546万
+$21,829/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$792万
+$20,623/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1290万
+$21,351/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1744万
+$28,634/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1377万
+$33,091/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1630万
+$28,904/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$540万
+$21,607/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$793万
+$20,345/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$804万
+$20,358/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$538万
+$21,528/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$790万
+$20,562/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1251万
+$20,713/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2107万
+$31,078/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1543万
+$32,613/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1744万
+$28,634/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1377万
+$33,091/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1630万
+$28,904/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$540万
+$21,607/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$793万
+$20,345/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$804万
+$20,358/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$538万
+$21,528/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$803万
+$20,904/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1251万
+$20,748/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2101万
+$30,985/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1538万
+$32,514/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1739万
+$28,549/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1372万
+$32,990/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1625万
+$28,818/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$554万
+$22,144/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$804万
+$20,623/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$811万
+$20,522/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$557万
+$22,298/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$787万
+$20,498/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1247万
+$20,651/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2129万
+$31,407/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1533万
+$32,416/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1733万
+$28,463/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 415呎 (1房)
+$1231万
+$29,672/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1620万
+$28,731/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$537万
+$21,481/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$789万
+$20,225/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$813万
+$20,575/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$535万
+$21,398/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$785万
+$20,438/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1244万
+$20,590/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2320万
+$34,221/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1529万
+$32,317/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1728万
+$28,377/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1364万
+$32,791/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1616万
+$28,645/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$535万
+$21,416/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$786万
+$20,162/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$797万
+$20,178/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$533万
+$21,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$782万
+$20,374/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1240万
+$20,561/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2313万
+$34,118/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1524万
+$32,218/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1723万
+$28,290/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1360万
+$32,690/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1611万
+$28,559/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$534万
+$21,355/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$784万
+$20,102/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$795万
+$20,117/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$538万
+$21,508/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$780万
+$20,313/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1270万
+$21,069/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2299万
+$33,912/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1514万
+$32,019/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1931万
+$31,711/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1352万
+$32,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1601万
+$28,387/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$532万
+$21,290/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$782万
+$20,042/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$805万
+$20,392/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$539万
+$21,564/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$778万
+$20,252/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1232万
+$20,437/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2285万
+$33,705/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1505万
+$31,822/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1919万
+$31,517/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1343万
+$32,291/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1591万
+$28,213/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$540万
+$21,583/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$795万
+$20,379/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$803万
+$20,329/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$529万
+$21,146/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$775万
+$20,189/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1229万
+$20,376/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2271万
+$33,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1496万
+$31,624/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1908万
+$31,323/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1335万
+$32,091/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1784万
+$31,624/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$529万
+$21,164/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$792万
+$20,319/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$801万
+$20,269/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$527万
+$21,082/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$773万
+$20,128/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1252万
+$20,730/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2271万
+$33,499/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1496万
+$31,624/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1908万
+$31,323/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1335万
+$32,091/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1784万
+$31,624/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$538万
+$21,517/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$792万
+$20,319/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$788万
+$19,937/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$527万
+$21,082/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$773万
+$20,128/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 603呎 (2房)
+$1225万
+$20,313/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2257万
+$33,292/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1486万
+$31,427/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1896万
+$31,130/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1327万
+$31,892/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1773万
+$31,429/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$536万
+$21,451/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$783万
+$20,078/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$785万
+$19,877/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$526万
+$21,020/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$783万
+$20,399/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1221万
+$20,219/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2243万
+$33,086/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1477万
+$31,228/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1884万
+$30,934/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1318万
+$31,690/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1762万
+$31,234/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$545万
+$21,817/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$788万
+$20,195/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$796万
+$20,146/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$530万
+$21,188/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$768万
+$20,004/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1217万
+$20,156/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+$2229万
+$32,879/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+$1468万
+$31,032/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1872万
+$30,742/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1310万
+$31,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1751万
+$31,041/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$535万
+$21,395/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$785万
+$20,132/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$793万
+$20,086/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$522万
+$20,894/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$779万
+$20,275/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1214万
+$20,095/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1854万
+$30,450/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1298万
+$31,190/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1734万
+$30,748/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$540万
+$21,620/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$780万
+$20,008/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$776万
+$19,636/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$528万
+$21,114/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$774万
+$20,149/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1206万
+$19,971/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 678呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 473呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 477呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>D | 609呎 (2房)
+$1831万
+$30,062/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+$1281万
+$30,791/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>F | 564呎 (2房)
+$1712万
+$30,358/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$525万
+$21,002/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (1房)
+$773万
+$19,821/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (1房)
+$782万
+$19,808/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>K | 250呎 (开放式)
+$515万
+$20,592/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>L | 384呎 (1房)
+$767万
+$19,985/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>M | 604呎 (2房)
+$1215万
+$20,118/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1444万
+$22,255/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1440万
+$22,184/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$613万
+$20,172/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$609万
+$20,109/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1411万
+$21,736/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1430万
+$22,028/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$610万
+$20,055/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$616万
+$20,253/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1394万
+$21,477/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1428万
+$22,002/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$613万
+$20,155/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$609万
+$20,020/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1415万
+$21,807/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1372万
+$21,148/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$610万
+$20,058/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$598万
+$19,744/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1722万
+$27,456/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 627呎 (3房)
+$1694万
+$27,010/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$638万
+$22,634/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$644万
+$22,848/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1524万
+$23,488/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1497万
+$23,069/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$617万
+$20,361/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$626万
+$20,664/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1481万
+$22,820/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1462万
+$22,530/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$662万
+$21,861/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$622万
+$20,540/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1440万
+$22,215/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1445万
+$22,260/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$610万
+$20,124/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$619万
+$20,415/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1422万
+$21,916/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 648呎 (3房)
+$1419万
+$21,904/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$606万
+$20,005/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$615万
+$20,223/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1711万
+$27,289/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 627呎 (3房)
+$1724万
+$27,498/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$656万
+$23,263/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$658万
+$23,339/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1521万
+$23,468/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 648呎 (3房)
+$1494万
+$23,049/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$657万
+$21,671/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$664万
+$21,834/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1491万
+$23,006/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1480万
+$22,809/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$660万
+$21,708/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$660万
+$21,775/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1482万
+$22,836/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1472万
+$22,673/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$660万
+$21,698/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$674万
+$22,176/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1473万
+$22,700/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1479万
+$22,788/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$645万
+$21,212/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$652万
+$21,446/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1759万
+$28,046/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 627呎 (3房)
+$1783万
+$28,433/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$681万
+$24,147/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$688万
+$24,415/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座D座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1401万
+$21,615/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1388万
+$21,386/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$625万
+$20,622/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$628万
+$20,740/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1381万
+$21,309/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1391万
+$21,432/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$611万
+$20,096/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$1391万
+$45,905/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1380万
+$21,299/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1390万
+$21,420/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$617万
+$20,308/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$611万
+$20,093/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1372万
+$21,141/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 648呎 (3房)
+$1359万
+$20,975/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$610万
+$20,074/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$607万
+$19,972/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1682万
+$26,821/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 626呎 (3房)
+$1685万
+$26,924/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$661万
+$23,433/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$672万
+$23,827/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -666,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
         <v>31600000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>33725</v>
+        <v>33761</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -36929,10 +36929,10 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3160万
-$33,725/呎
-(26年-06月)</t>
+$33,761/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -22318,14 +22318,14 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>13287600</v>
+        <v>13509060</v>
       </c>
       <c r="L334" s="5" t="n">
-        <v>31941</v>
+        <v>32474</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
@@ -23086,14 +23086,14 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>13137300</v>
+        <v>13356255</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>31580</v>
+        <v>32106</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
@@ -23846,14 +23846,14 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>13062600</v>
+        <v>13280310</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>31400</v>
+        <v>31924</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
@@ -24606,14 +24606,14 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>12987900</v>
+        <v>13204365</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>31221</v>
+        <v>31741</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
@@ -25358,14 +25358,14 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>12913200</v>
+        <v>13128420</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>31041</v>
+        <v>31559</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -26110,14 +26110,14 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>12838500</v>
+        <v>13052475</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>30862</v>
+        <v>31376</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
@@ -26862,14 +26862,14 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>12763800</v>
+        <v>12976530</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>30682</v>
+        <v>31194</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
@@ -27056,14 +27056,14 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>14304600</v>
+        <v>14543010</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>30242</v>
+        <v>30746</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -27614,14 +27614,14 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K418" s="5" t="n">
-        <v>12688200</v>
+        <v>12899670</v>
       </c>
       <c r="L418" s="5" t="n">
-        <v>30500</v>
+        <v>31009</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
@@ -27808,14 +27808,14 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>14220000</v>
+        <v>14457000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>30063</v>
+        <v>30564</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -28366,14 +28366,14 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>12613500</v>
+        <v>12823725</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>30321</v>
+        <v>30826</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
@@ -28560,14 +28560,14 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>14136300</v>
+        <v>14371905</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>29886</v>
+        <v>30385</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -29118,14 +29118,14 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>12538800</v>
+        <v>12747780</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>30141</v>
+        <v>30644</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
@@ -29886,14 +29886,14 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12501000</v>
+        <v>12709350</v>
       </c>
       <c r="L454" s="5" t="n">
-        <v>30050</v>
+        <v>30551</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
@@ -30654,14 +30654,14 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K466" s="5" t="n">
-        <v>12464100</v>
+        <v>12671835</v>
       </c>
       <c r="L466" s="5" t="n">
-        <v>29962</v>
+        <v>30461</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
@@ -31422,14 +31422,14 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>12426300</v>
+        <v>12633405</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>29871</v>
+        <v>30369</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -32190,14 +32190,14 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>12389400</v>
+        <v>12595890</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>29782</v>
+        <v>30279</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
@@ -32958,14 +32958,14 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>12389400</v>
+        <v>12595890</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>29782</v>
+        <v>30279</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
@@ -33152,14 +33152,14 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>13883400</v>
+        <v>14114790</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>29352</v>
+        <v>29841</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -33710,14 +33710,14 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K514" s="5" t="n">
-        <v>12351600</v>
+        <v>12557460</v>
       </c>
       <c r="L514" s="5" t="n">
-        <v>29691</v>
+        <v>30186</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
@@ -33904,14 +33904,14 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K517" s="5" t="n">
-        <v>13841100</v>
+        <v>14071785</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>29262</v>
+        <v>29750</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
@@ -34656,14 +34656,14 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>13799700</v>
+        <v>14029695</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>29175</v>
+        <v>29661</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
@@ -35214,14 +35214,14 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>12276900</v>
+        <v>12481515</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>29512</v>
+        <v>30004</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
@@ -35408,14 +35408,14 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>13757400</v>
+        <v>13986690</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>29085</v>
+        <v>29570</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
@@ -35470,14 +35470,14 @@
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K542" s="5" t="n">
-        <v>20881800</v>
+        <v>21229830</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>30799</v>
+        <v>31312</v>
       </c>
       <c r="M542" s="3" t="inlineStr">
         <is>
@@ -35966,14 +35966,14 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>12239100</v>
+        <v>12443085</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>29421</v>
+        <v>29911</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
@@ -36160,14 +36160,14 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>13715100</v>
+        <v>13943685</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>28996</v>
+        <v>29479</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
@@ -36222,14 +36222,14 @@
       </c>
       <c r="J554" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K554" s="5" t="n">
-        <v>20818800</v>
+        <v>21165780</v>
       </c>
       <c r="L554" s="5" t="n">
-        <v>30706</v>
+        <v>31218</v>
       </c>
       <c r="M554" s="3" t="inlineStr">
         <is>
@@ -36718,14 +36718,14 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>12164400</v>
+        <v>12367140</v>
       </c>
       <c r="L562" s="5" t="n">
-        <v>29241</v>
+        <v>29729</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
@@ -36780,14 +36780,14 @@
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K563" s="5" t="n">
-        <v>17380800</v>
+        <v>17670480</v>
       </c>
       <c r="L563" s="5" t="n">
-        <v>28540</v>
+        <v>29016</v>
       </c>
       <c r="M563" s="3" t="inlineStr">
         <is>
@@ -36912,14 +36912,14 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K565" s="5" t="n">
-        <v>13630500</v>
+        <v>13857675</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>28817</v>
+        <v>29297</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -36974,14 +36974,14 @@
       </c>
       <c r="J566" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K566" s="5" t="n">
-        <v>20692800</v>
+        <v>21037680</v>
       </c>
       <c r="L566" s="5" t="n">
-        <v>30520</v>
+        <v>31029</v>
       </c>
       <c r="M566" s="3" t="inlineStr">
         <is>
@@ -37470,14 +37470,14 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K574" s="5" t="n">
-        <v>12089700</v>
+        <v>12291195</v>
       </c>
       <c r="L574" s="5" t="n">
-        <v>29062</v>
+        <v>29546</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
@@ -37532,14 +37532,14 @@
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K575" s="5" t="n">
-        <v>17274600</v>
+        <v>17562510</v>
       </c>
       <c r="L575" s="5" t="n">
-        <v>28366</v>
+        <v>28838</v>
       </c>
       <c r="M575" s="3" t="inlineStr">
         <is>
@@ -37664,14 +37664,14 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>13546800</v>
+        <v>13772580</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>28640</v>
+        <v>29118</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
@@ -37726,14 +37726,14 @@
       </c>
       <c r="J578" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K578" s="5" t="n">
-        <v>20566800</v>
+        <v>20909580</v>
       </c>
       <c r="L578" s="5" t="n">
-        <v>30335</v>
+        <v>30840</v>
       </c>
       <c r="M578" s="3" t="inlineStr">
         <is>
@@ -38160,14 +38160,14 @@
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K585" s="5" t="n">
-        <v>16052400</v>
+        <v>16319940</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>28462</v>
+        <v>28936</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -38222,14 +38222,14 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>12015000</v>
+        <v>12215250</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>28882</v>
+        <v>29364</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
@@ -38284,14 +38284,14 @@
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>17168400</v>
+        <v>17454540</v>
       </c>
       <c r="L587" s="5" t="n">
-        <v>28191</v>
+        <v>28661</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
@@ -38416,14 +38416,14 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>13462200</v>
+        <v>13686570</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>28461</v>
+        <v>28936</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
@@ -38478,14 +38478,14 @@
       </c>
       <c r="J590" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K590" s="5" t="n">
-        <v>20440800</v>
+        <v>20781480</v>
       </c>
       <c r="L590" s="5" t="n">
-        <v>30149</v>
+        <v>30651</v>
       </c>
       <c r="M590" s="3" t="inlineStr">
         <is>
@@ -38912,14 +38912,14 @@
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K597" s="5" t="n">
-        <v>16052400</v>
+        <v>16319940</v>
       </c>
       <c r="L597" s="5" t="n">
-        <v>28462</v>
+        <v>28936</v>
       </c>
       <c r="M597" s="3" t="inlineStr">
         <is>
@@ -38974,14 +38974,14 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K598" s="5" t="n">
-        <v>12015000</v>
+        <v>12215250</v>
       </c>
       <c r="L598" s="5" t="n">
-        <v>28882</v>
+        <v>29364</v>
       </c>
       <c r="M598" s="3" t="inlineStr">
         <is>
@@ -39036,14 +39036,14 @@
       </c>
       <c r="J599" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K599" s="5" t="n">
-        <v>17168400</v>
+        <v>17454540</v>
       </c>
       <c r="L599" s="5" t="n">
-        <v>28191</v>
+        <v>28661</v>
       </c>
       <c r="M599" s="3" t="inlineStr">
         <is>
@@ -39168,14 +39168,14 @@
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K601" s="5" t="n">
-        <v>13462200</v>
+        <v>13686570</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>28461</v>
+        <v>28936</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
@@ -39230,14 +39230,14 @@
       </c>
       <c r="J602" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K602" s="5" t="n">
-        <v>20440800</v>
+        <v>20781480</v>
       </c>
       <c r="L602" s="5" t="n">
-        <v>30149</v>
+        <v>30651</v>
       </c>
       <c r="M602" s="3" t="inlineStr">
         <is>
@@ -39664,14 +39664,14 @@
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K609" s="5" t="n">
-        <v>15953400</v>
+        <v>16219290</v>
       </c>
       <c r="L609" s="5" t="n">
-        <v>28286</v>
+        <v>28758</v>
       </c>
       <c r="M609" s="3" t="inlineStr">
         <is>
@@ -39726,14 +39726,14 @@
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K610" s="5" t="n">
-        <v>11940300</v>
+        <v>12139305</v>
       </c>
       <c r="L610" s="5" t="n">
-        <v>28703</v>
+        <v>29181</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
@@ -39788,14 +39788,14 @@
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K611" s="5" t="n">
-        <v>17062200</v>
+        <v>17346570</v>
       </c>
       <c r="L611" s="5" t="n">
-        <v>28017</v>
+        <v>28484</v>
       </c>
       <c r="M611" s="3" t="inlineStr">
         <is>
@@ -39920,14 +39920,14 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K613" s="5" t="n">
-        <v>13378500</v>
+        <v>13601475</v>
       </c>
       <c r="L613" s="5" t="n">
-        <v>28284</v>
+        <v>28756</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
@@ -39982,14 +39982,14 @@
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K614" s="5" t="n">
-        <v>20314800</v>
+        <v>20653380</v>
       </c>
       <c r="L614" s="5" t="n">
-        <v>29963</v>
+        <v>30462</v>
       </c>
       <c r="M614" s="3" t="inlineStr">
         <is>
@@ -40416,14 +40416,14 @@
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K621" s="5" t="n">
-        <v>15854400</v>
+        <v>16118640</v>
       </c>
       <c r="L621" s="5" t="n">
-        <v>28111</v>
+        <v>28579</v>
       </c>
       <c r="M621" s="3" t="inlineStr">
         <is>
@@ -40478,14 +40478,14 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K622" s="5" t="n">
-        <v>11864700</v>
+        <v>12062445</v>
       </c>
       <c r="L622" s="5" t="n">
-        <v>28521</v>
+        <v>28996</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
@@ -40540,14 +40540,14 @@
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K623" s="5" t="n">
-        <v>16955100</v>
+        <v>17237685</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>27841</v>
+        <v>28305</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -40672,14 +40672,14 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K625" s="5" t="n">
-        <v>13293900</v>
+        <v>13515465</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>28105</v>
+        <v>28574</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
@@ -40734,14 +40734,14 @@
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K626" s="5" t="n">
-        <v>20188800</v>
+        <v>20525280</v>
       </c>
       <c r="L626" s="5" t="n">
-        <v>29777</v>
+        <v>30273</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
@@ -41168,14 +41168,14 @@
       </c>
       <c r="J633" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K633" s="5" t="n">
-        <v>15756300</v>
+        <v>16018905</v>
       </c>
       <c r="L633" s="5" t="n">
-        <v>27937</v>
+        <v>28402</v>
       </c>
       <c r="M633" s="3" t="inlineStr">
         <is>
@@ -41230,14 +41230,14 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K634" s="5" t="n">
-        <v>11790000</v>
+        <v>11986500</v>
       </c>
       <c r="L634" s="5" t="n">
-        <v>28341</v>
+        <v>28814</v>
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
@@ -41292,14 +41292,14 @@
       </c>
       <c r="J635" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K635" s="5" t="n">
-        <v>16849800</v>
+        <v>17130630</v>
       </c>
       <c r="L635" s="5" t="n">
-        <v>27668</v>
+        <v>28129</v>
       </c>
       <c r="M635" s="3" t="inlineStr">
         <is>
@@ -41424,14 +41424,14 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K637" s="5" t="n">
-        <v>13210200</v>
+        <v>13430370</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>27929</v>
+        <v>28394</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
@@ -41486,14 +41486,14 @@
       </c>
       <c r="J638" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K638" s="5" t="n">
-        <v>20062800</v>
+        <v>20397180</v>
       </c>
       <c r="L638" s="5" t="n">
-        <v>29591</v>
+        <v>30084</v>
       </c>
       <c r="M638" s="3" t="inlineStr">
         <is>
@@ -41920,14 +41920,14 @@
       </c>
       <c r="J645" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K645" s="5" t="n">
-        <v>15607800</v>
+        <v>15867930</v>
       </c>
       <c r="L645" s="5" t="n">
-        <v>27673</v>
+        <v>28135</v>
       </c>
       <c r="M645" s="3" t="inlineStr">
         <is>
@@ -41982,14 +41982,14 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K646" s="5" t="n">
-        <v>11677500</v>
+        <v>11872125</v>
       </c>
       <c r="L646" s="5" t="n">
-        <v>28071</v>
+        <v>28539</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
@@ -42044,14 +42044,14 @@
       </c>
       <c r="J647" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K647" s="5" t="n">
-        <v>16689600</v>
+        <v>16967760</v>
       </c>
       <c r="L647" s="5" t="n">
-        <v>27405</v>
+        <v>27862</v>
       </c>
       <c r="M647" s="3" t="inlineStr">
         <is>
@@ -42688,14 +42688,14 @@
       </c>
       <c r="J657" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K657" s="5" t="n">
-        <v>15409800</v>
+        <v>15666630</v>
       </c>
       <c r="L657" s="5" t="n">
-        <v>27322</v>
+        <v>27778</v>
       </c>
       <c r="M657" s="3" t="inlineStr">
         <is>
@@ -42750,14 +42750,14 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K658" s="5" t="n">
-        <v>11528100</v>
+        <v>11720235</v>
       </c>
       <c r="L658" s="5" t="n">
-        <v>27712</v>
+        <v>28174</v>
       </c>
       <c r="M658" s="3" t="inlineStr">
         <is>
@@ -42812,14 +42812,14 @@
       </c>
       <c r="J659" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K659" s="5" t="n">
-        <v>16477200</v>
+        <v>16751820</v>
       </c>
       <c r="L659" s="5" t="n">
-        <v>27056</v>
+        <v>27507</v>
       </c>
       <c r="M659" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -666,12 +666,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -22318,18 +22318,18 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>13509060</v>
+        <v>13435200</v>
       </c>
       <c r="L334" s="5" t="n">
-        <v>32474</v>
+        <v>32296</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -23086,18 +23086,18 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>13356255</v>
+        <v>13283200</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>32106</v>
+        <v>31931</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23846,18 +23846,18 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>13280310</v>
+        <v>13207700</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>31924</v>
+        <v>31749</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -24606,18 +24606,18 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>13204365</v>
+        <v>13132200</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>31741</v>
+        <v>31568</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25358,18 +25358,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>13128420</v>
+        <v>13056600</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>31559</v>
+        <v>31386</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -26110,18 +26110,18 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>13052475</v>
+        <v>12981100</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>31376</v>
+        <v>31205</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26862,18 +26862,18 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>12976530</v>
+        <v>12905600</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>31194</v>
+        <v>31023</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -27056,18 +27056,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>14543010</v>
+        <v>14762500</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>30746</v>
+        <v>31210</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -27614,18 +27614,18 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K418" s="5" t="n">
-        <v>12899670</v>
+        <v>12829100</v>
       </c>
       <c r="L418" s="5" t="n">
-        <v>31009</v>
+        <v>30839</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
@@ -27808,18 +27808,18 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>14457000</v>
+        <v>14675200</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>30564</v>
+        <v>31026</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -28366,18 +28366,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>12823725</v>
+        <v>12753600</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>30826</v>
+        <v>30658</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -28560,18 +28560,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>14371905</v>
+        <v>14588800</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>30385</v>
+        <v>30843</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -29118,18 +29118,18 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>12747780</v>
+        <v>12678100</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>30644</v>
+        <v>30476</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N442" s="3" t="inlineStr">
@@ -29886,18 +29886,18 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12709350</v>
+        <v>12639900</v>
       </c>
       <c r="L454" s="5" t="n">
-        <v>30551</v>
+        <v>30384</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -30654,18 +30654,18 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K466" s="5" t="n">
-        <v>12671835</v>
+        <v>12602500</v>
       </c>
       <c r="L466" s="5" t="n">
-        <v>30461</v>
+        <v>30294</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N466" s="3" t="inlineStr">
@@ -31422,18 +31422,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>12633405</v>
+        <v>12564300</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>30369</v>
+        <v>30203</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -32190,18 +32190,18 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>12595890</v>
+        <v>12527000</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>30279</v>
+        <v>30113</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32958,18 +32958,18 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>12595890</v>
+        <v>12527000</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>30279</v>
+        <v>30113</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N502" s="3" t="inlineStr">
@@ -33152,18 +33152,18 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>14114790</v>
+        <v>14886000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>29841</v>
+        <v>31471</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -33710,18 +33710,18 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K514" s="5" t="n">
-        <v>12557460</v>
+        <v>12488800</v>
       </c>
       <c r="L514" s="5" t="n">
-        <v>30186</v>
+        <v>30021</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -33904,18 +33904,18 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K517" s="5" t="n">
-        <v>14071785</v>
+        <v>14284100</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>29750</v>
+        <v>30199</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N517" s="3" t="inlineStr">
@@ -34656,18 +34656,18 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>14029695</v>
+        <v>14241400</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>29661</v>
+        <v>30109</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N529" s="3" t="inlineStr">
@@ -35214,18 +35214,18 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>12481515</v>
+        <v>12413300</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>30004</v>
+        <v>29840</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N538" s="3" t="inlineStr">
@@ -35408,18 +35408,18 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>13986690</v>
+        <v>14197700</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>29570</v>
+        <v>30016</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N541" s="3" t="inlineStr">
@@ -35470,18 +35470,18 @@
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K542" s="5" t="n">
-        <v>21229830</v>
+        <v>21438300</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>31312</v>
+        <v>31620</v>
       </c>
       <c r="M542" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N542" s="3" t="inlineStr">
@@ -35966,18 +35966,18 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>12443085</v>
+        <v>12375000</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>29911</v>
+        <v>29748</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N550" s="3" t="inlineStr">
@@ -36160,18 +36160,18 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>13943685</v>
+        <v>14154100</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>29479</v>
+        <v>29924</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N553" s="3" t="inlineStr">
@@ -36222,18 +36222,18 @@
       </c>
       <c r="J554" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K554" s="5" t="n">
-        <v>21165780</v>
+        <v>21373600</v>
       </c>
       <c r="L554" s="5" t="n">
-        <v>31218</v>
+        <v>31524</v>
       </c>
       <c r="M554" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N554" s="3" t="inlineStr">
@@ -36718,18 +36718,18 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>12367140</v>
+        <v>12299500</v>
       </c>
       <c r="L562" s="5" t="n">
-        <v>29729</v>
+        <v>29566</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N562" s="3" t="inlineStr">
@@ -36773,25 +36773,25 @@
         </is>
       </c>
       <c r="H563" s="5" t="n">
-        <v>19312000</v>
+        <v>1902700019312000</v>
       </c>
       <c r="I563" s="5" t="n">
-        <v>31711</v>
+        <v>3124302166358</v>
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K563" s="5" t="n">
-        <v>17670480</v>
+        <v>1758071034093900</v>
       </c>
       <c r="L563" s="5" t="n">
-        <v>29016</v>
+        <v>2886816147937</v>
       </c>
       <c r="M563" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N563" s="3" t="inlineStr">
@@ -36912,18 +36912,18 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K565" s="5" t="n">
-        <v>13857675</v>
+        <v>14066800</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>29297</v>
+        <v>29740</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N565" s="3" t="inlineStr">
@@ -36974,18 +36974,18 @@
       </c>
       <c r="J566" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K566" s="5" t="n">
-        <v>21037680</v>
+        <v>21244200</v>
       </c>
       <c r="L566" s="5" t="n">
-        <v>31029</v>
+        <v>31334</v>
       </c>
       <c r="M566" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N566" s="3" t="inlineStr">
@@ -37470,18 +37470,18 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K574" s="5" t="n">
-        <v>12291195</v>
+        <v>12224000</v>
       </c>
       <c r="L574" s="5" t="n">
-        <v>29546</v>
+        <v>29385</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N574" s="3" t="inlineStr">
@@ -37525,25 +37525,25 @@
         </is>
       </c>
       <c r="H575" s="5" t="n">
-        <v>19194000</v>
+        <v>1891000019194000</v>
       </c>
       <c r="I575" s="5" t="n">
-        <v>31517</v>
+        <v>3105090343504</v>
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K575" s="5" t="n">
-        <v>17562510</v>
+        <v>1747260380235000</v>
       </c>
       <c r="L575" s="5" t="n">
-        <v>28838</v>
+        <v>2869064663768</v>
       </c>
       <c r="M575" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N575" s="3" t="inlineStr">
@@ -37664,18 +37664,18 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>13772580</v>
+        <v>13980400</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>29118</v>
+        <v>29557</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -37726,18 +37726,18 @@
       </c>
       <c r="J578" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K578" s="5" t="n">
-        <v>20909580</v>
+        <v>21114800</v>
       </c>
       <c r="L578" s="5" t="n">
-        <v>30840</v>
+        <v>31143</v>
       </c>
       <c r="M578" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N578" s="3" t="inlineStr">
@@ -38153,25 +38153,25 @@
         </is>
       </c>
       <c r="H585" s="5" t="n">
-        <v>17836000</v>
+        <v>1757200017836000</v>
       </c>
       <c r="I585" s="5" t="n">
-        <v>31624</v>
+        <v>3115602868504</v>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K585" s="5" t="n">
-        <v>16319940</v>
+        <v>1623630851480200</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>28936</v>
+        <v>2878778105461</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N585" s="3" t="inlineStr">
@@ -38222,18 +38222,18 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>12215250</v>
+        <v>12148500</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>29364</v>
+        <v>29203</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N586" s="3" t="inlineStr">
@@ -38277,25 +38277,25 @@
         </is>
       </c>
       <c r="H587" s="5" t="n">
-        <v>19076000</v>
+        <v>1879400019076000</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>31323</v>
+        <v>3086042724263</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>17454540</v>
+        <v>1736542125125900</v>
       </c>
       <c r="L587" s="5" t="n">
-        <v>28661</v>
+        <v>2851464901685</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N587" s="3" t="inlineStr">
@@ -38416,18 +38416,18 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>13686570</v>
+        <v>13893100</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>28936</v>
+        <v>29372</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N589" s="3" t="inlineStr">
@@ -38478,18 +38478,18 @@
       </c>
       <c r="J590" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K590" s="5" t="n">
-        <v>20781480</v>
+        <v>20985500</v>
       </c>
       <c r="L590" s="5" t="n">
-        <v>30651</v>
+        <v>30952</v>
       </c>
       <c r="M590" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N590" s="3" t="inlineStr">
@@ -38905,25 +38905,25 @@
         </is>
       </c>
       <c r="H597" s="5" t="n">
-        <v>17836000</v>
+        <v>1757200017836000</v>
       </c>
       <c r="I597" s="5" t="n">
-        <v>31624</v>
+        <v>3115602868504</v>
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K597" s="5" t="n">
-        <v>16319940</v>
+        <v>1623630851480200</v>
       </c>
       <c r="L597" s="5" t="n">
-        <v>28936</v>
+        <v>2878778105461</v>
       </c>
       <c r="M597" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N597" s="3" t="inlineStr">
@@ -38974,18 +38974,18 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K598" s="5" t="n">
-        <v>12215250</v>
+        <v>12148500</v>
       </c>
       <c r="L598" s="5" t="n">
-        <v>29364</v>
+        <v>29203</v>
       </c>
       <c r="M598" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N598" s="3" t="inlineStr">
@@ -39029,25 +39029,25 @@
         </is>
       </c>
       <c r="H599" s="5" t="n">
-        <v>19076000</v>
+        <v>1879400019076000</v>
       </c>
       <c r="I599" s="5" t="n">
-        <v>31323</v>
+        <v>3086042724263</v>
       </c>
       <c r="J599" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K599" s="5" t="n">
-        <v>17454540</v>
+        <v>1736542125125900</v>
       </c>
       <c r="L599" s="5" t="n">
-        <v>28661</v>
+        <v>2851464901685</v>
       </c>
       <c r="M599" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N599" s="3" t="inlineStr">
@@ -39168,18 +39168,18 @@
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K601" s="5" t="n">
-        <v>13686570</v>
+        <v>13893100</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>28936</v>
+        <v>29372</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N601" s="3" t="inlineStr">
@@ -39230,18 +39230,18 @@
       </c>
       <c r="J602" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K602" s="5" t="n">
-        <v>20781480</v>
+        <v>20985500</v>
       </c>
       <c r="L602" s="5" t="n">
-        <v>30651</v>
+        <v>30952</v>
       </c>
       <c r="M602" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N602" s="3" t="inlineStr">
@@ -39657,25 +39657,25 @@
         </is>
       </c>
       <c r="H609" s="5" t="n">
-        <v>17726000</v>
+        <v>1746400017726000</v>
       </c>
       <c r="I609" s="5" t="n">
-        <v>31429</v>
+        <v>3096453932138</v>
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K609" s="5" t="n">
-        <v>16219290</v>
+        <v>1613651786378500</v>
       </c>
       <c r="L609" s="5" t="n">
-        <v>28758</v>
+        <v>2861084727621</v>
       </c>
       <c r="M609" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N609" s="3" t="inlineStr">
@@ -39726,18 +39726,18 @@
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K610" s="5" t="n">
-        <v>12139305</v>
+        <v>12072900</v>
       </c>
       <c r="L610" s="5" t="n">
-        <v>29181</v>
+        <v>29021</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N610" s="3" t="inlineStr">
@@ -39781,25 +39781,25 @@
         </is>
       </c>
       <c r="H611" s="5" t="n">
-        <v>18958000</v>
+        <v>1867800018958000</v>
       </c>
       <c r="I611" s="5" t="n">
-        <v>31130</v>
+        <v>3066995105021</v>
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K611" s="5" t="n">
-        <v>17346570</v>
+        <v>1725823870016800</v>
       </c>
       <c r="L611" s="5" t="n">
-        <v>28484</v>
+        <v>2833865139601</v>
       </c>
       <c r="M611" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N611" s="3" t="inlineStr">
@@ -39920,18 +39920,18 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K613" s="5" t="n">
-        <v>13601475</v>
+        <v>13806700</v>
       </c>
       <c r="L613" s="5" t="n">
-        <v>28756</v>
+        <v>29190</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N613" s="3" t="inlineStr">
@@ -39982,18 +39982,18 @@
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K614" s="5" t="n">
-        <v>20653380</v>
+        <v>20856100</v>
       </c>
       <c r="L614" s="5" t="n">
-        <v>30462</v>
+        <v>30761</v>
       </c>
       <c r="M614" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N614" s="3" t="inlineStr">
@@ -40409,25 +40409,25 @@
         </is>
       </c>
       <c r="H621" s="5" t="n">
-        <v>17616000</v>
+        <v>1735600017616000</v>
       </c>
       <c r="I621" s="5" t="n">
-        <v>31234</v>
+        <v>3077304995773</v>
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K621" s="5" t="n">
-        <v>16118640</v>
+        <v>1603672721276900</v>
       </c>
       <c r="L621" s="5" t="n">
-        <v>28579</v>
+        <v>2843391349782</v>
       </c>
       <c r="M621" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N621" s="3" t="inlineStr">
@@ -40478,18 +40478,18 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K622" s="5" t="n">
-        <v>12062445</v>
+        <v>11996500</v>
       </c>
       <c r="L622" s="5" t="n">
-        <v>28996</v>
+        <v>28838</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N622" s="3" t="inlineStr">
@@ -40533,25 +40533,25 @@
         </is>
       </c>
       <c r="H623" s="5" t="n">
-        <v>18839000</v>
+        <v>1856100018839000</v>
       </c>
       <c r="I623" s="5" t="n">
-        <v>30934</v>
+        <v>3047783282166</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K623" s="5" t="n">
-        <v>17237685</v>
+        <v>1715013216156900</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>28305</v>
+        <v>2816113655430</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N623" s="3" t="inlineStr">
@@ -40672,18 +40672,18 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K625" s="5" t="n">
-        <v>13515465</v>
+        <v>13719400</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>28574</v>
+        <v>29005</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N625" s="3" t="inlineStr">
@@ -40734,18 +40734,18 @@
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.58%</t>
         </is>
       </c>
       <c r="K626" s="5" t="n">
-        <v>20525280</v>
+        <v>20732100</v>
       </c>
       <c r="L626" s="5" t="n">
-        <v>30273</v>
+        <v>30578</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N626" s="3" t="inlineStr">
@@ -41161,25 +41161,25 @@
         </is>
       </c>
       <c r="H633" s="5" t="n">
-        <v>17507000</v>
+        <v>1724800017507000</v>
       </c>
       <c r="I633" s="5" t="n">
-        <v>31041</v>
+        <v>3058156059410</v>
       </c>
       <c r="J633" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K633" s="5" t="n">
-        <v>16018905</v>
+        <v>1593693656176100</v>
       </c>
       <c r="L633" s="5" t="n">
-        <v>28402</v>
+        <v>2825697971943</v>
       </c>
       <c r="M633" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N633" s="3" t="inlineStr">
@@ -41230,18 +41230,18 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K634" s="5" t="n">
-        <v>11986500</v>
+        <v>11921000</v>
       </c>
       <c r="L634" s="5" t="n">
-        <v>28814</v>
+        <v>28656</v>
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N634" s="3" t="inlineStr">
@@ -41285,25 +41285,25 @@
         </is>
       </c>
       <c r="H635" s="5" t="n">
-        <v>18722000</v>
+        <v>1844500018722000</v>
       </c>
       <c r="I635" s="5" t="n">
-        <v>30742</v>
+        <v>3028735662926</v>
       </c>
       <c r="J635" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K635" s="5" t="n">
-        <v>17130630</v>
+        <v>1704294961048800</v>
       </c>
       <c r="L635" s="5" t="n">
-        <v>28129</v>
+        <v>2798513893348</v>
       </c>
       <c r="M635" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N635" s="3" t="inlineStr">
@@ -41424,18 +41424,18 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K637" s="5" t="n">
-        <v>13430370</v>
+        <v>13633000</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>28394</v>
+        <v>28822</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N637" s="3" t="inlineStr">
@@ -41486,18 +41486,18 @@
       </c>
       <c r="J638" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="K638" s="5" t="n">
-        <v>20397180</v>
+        <v>20610500</v>
       </c>
       <c r="L638" s="5" t="n">
-        <v>30084</v>
+        <v>30399</v>
       </c>
       <c r="M638" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N638" s="3" t="inlineStr">
@@ -41913,25 +41913,25 @@
         </is>
       </c>
       <c r="H645" s="5" t="n">
-        <v>17342000</v>
+        <v>1708600017342000</v>
       </c>
       <c r="I645" s="5" t="n">
-        <v>30748</v>
+        <v>3029432654862</v>
       </c>
       <c r="J645" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K645" s="5" t="n">
-        <v>15867930</v>
+        <v>1578725058523700</v>
       </c>
       <c r="L645" s="5" t="n">
-        <v>28135</v>
+        <v>2799157905184</v>
       </c>
       <c r="M645" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N645" s="3" t="inlineStr">
@@ -41982,18 +41982,18 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K646" s="5" t="n">
-        <v>11872125</v>
+        <v>11807200</v>
       </c>
       <c r="L646" s="5" t="n">
-        <v>28539</v>
+        <v>28383</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N646" s="3" t="inlineStr">
@@ -42037,25 +42037,25 @@
         </is>
       </c>
       <c r="H647" s="5" t="n">
-        <v>18544000</v>
+        <v>1827000018544000</v>
       </c>
       <c r="I647" s="5" t="n">
-        <v>30450</v>
+        <v>3000000030450</v>
       </c>
       <c r="J647" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K647" s="5" t="n">
-        <v>16967760</v>
+        <v>1688125179634300</v>
       </c>
       <c r="L647" s="5" t="n">
-        <v>27862</v>
+        <v>2771962528135</v>
       </c>
       <c r="M647" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N647" s="3" t="inlineStr">
@@ -42681,25 +42681,25 @@
         </is>
       </c>
       <c r="H657" s="5" t="n">
-        <v>17122000</v>
+        <v>1686900017122000</v>
       </c>
       <c r="I657" s="5" t="n">
-        <v>30358</v>
+        <v>2990957477167</v>
       </c>
       <c r="J657" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K657" s="5" t="n">
-        <v>15666630</v>
+        <v>1558674529570400</v>
       </c>
       <c r="L657" s="5" t="n">
-        <v>27778</v>
+        <v>2763607321933</v>
       </c>
       <c r="M657" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N657" s="3" t="inlineStr">
@@ -42750,18 +42750,18 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K658" s="5" t="n">
-        <v>11720235</v>
+        <v>11656100</v>
       </c>
       <c r="L658" s="5" t="n">
-        <v>28174</v>
+        <v>28019</v>
       </c>
       <c r="M658" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N658" s="3" t="inlineStr">
@@ -42805,25 +42805,25 @@
         </is>
       </c>
       <c r="H659" s="5" t="n">
-        <v>18308000</v>
+        <v>1803700018308000</v>
       </c>
       <c r="I659" s="5" t="n">
-        <v>30062</v>
+        <v>2961740588355</v>
       </c>
       <c r="J659" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K659" s="5" t="n">
-        <v>16751820</v>
+        <v>1666596270666300</v>
       </c>
       <c r="L659" s="5" t="n">
-        <v>27507</v>
+        <v>2736611281882</v>
       </c>
       <c r="M659" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N659" s="3" t="inlineStr">
@@ -53137,8 +53137,8 @@
       <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1931万
-$31,711/呎
+$190270001931万
+$3,124,302,166,358/呎
 (在售)</t>
         </is>
       </c>
@@ -53240,8 +53240,8 @@
       <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1919万
-$31,517/呎
+$189100001919万
+$3,105,090,343,504/呎
 (在售)</t>
         </is>
       </c>
@@ -53343,8 +53343,8 @@
       <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1908万
-$31,323/呎
+$187940001908万
+$3,086,042,724,263/呎
 (在售)</t>
         </is>
       </c>
@@ -53359,8 +53359,8 @@
       <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1784万
-$31,624/呎
+$175720001784万
+$3,115,602,868,504/呎
 (在售)</t>
         </is>
       </c>
@@ -53446,8 +53446,8 @@
       <c r="E28" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1908万
-$31,323/呎
+$187940001908万
+$3,086,042,724,263/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53462,8 +53462,8 @@
       <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1784万
-$31,624/呎
+$175720001784万
+$3,115,602,868,504/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53549,8 +53549,8 @@
       <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1896万
-$31,130/呎
+$186780001896万
+$3,066,995,105,021/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53565,8 +53565,8 @@
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1773万
-$31,429/呎
+$174640001773万
+$3,096,453,932,138/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53652,8 +53652,8 @@
       <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1884万
-$30,934/呎
+$185610001884万
+$3,047,783,282,166/呎
 (在售)</t>
         </is>
       </c>
@@ -53668,8 +53668,8 @@
       <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1762万
-$31,234/呎
+$173560001762万
+$3,077,304,995,773/呎
 (在售)</t>
         </is>
       </c>
@@ -53755,8 +53755,8 @@
       <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1872万
-$30,742/呎
+$184450001872万
+$3,028,735,662,926/呎
 (在售)</t>
         </is>
       </c>
@@ -53771,8 +53771,8 @@
       <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1751万
-$31,041/呎
+$172480001751万
+$3,058,156,059,410/呎
 (在售)</t>
         </is>
       </c>
@@ -53858,8 +53858,8 @@
       <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1854万
-$30,450/呎
+$182700001854万
+$3,000,000,030,450/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53874,8 +53874,8 @@
       <c r="G32" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1734万
-$30,748/呎
+$170860001734万
+$3,029,432,654,862/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53961,8 +53961,8 @@
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1831万
-$30,062/呎
+$180370001831万
+$2,961,740,588,355/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53977,8 +53977,8 @@
       <c r="G33" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$1712万
-$30,358/呎
+$168690001712万
+$2,990,957,477,167/呎
 (已定价未售)</t>
         </is>
       </c>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -666,11 +666,11 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
@@ -22318,18 +22318,18 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>13435200</v>
+        <v>13509000</v>
       </c>
       <c r="L334" s="5" t="n">
-        <v>32296</v>
+        <v>32474</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -23086,18 +23086,18 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>13283200</v>
+        <v>13356200</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>31931</v>
+        <v>32106</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23846,18 +23846,18 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>13207700</v>
+        <v>13280300</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>31749</v>
+        <v>31924</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -24606,18 +24606,18 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>13132200</v>
+        <v>13204300</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>31568</v>
+        <v>31741</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25358,18 +25358,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>13056600</v>
+        <v>13128400</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>31386</v>
+        <v>31559</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -26110,18 +26110,18 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>12981100</v>
+        <v>13052400</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>31205</v>
+        <v>31376</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26862,18 +26862,18 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>12905600</v>
+        <v>12976500</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>31023</v>
+        <v>31194</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -27056,18 +27056,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>14762500</v>
+        <v>13997600</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>31210</v>
+        <v>29593</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -27614,18 +27614,18 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K418" s="5" t="n">
-        <v>12829100</v>
+        <v>12899600</v>
       </c>
       <c r="L418" s="5" t="n">
-        <v>30839</v>
+        <v>31009</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
@@ -27808,18 +27808,18 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>14675200</v>
+        <v>13914800</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>31026</v>
+        <v>29418</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -28366,18 +28366,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>12753600</v>
+        <v>12823700</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>30658</v>
+        <v>30826</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -28560,18 +28560,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>14588800</v>
+        <v>13832900</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>30843</v>
+        <v>29245</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -29118,18 +29118,18 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>12678100</v>
+        <v>12747700</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>30476</v>
+        <v>30644</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N442" s="3" t="inlineStr">
@@ -29886,18 +29886,18 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12639900</v>
+        <v>12709300</v>
       </c>
       <c r="L454" s="5" t="n">
-        <v>30384</v>
+        <v>30551</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -30654,18 +30654,18 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K466" s="5" t="n">
-        <v>12602500</v>
+        <v>12671800</v>
       </c>
       <c r="L466" s="5" t="n">
-        <v>30294</v>
+        <v>30461</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N466" s="3" t="inlineStr">
@@ -31422,18 +31422,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>12564300</v>
+        <v>12633400</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>30203</v>
+        <v>30369</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -32190,18 +32190,18 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>12527000</v>
+        <v>12595800</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>30113</v>
+        <v>30278</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32958,18 +32958,18 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>12527000</v>
+        <v>12595800</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>30113</v>
+        <v>30278</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N502" s="3" t="inlineStr">
@@ -33152,18 +33152,18 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>14886000</v>
+        <v>14114700</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>31471</v>
+        <v>29841</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -33710,18 +33710,18 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K514" s="5" t="n">
-        <v>12488800</v>
+        <v>12557400</v>
       </c>
       <c r="L514" s="5" t="n">
-        <v>30021</v>
+        <v>30186</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -33904,18 +33904,18 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K517" s="5" t="n">
-        <v>14284100</v>
+        <v>13544000</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>30199</v>
+        <v>28634</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N517" s="3" t="inlineStr">
@@ -34656,18 +34656,18 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>14241400</v>
+        <v>13503400</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>30109</v>
+        <v>28548</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N529" s="3" t="inlineStr">
@@ -35214,18 +35214,18 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>12413300</v>
+        <v>12481500</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>29840</v>
+        <v>30004</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N538" s="3" t="inlineStr">
@@ -35408,18 +35408,18 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>14197700</v>
+        <v>13462100</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>30016</v>
+        <v>28461</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N541" s="3" t="inlineStr">
@@ -35470,18 +35470,18 @@
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.26%</t>
         </is>
       </c>
       <c r="K542" s="5" t="n">
-        <v>21438300</v>
+        <v>20356800</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>31620</v>
+        <v>30025</v>
       </c>
       <c r="M542" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N542" s="3" t="inlineStr">
@@ -35966,18 +35966,18 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>12375000</v>
+        <v>12443000</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>29748</v>
+        <v>29911</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N550" s="3" t="inlineStr">
@@ -36160,18 +36160,18 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>14154100</v>
+        <v>13420700</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>29924</v>
+        <v>28374</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N553" s="3" t="inlineStr">
@@ -36222,18 +36222,18 @@
       </c>
       <c r="J554" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.25%</t>
         </is>
       </c>
       <c r="K554" s="5" t="n">
-        <v>21373600</v>
+        <v>20299100</v>
       </c>
       <c r="L554" s="5" t="n">
-        <v>31524</v>
+        <v>29940</v>
       </c>
       <c r="M554" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N554" s="3" t="inlineStr">
@@ -36718,18 +36718,18 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>12299500</v>
+        <v>12367100</v>
       </c>
       <c r="L562" s="5" t="n">
-        <v>29566</v>
+        <v>29729</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N562" s="3" t="inlineStr">
@@ -36773,25 +36773,25 @@
         </is>
       </c>
       <c r="H563" s="5" t="n">
-        <v>1902700019312000</v>
+        <v>19312000</v>
       </c>
       <c r="I563" s="5" t="n">
-        <v>3124302166358</v>
+        <v>31711</v>
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K563" s="5" t="n">
-        <v>1758071034093900</v>
+        <v>17007700</v>
       </c>
       <c r="L563" s="5" t="n">
-        <v>2886816147937</v>
+        <v>27927</v>
       </c>
       <c r="M563" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N563" s="3" t="inlineStr">
@@ -36912,18 +36912,18 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K565" s="5" t="n">
-        <v>14066800</v>
+        <v>13337900</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>29740</v>
+        <v>28199</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N565" s="3" t="inlineStr">
@@ -36974,18 +36974,18 @@
       </c>
       <c r="J566" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.21%</t>
         </is>
       </c>
       <c r="K566" s="5" t="n">
-        <v>21244200</v>
+        <v>20183800</v>
       </c>
       <c r="L566" s="5" t="n">
-        <v>31334</v>
+        <v>29770</v>
       </c>
       <c r="M566" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N566" s="3" t="inlineStr">
@@ -37470,18 +37470,18 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K574" s="5" t="n">
-        <v>12224000</v>
+        <v>12291100</v>
       </c>
       <c r="L574" s="5" t="n">
-        <v>29385</v>
+        <v>29546</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N574" s="3" t="inlineStr">
@@ -37525,25 +37525,25 @@
         </is>
       </c>
       <c r="H575" s="5" t="n">
-        <v>1891000019194000</v>
+        <v>19194000</v>
       </c>
       <c r="I575" s="5" t="n">
-        <v>3105090343504</v>
+        <v>31517</v>
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K575" s="5" t="n">
-        <v>1747260380235000</v>
+        <v>16903900</v>
       </c>
       <c r="L575" s="5" t="n">
-        <v>2869064663768</v>
+        <v>27757</v>
       </c>
       <c r="M575" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N575" s="3" t="inlineStr">
@@ -37664,18 +37664,18 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>13980400</v>
+        <v>13256000</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>29557</v>
+        <v>28025</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -37726,18 +37726,18 @@
       </c>
       <c r="J578" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.18%</t>
         </is>
       </c>
       <c r="K578" s="5" t="n">
-        <v>21114800</v>
+        <v>20068500</v>
       </c>
       <c r="L578" s="5" t="n">
-        <v>31143</v>
+        <v>29600</v>
       </c>
       <c r="M578" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N578" s="3" t="inlineStr">
@@ -38153,25 +38153,25 @@
         </is>
       </c>
       <c r="H585" s="5" t="n">
-        <v>1757200017836000</v>
+        <v>17836000</v>
       </c>
       <c r="I585" s="5" t="n">
-        <v>3115602868504</v>
+        <v>31624</v>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K585" s="5" t="n">
-        <v>1623630851480200</v>
+        <v>15707900</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>2878778105461</v>
+        <v>27851</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N585" s="3" t="inlineStr">
@@ -38222,18 +38222,18 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>12148500</v>
+        <v>12215200</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>29203</v>
+        <v>29363</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N586" s="3" t="inlineStr">
@@ -38277,25 +38277,25 @@
         </is>
       </c>
       <c r="H587" s="5" t="n">
-        <v>1879400019076000</v>
+        <v>19076000</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>3086042724263</v>
+        <v>31323</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>1736542125125900</v>
+        <v>16799900</v>
       </c>
       <c r="L587" s="5" t="n">
-        <v>2851464901685</v>
+        <v>27586</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N587" s="3" t="inlineStr">
@@ -38416,18 +38416,18 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>13893100</v>
+        <v>13173200</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>29372</v>
+        <v>27850</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N589" s="3" t="inlineStr">
@@ -38478,18 +38478,18 @@
       </c>
       <c r="J590" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.15%</t>
         </is>
       </c>
       <c r="K590" s="5" t="n">
-        <v>20985500</v>
+        <v>19953200</v>
       </c>
       <c r="L590" s="5" t="n">
-        <v>30952</v>
+        <v>29429</v>
       </c>
       <c r="M590" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N590" s="3" t="inlineStr">
@@ -38905,25 +38905,25 @@
         </is>
       </c>
       <c r="H597" s="5" t="n">
-        <v>1757200017836000</v>
+        <v>17836000</v>
       </c>
       <c r="I597" s="5" t="n">
-        <v>3115602868504</v>
+        <v>31624</v>
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K597" s="5" t="n">
-        <v>1623630851480200</v>
+        <v>15707900</v>
       </c>
       <c r="L597" s="5" t="n">
-        <v>2878778105461</v>
+        <v>27851</v>
       </c>
       <c r="M597" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N597" s="3" t="inlineStr">
@@ -38974,18 +38974,18 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K598" s="5" t="n">
-        <v>12148500</v>
+        <v>12215200</v>
       </c>
       <c r="L598" s="5" t="n">
-        <v>29203</v>
+        <v>29363</v>
       </c>
       <c r="M598" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N598" s="3" t="inlineStr">
@@ -39029,25 +39029,25 @@
         </is>
       </c>
       <c r="H599" s="5" t="n">
-        <v>1879400019076000</v>
+        <v>19076000</v>
       </c>
       <c r="I599" s="5" t="n">
-        <v>3086042724263</v>
+        <v>31323</v>
       </c>
       <c r="J599" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K599" s="5" t="n">
-        <v>1736542125125900</v>
+        <v>16799900</v>
       </c>
       <c r="L599" s="5" t="n">
-        <v>2851464901685</v>
+        <v>27586</v>
       </c>
       <c r="M599" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N599" s="3" t="inlineStr">
@@ -39168,18 +39168,18 @@
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K601" s="5" t="n">
-        <v>13893100</v>
+        <v>13173200</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>29372</v>
+        <v>27850</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N601" s="3" t="inlineStr">
@@ -39230,18 +39230,18 @@
       </c>
       <c r="J602" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.15%</t>
         </is>
       </c>
       <c r="K602" s="5" t="n">
-        <v>20985500</v>
+        <v>19953200</v>
       </c>
       <c r="L602" s="5" t="n">
-        <v>30952</v>
+        <v>29429</v>
       </c>
       <c r="M602" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N602" s="3" t="inlineStr">
@@ -39657,25 +39657,25 @@
         </is>
       </c>
       <c r="H609" s="5" t="n">
-        <v>1746400017726000</v>
+        <v>17726000</v>
       </c>
       <c r="I609" s="5" t="n">
-        <v>3096453932138</v>
+        <v>31429</v>
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K609" s="5" t="n">
-        <v>1613651786378500</v>
+        <v>15610900</v>
       </c>
       <c r="L609" s="5" t="n">
-        <v>2861084727621</v>
+        <v>27679</v>
       </c>
       <c r="M609" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N609" s="3" t="inlineStr">
@@ -39726,18 +39726,18 @@
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K610" s="5" t="n">
-        <v>12072900</v>
+        <v>12139300</v>
       </c>
       <c r="L610" s="5" t="n">
-        <v>29021</v>
+        <v>29181</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N610" s="3" t="inlineStr">
@@ -39781,25 +39781,25 @@
         </is>
       </c>
       <c r="H611" s="5" t="n">
-        <v>1867800018958000</v>
+        <v>18958000</v>
       </c>
       <c r="I611" s="5" t="n">
-        <v>3066995105021</v>
+        <v>31130</v>
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K611" s="5" t="n">
-        <v>1725823870016800</v>
+        <v>16696000</v>
       </c>
       <c r="L611" s="5" t="n">
-        <v>2833865139601</v>
+        <v>27415</v>
       </c>
       <c r="M611" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N611" s="3" t="inlineStr">
@@ -39920,18 +39920,18 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K613" s="5" t="n">
-        <v>13806700</v>
+        <v>13091300</v>
       </c>
       <c r="L613" s="5" t="n">
-        <v>29190</v>
+        <v>27677</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N613" s="3" t="inlineStr">
@@ -39982,18 +39982,18 @@
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>12.11%</t>
         </is>
       </c>
       <c r="K614" s="5" t="n">
-        <v>20856100</v>
+        <v>19837900</v>
       </c>
       <c r="L614" s="5" t="n">
-        <v>30761</v>
+        <v>29259</v>
       </c>
       <c r="M614" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N614" s="3" t="inlineStr">
@@ -40409,25 +40409,25 @@
         </is>
       </c>
       <c r="H621" s="5" t="n">
-        <v>1735600017616000</v>
+        <v>17616000</v>
       </c>
       <c r="I621" s="5" t="n">
-        <v>3077304995773</v>
+        <v>31234</v>
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K621" s="5" t="n">
-        <v>1603672721276900</v>
+        <v>15514100</v>
       </c>
       <c r="L621" s="5" t="n">
-        <v>2843391349782</v>
+        <v>27507</v>
       </c>
       <c r="M621" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N621" s="3" t="inlineStr">
@@ -40478,18 +40478,18 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K622" s="5" t="n">
-        <v>11996500</v>
+        <v>12062400</v>
       </c>
       <c r="L622" s="5" t="n">
-        <v>28838</v>
+        <v>28996</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N622" s="3" t="inlineStr">
@@ -40533,25 +40533,25 @@
         </is>
       </c>
       <c r="H623" s="5" t="n">
-        <v>1856100018839000</v>
+        <v>18839000</v>
       </c>
       <c r="I623" s="5" t="n">
-        <v>3047783282166</v>
+        <v>30934</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K623" s="5" t="n">
-        <v>1715013216156900</v>
+        <v>16591100</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>2816113655430</v>
+        <v>27243</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N623" s="3" t="inlineStr">
@@ -40672,18 +40672,18 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K625" s="5" t="n">
-        <v>13719400</v>
+        <v>13008500</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>29005</v>
+        <v>27502</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N625" s="3" t="inlineStr">
@@ -40734,18 +40734,18 @@
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>7.58%</t>
+          <t>12.08%</t>
         </is>
       </c>
       <c r="K626" s="5" t="n">
-        <v>20732100</v>
+        <v>19722600</v>
       </c>
       <c r="L626" s="5" t="n">
-        <v>30578</v>
+        <v>29089</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N626" s="3" t="inlineStr">
@@ -41161,25 +41161,25 @@
         </is>
       </c>
       <c r="H633" s="5" t="n">
-        <v>1724800017507000</v>
+        <v>17507000</v>
       </c>
       <c r="I633" s="5" t="n">
-        <v>3058156059410</v>
+        <v>31041</v>
       </c>
       <c r="J633" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K633" s="5" t="n">
-        <v>1593693656176100</v>
+        <v>15418100</v>
       </c>
       <c r="L633" s="5" t="n">
-        <v>2825697971943</v>
+        <v>27337</v>
       </c>
       <c r="M633" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N633" s="3" t="inlineStr">
@@ -41230,18 +41230,18 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K634" s="5" t="n">
-        <v>11921000</v>
+        <v>11986500</v>
       </c>
       <c r="L634" s="5" t="n">
-        <v>28656</v>
+        <v>28814</v>
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N634" s="3" t="inlineStr">
@@ -41285,25 +41285,25 @@
         </is>
       </c>
       <c r="H635" s="5" t="n">
-        <v>1844500018722000</v>
+        <v>18722000</v>
       </c>
       <c r="I635" s="5" t="n">
-        <v>3028735662926</v>
+        <v>30742</v>
       </c>
       <c r="J635" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K635" s="5" t="n">
-        <v>1704294961048800</v>
+        <v>16488200</v>
       </c>
       <c r="L635" s="5" t="n">
-        <v>2798513893348</v>
+        <v>27074</v>
       </c>
       <c r="M635" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N635" s="3" t="inlineStr">
@@ -41424,18 +41424,18 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K637" s="5" t="n">
-        <v>13633000</v>
+        <v>12926600</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>28822</v>
+        <v>27329</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N637" s="3" t="inlineStr">
@@ -41486,18 +41486,18 @@
       </c>
       <c r="J638" s="3" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>12.04%</t>
         </is>
       </c>
       <c r="K638" s="5" t="n">
-        <v>20610500</v>
+        <v>19607300</v>
       </c>
       <c r="L638" s="5" t="n">
-        <v>30399</v>
+        <v>28919</v>
       </c>
       <c r="M638" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N638" s="3" t="inlineStr">
@@ -41913,25 +41913,25 @@
         </is>
       </c>
       <c r="H645" s="5" t="n">
-        <v>1708600017342000</v>
+        <v>17342000</v>
       </c>
       <c r="I645" s="5" t="n">
-        <v>3029432654862</v>
+        <v>30748</v>
       </c>
       <c r="J645" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K645" s="5" t="n">
-        <v>1578725058523700</v>
+        <v>15272800</v>
       </c>
       <c r="L645" s="5" t="n">
-        <v>2799157905184</v>
+        <v>27079</v>
       </c>
       <c r="M645" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N645" s="3" t="inlineStr">
@@ -41982,18 +41982,18 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K646" s="5" t="n">
-        <v>11807200</v>
+        <v>11872100</v>
       </c>
       <c r="L646" s="5" t="n">
-        <v>28383</v>
+        <v>28539</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N646" s="3" t="inlineStr">
@@ -42037,25 +42037,25 @@
         </is>
       </c>
       <c r="H647" s="5" t="n">
-        <v>1827000018544000</v>
+        <v>18544000</v>
       </c>
       <c r="I647" s="5" t="n">
-        <v>3000000030450</v>
+        <v>30450</v>
       </c>
       <c r="J647" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K647" s="5" t="n">
-        <v>1688125179634300</v>
+        <v>16331400</v>
       </c>
       <c r="L647" s="5" t="n">
-        <v>2771962528135</v>
+        <v>26817</v>
       </c>
       <c r="M647" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N647" s="3" t="inlineStr">
@@ -42681,25 +42681,25 @@
         </is>
       </c>
       <c r="H657" s="5" t="n">
-        <v>1686900017122000</v>
+        <v>17122000</v>
       </c>
       <c r="I657" s="5" t="n">
-        <v>2990957477167</v>
+        <v>30358</v>
       </c>
       <c r="J657" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K657" s="5" t="n">
-        <v>1558674529570400</v>
+        <v>15079100</v>
       </c>
       <c r="L657" s="5" t="n">
-        <v>2763607321933</v>
+        <v>26736</v>
       </c>
       <c r="M657" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N657" s="3" t="inlineStr">
@@ -42750,18 +42750,18 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K658" s="5" t="n">
-        <v>11656100</v>
+        <v>11720200</v>
       </c>
       <c r="L658" s="5" t="n">
-        <v>28019</v>
+        <v>28174</v>
       </c>
       <c r="M658" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N658" s="3" t="inlineStr">
@@ -42805,25 +42805,25 @@
         </is>
       </c>
       <c r="H659" s="5" t="n">
-        <v>1803700018308000</v>
+        <v>18308000</v>
       </c>
       <c r="I659" s="5" t="n">
-        <v>2961740588355</v>
+        <v>30062</v>
       </c>
       <c r="J659" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K659" s="5" t="n">
-        <v>1666596270666300</v>
+        <v>16123600</v>
       </c>
       <c r="L659" s="5" t="n">
-        <v>2736611281882</v>
+        <v>26476</v>
       </c>
       <c r="M659" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N659" s="3" t="inlineStr">
@@ -53137,8 +53137,8 @@
       <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$190270001931万
-$3,124,302,166,358/呎
+$1931万
+$31,711/呎
 (在售)</t>
         </is>
       </c>
@@ -53240,8 +53240,8 @@
       <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$189100001919万
-$3,105,090,343,504/呎
+$1919万
+$31,517/呎
 (在售)</t>
         </is>
       </c>
@@ -53343,8 +53343,8 @@
       <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$187940001908万
-$3,086,042,724,263/呎
+$1908万
+$31,323/呎
 (在售)</t>
         </is>
       </c>
@@ -53359,8 +53359,8 @@
       <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$175720001784万
-$3,115,602,868,504/呎
+$1784万
+$31,624/呎
 (在售)</t>
         </is>
       </c>
@@ -53446,8 +53446,8 @@
       <c r="E28" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$187940001908万
-$3,086,042,724,263/呎
+$1908万
+$31,323/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53462,8 +53462,8 @@
       <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$175720001784万
-$3,115,602,868,504/呎
+$1784万
+$31,624/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53549,8 +53549,8 @@
       <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$186780001896万
-$3,066,995,105,021/呎
+$1896万
+$31,130/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53565,8 +53565,8 @@
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$174640001773万
-$3,096,453,932,138/呎
+$1773万
+$31,429/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53652,8 +53652,8 @@
       <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$185610001884万
-$3,047,783,282,166/呎
+$1884万
+$30,934/呎
 (在售)</t>
         </is>
       </c>
@@ -53668,8 +53668,8 @@
       <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$173560001762万
-$3,077,304,995,773/呎
+$1762万
+$31,234/呎
 (在售)</t>
         </is>
       </c>
@@ -53755,8 +53755,8 @@
       <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$184450001872万
-$3,028,735,662,926/呎
+$1872万
+$30,742/呎
 (在售)</t>
         </is>
       </c>
@@ -53771,8 +53771,8 @@
       <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$172480001751万
-$3,058,156,059,410/呎
+$1751万
+$31,041/呎
 (在售)</t>
         </is>
       </c>
@@ -53858,8 +53858,8 @@
       <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$182700001854万
-$3,000,000,030,450/呎
+$1854万
+$30,450/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53874,8 +53874,8 @@
       <c r="G32" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$170860001734万
-$3,029,432,654,862/呎
+$1734万
+$30,748/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53961,8 +53961,8 @@
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$180370001831万
-$2,961,740,588,355/呎
+$1831万
+$30,062/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -53977,8 +53977,8 @@
       <c r="G33" s="24" t="inlineStr">
         <is>
           <t>F | 564呎 (2房)
-$168690001712万
-$2,990,957,477,167/呎
+$1712万
+$30,358/呎
 (已定价未售)</t>
         </is>
       </c>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -22318,18 +22318,18 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>13509000</v>
+        <v>13509060</v>
       </c>
       <c r="L334" s="5" t="n">
         <v>32474</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -23086,18 +23086,18 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>13356200</v>
+        <v>13356255</v>
       </c>
       <c r="L346" s="5" t="n">
         <v>32106</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23846,18 +23846,18 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>13280300</v>
+        <v>13280310</v>
       </c>
       <c r="L358" s="5" t="n">
         <v>31924</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -24606,18 +24606,18 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>13204300</v>
+        <v>13204365</v>
       </c>
       <c r="L370" s="5" t="n">
         <v>31741</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25358,18 +25358,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>13128400</v>
+        <v>13128420</v>
       </c>
       <c r="L382" s="5" t="n">
         <v>31559</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -26110,18 +26110,18 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>13052400</v>
+        <v>13052475</v>
       </c>
       <c r="L394" s="5" t="n">
         <v>31376</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26862,18 +26862,18 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>12976500</v>
+        <v>12976530</v>
       </c>
       <c r="L406" s="5" t="n">
         <v>31194</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -27056,18 +27056,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>13997600</v>
+        <v>14543010</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>29593</v>
+        <v>30746</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -27614,18 +27614,18 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K418" s="5" t="n">
-        <v>12899600</v>
+        <v>12899670</v>
       </c>
       <c r="L418" s="5" t="n">
         <v>31009</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
@@ -27808,18 +27808,18 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>13914800</v>
+        <v>14457000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>29418</v>
+        <v>30564</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -28366,18 +28366,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>12823700</v>
+        <v>12823725</v>
       </c>
       <c r="L430" s="5" t="n">
         <v>30826</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -28560,18 +28560,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>13832900</v>
+        <v>14371905</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>29245</v>
+        <v>30385</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -29118,18 +29118,18 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>12747700</v>
+        <v>12747780</v>
       </c>
       <c r="L442" s="5" t="n">
         <v>30644</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N442" s="3" t="inlineStr">
@@ -29886,18 +29886,18 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12709300</v>
+        <v>12709350</v>
       </c>
       <c r="L454" s="5" t="n">
         <v>30551</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -30654,18 +30654,18 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K466" s="5" t="n">
-        <v>12671800</v>
+        <v>12671835</v>
       </c>
       <c r="L466" s="5" t="n">
         <v>30461</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N466" s="3" t="inlineStr">
@@ -31422,18 +31422,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>12633400</v>
+        <v>12633405</v>
       </c>
       <c r="L478" s="5" t="n">
         <v>30369</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -32190,18 +32190,18 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>12595800</v>
+        <v>12595890</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>30278</v>
+        <v>30279</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32958,18 +32958,18 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>12595800</v>
+        <v>12595890</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>30278</v>
+        <v>30279</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N502" s="3" t="inlineStr">
@@ -33152,18 +33152,18 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>14114700</v>
+        <v>14114790</v>
       </c>
       <c r="L505" s="5" t="n">
         <v>29841</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -33710,18 +33710,18 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K514" s="5" t="n">
-        <v>12557400</v>
+        <v>12557460</v>
       </c>
       <c r="L514" s="5" t="n">
         <v>30186</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -33904,18 +33904,18 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K517" s="5" t="n">
-        <v>13544000</v>
+        <v>14071785</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>28634</v>
+        <v>29750</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N517" s="3" t="inlineStr">
@@ -34656,18 +34656,18 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>13503400</v>
+        <v>14029695</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>28548</v>
+        <v>29661</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N529" s="3" t="inlineStr">
@@ -35214,18 +35214,18 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>12481500</v>
+        <v>12481515</v>
       </c>
       <c r="L538" s="5" t="n">
         <v>30004</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N538" s="3" t="inlineStr">
@@ -35408,18 +35408,18 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>13462100</v>
+        <v>13986690</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>28461</v>
+        <v>29570</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N541" s="3" t="inlineStr">
@@ -35966,18 +35966,18 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>12443000</v>
+        <v>12443085</v>
       </c>
       <c r="L550" s="5" t="n">
         <v>29911</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N550" s="3" t="inlineStr">
@@ -36160,18 +36160,18 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>13420700</v>
+        <v>13943685</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>28374</v>
+        <v>29479</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N553" s="3" t="inlineStr">
@@ -36718,18 +36718,18 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>12367100</v>
+        <v>12367140</v>
       </c>
       <c r="L562" s="5" t="n">
         <v>29729</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N562" s="3" t="inlineStr">
@@ -36912,18 +36912,18 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K565" s="5" t="n">
-        <v>13337900</v>
+        <v>13857675</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>28199</v>
+        <v>29297</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N565" s="3" t="inlineStr">
@@ -37470,18 +37470,18 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K574" s="5" t="n">
-        <v>12291100</v>
+        <v>12291195</v>
       </c>
       <c r="L574" s="5" t="n">
         <v>29546</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N574" s="3" t="inlineStr">
@@ -37664,18 +37664,18 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>13256000</v>
+        <v>13772580</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>28025</v>
+        <v>29118</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -38222,18 +38222,18 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>12215200</v>
+        <v>12215250</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>29363</v>
+        <v>29364</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N586" s="3" t="inlineStr">
@@ -38416,18 +38416,18 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>13173200</v>
+        <v>13686570</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>27850</v>
+        <v>28936</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N589" s="3" t="inlineStr">
@@ -38974,18 +38974,18 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K598" s="5" t="n">
-        <v>12215200</v>
+        <v>12215250</v>
       </c>
       <c r="L598" s="5" t="n">
-        <v>29363</v>
+        <v>29364</v>
       </c>
       <c r="M598" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N598" s="3" t="inlineStr">
@@ -39168,18 +39168,18 @@
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K601" s="5" t="n">
-        <v>13173200</v>
+        <v>13686570</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>27850</v>
+        <v>28936</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N601" s="3" t="inlineStr">
@@ -39726,18 +39726,18 @@
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K610" s="5" t="n">
-        <v>12139300</v>
+        <v>12139305</v>
       </c>
       <c r="L610" s="5" t="n">
         <v>29181</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N610" s="3" t="inlineStr">
@@ -39920,18 +39920,18 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K613" s="5" t="n">
-        <v>13091300</v>
+        <v>13601475</v>
       </c>
       <c r="L613" s="5" t="n">
-        <v>27677</v>
+        <v>28756</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N613" s="3" t="inlineStr">
@@ -40478,18 +40478,18 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K622" s="5" t="n">
-        <v>12062400</v>
+        <v>12062445</v>
       </c>
       <c r="L622" s="5" t="n">
         <v>28996</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N622" s="3" t="inlineStr">
@@ -40672,18 +40672,18 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K625" s="5" t="n">
-        <v>13008500</v>
+        <v>13515465</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>27502</v>
+        <v>28574</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N625" s="3" t="inlineStr">
@@ -41230,7 +41230,7 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K634" s="5" t="n">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N634" s="3" t="inlineStr">
@@ -41424,18 +41424,18 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K637" s="5" t="n">
-        <v>12926600</v>
+        <v>13430370</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>27329</v>
+        <v>28394</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N637" s="3" t="inlineStr">
@@ -41982,18 +41982,18 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K646" s="5" t="n">
-        <v>11872100</v>
+        <v>11872125</v>
       </c>
       <c r="L646" s="5" t="n">
         <v>28539</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N646" s="3" t="inlineStr">
@@ -42750,18 +42750,18 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K658" s="5" t="n">
-        <v>11720200</v>
+        <v>11720235</v>
       </c>
       <c r="L658" s="5" t="n">
         <v>28174</v>
       </c>
       <c r="M658" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N658" s="3" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -22318,18 +22318,18 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>13509060</v>
+        <v>13509000</v>
       </c>
       <c r="L334" s="5" t="n">
         <v>32474</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -23086,18 +23086,18 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>13356255</v>
+        <v>13356200</v>
       </c>
       <c r="L346" s="5" t="n">
         <v>32106</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23846,18 +23846,18 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>13280310</v>
+        <v>13280300</v>
       </c>
       <c r="L358" s="5" t="n">
         <v>31924</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -24606,18 +24606,18 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>13204365</v>
+        <v>13204300</v>
       </c>
       <c r="L370" s="5" t="n">
         <v>31741</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25358,18 +25358,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>13128420</v>
+        <v>13128400</v>
       </c>
       <c r="L382" s="5" t="n">
         <v>31559</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -26110,18 +26110,18 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>13052475</v>
+        <v>13052400</v>
       </c>
       <c r="L394" s="5" t="n">
         <v>31376</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26862,18 +26862,18 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>12976530</v>
+        <v>12976500</v>
       </c>
       <c r="L406" s="5" t="n">
         <v>31194</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -27056,18 +27056,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>14543010</v>
+        <v>13997600</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>30746</v>
+        <v>29593</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -27614,18 +27614,18 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K418" s="5" t="n">
-        <v>12899670</v>
+        <v>12899600</v>
       </c>
       <c r="L418" s="5" t="n">
         <v>31009</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
@@ -27808,18 +27808,18 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>14457000</v>
+        <v>13914800</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>30564</v>
+        <v>29418</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -28366,18 +28366,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>12823725</v>
+        <v>12823700</v>
       </c>
       <c r="L430" s="5" t="n">
         <v>30826</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -28560,18 +28560,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>14371905</v>
+        <v>13832900</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>30385</v>
+        <v>29245</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -29118,18 +29118,18 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>12747780</v>
+        <v>12747700</v>
       </c>
       <c r="L442" s="5" t="n">
         <v>30644</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N442" s="3" t="inlineStr">
@@ -29886,18 +29886,18 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12709350</v>
+        <v>12709300</v>
       </c>
       <c r="L454" s="5" t="n">
         <v>30551</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -30654,18 +30654,18 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K466" s="5" t="n">
-        <v>12671835</v>
+        <v>12671800</v>
       </c>
       <c r="L466" s="5" t="n">
         <v>30461</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N466" s="3" t="inlineStr">
@@ -31422,18 +31422,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>12633405</v>
+        <v>12633400</v>
       </c>
       <c r="L478" s="5" t="n">
         <v>30369</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -32190,18 +32190,18 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>12595890</v>
+        <v>12595800</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>30279</v>
+        <v>30278</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32958,18 +32958,18 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>12595890</v>
+        <v>12595800</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>30279</v>
+        <v>30278</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N502" s="3" t="inlineStr">
@@ -33152,18 +33152,18 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>14114790</v>
+        <v>14114700</v>
       </c>
       <c r="L505" s="5" t="n">
         <v>29841</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -33710,18 +33710,18 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K514" s="5" t="n">
-        <v>12557460</v>
+        <v>12557400</v>
       </c>
       <c r="L514" s="5" t="n">
         <v>30186</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -33904,18 +33904,18 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K517" s="5" t="n">
-        <v>14071785</v>
+        <v>13544000</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>29750</v>
+        <v>28634</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N517" s="3" t="inlineStr">
@@ -34656,18 +34656,18 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>14029695</v>
+        <v>13503400</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>29661</v>
+        <v>28548</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N529" s="3" t="inlineStr">
@@ -35214,18 +35214,18 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>12481515</v>
+        <v>12481500</v>
       </c>
       <c r="L538" s="5" t="n">
         <v>30004</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N538" s="3" t="inlineStr">
@@ -35408,18 +35408,18 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>13986690</v>
+        <v>13462100</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>29570</v>
+        <v>28461</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N541" s="3" t="inlineStr">
@@ -35966,18 +35966,18 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>12443085</v>
+        <v>12443000</v>
       </c>
       <c r="L550" s="5" t="n">
         <v>29911</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N550" s="3" t="inlineStr">
@@ -36160,18 +36160,18 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>13943685</v>
+        <v>13420700</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>29479</v>
+        <v>28374</v>
       </c>
       <c r="M553" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N553" s="3" t="inlineStr">
@@ -36718,18 +36718,18 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>12367140</v>
+        <v>12367100</v>
       </c>
       <c r="L562" s="5" t="n">
         <v>29729</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N562" s="3" t="inlineStr">
@@ -36912,18 +36912,18 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K565" s="5" t="n">
-        <v>13857675</v>
+        <v>13337900</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>29297</v>
+        <v>28199</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N565" s="3" t="inlineStr">
@@ -37470,18 +37470,18 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K574" s="5" t="n">
-        <v>12291195</v>
+        <v>12291100</v>
       </c>
       <c r="L574" s="5" t="n">
         <v>29546</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N574" s="3" t="inlineStr">
@@ -37664,18 +37664,18 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>13772580</v>
+        <v>13256000</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>29118</v>
+        <v>28025</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -38222,18 +38222,18 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>12215250</v>
+        <v>12215200</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>29364</v>
+        <v>29363</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N586" s="3" t="inlineStr">
@@ -38416,18 +38416,18 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>13686570</v>
+        <v>13173200</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>28936</v>
+        <v>27850</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N589" s="3" t="inlineStr">
@@ -38974,18 +38974,18 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K598" s="5" t="n">
-        <v>12215250</v>
+        <v>12215200</v>
       </c>
       <c r="L598" s="5" t="n">
-        <v>29364</v>
+        <v>29363</v>
       </c>
       <c r="M598" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N598" s="3" t="inlineStr">
@@ -39168,18 +39168,18 @@
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K601" s="5" t="n">
-        <v>13686570</v>
+        <v>13173200</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>28936</v>
+        <v>27850</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N601" s="3" t="inlineStr">
@@ -39726,18 +39726,18 @@
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K610" s="5" t="n">
-        <v>12139305</v>
+        <v>12139300</v>
       </c>
       <c r="L610" s="5" t="n">
         <v>29181</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N610" s="3" t="inlineStr">
@@ -39920,18 +39920,18 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K613" s="5" t="n">
-        <v>13601475</v>
+        <v>13091300</v>
       </c>
       <c r="L613" s="5" t="n">
-        <v>28756</v>
+        <v>27677</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N613" s="3" t="inlineStr">
@@ -40478,18 +40478,18 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K622" s="5" t="n">
-        <v>12062445</v>
+        <v>12062400</v>
       </c>
       <c r="L622" s="5" t="n">
         <v>28996</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N622" s="3" t="inlineStr">
@@ -40672,18 +40672,18 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K625" s="5" t="n">
-        <v>13515465</v>
+        <v>13008500</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>28574</v>
+        <v>27502</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N625" s="3" t="inlineStr">
@@ -41230,7 +41230,7 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="K634" s="5" t="n">
@@ -41424,18 +41424,18 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11.93%</t>
         </is>
       </c>
       <c r="K637" s="5" t="n">
-        <v>13430370</v>
+        <v>12926600</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>28394</v>
+        <v>27329</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N637" s="3" t="inlineStr">
@@ -41982,18 +41982,18 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K646" s="5" t="n">
-        <v>11872125</v>
+        <v>11872100</v>
       </c>
       <c r="L646" s="5" t="n">
         <v>28539</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N646" s="3" t="inlineStr">
@@ -42750,18 +42750,18 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K658" s="5" t="n">
-        <v>11720235</v>
+        <v>11720200</v>
       </c>
       <c r="L658" s="5" t="n">
         <v>28174</v>
       </c>
       <c r="M658" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減8.5%)</t>
         </is>
       </c>
       <c r="N658" s="3" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -9919,14 +9919,14 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>8179200</v>
+        <v>8315500</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>20865</v>
+        <v>21213</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>8179200</v>
+        <v>8315500</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>20865</v>
+        <v>21213</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>31838000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>33979</v>
+        <v>34015</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>31838000</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>33979</v>
+        <v>34015</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12589,14 +12589,14 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
         <v>31764300</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>33900</v>
+        <v>33936</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>31764300</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>33900</v>
+        <v>33936</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -13303,14 +13303,14 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
         <v>31670600</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>33800</v>
+        <v>33836</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>31670600</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>33800</v>
+        <v>33836</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14017,14 +14017,14 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
         <v>31576900</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>33700</v>
+        <v>33736</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>31576900</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>33700</v>
+        <v>33736</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -49447,9 +49447,9 @@
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 392呎 (1房)
-$818万
-$20,865/呎
-(23年-06月-30日)</t>
+$832万
+$21,213/呎
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -49572,9 +49572,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3184万
-$33,979/呎
+$34,015/呎
 (26年-07月-06日)</t>
         </is>
       </c>
@@ -49667,10 +49667,10 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3176万
-$33,900/呎
-(26年-06月-11日)</t>
+$33,936/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -49762,10 +49762,10 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3167万
-$33,800/呎
-(26年-06月-11日)</t>
+$33,836/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -49857,10 +49857,10 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3158万
-$33,700/呎
-(26年-06月-11日)</t>
+$33,736/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -51261,7 +51261,7 @@
           <t>A | 678呎 (2房)
 $2271万
 $33,500/呎
-(26年-06月-23日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -44242,7 +44242,7 @@
         </is>
       </c>
       <c r="E682" s="4" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F682" s="3" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>17215200</v>
       </c>
       <c r="I682" s="5" t="n">
-        <v>27456</v>
+        <v>27500</v>
       </c>
       <c r="J682" s="3" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>17215200</v>
       </c>
       <c r="L682" s="5" t="n">
-        <v>27456</v>
+        <v>27500</v>
       </c>
       <c r="M682" s="3" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
           <t>C | 384呎 (1房)
 $858万
 $22,341/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -48202,7 +48202,7 @@
           <t>D | 384呎 (1房)
 $858万
 $22,341/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -48210,7 +48210,7 @@
           <t>E | 250呎 (开放式)
 $584万
 $23,361/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -48218,7 +48218,7 @@
           <t>F | 392呎 (1房)
 $895万
 $22,836/呎
-(25年-03月-09日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -48226,7 +48226,7 @@
           <t>G | 391呎 (1房)
 $881万
 $22,535/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr"/>
@@ -48269,7 +48269,7 @@
           <t>D | 609呎 (2房)
 $2028万
 $33,300/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -48285,7 +48285,7 @@
           <t>F | 384呎 (1房)
 $834万
 $21,710/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -48293,7 +48293,7 @@
           <t>G | 384呎 (1房)
 $848万
 $22,072/呎
-(23年-11月-07日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -48301,7 +48301,7 @@
           <t>H | 250呎 (开放式)
 $568万
 $22,702/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -48309,7 +48309,7 @@
           <t>J | 392呎 (1房)
 $855万
 $21,809/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -48317,7 +48317,7 @@
           <t>K | 388呎 (1房)
 $869万
 $22,386/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -48325,7 +48325,7 @@
           <t>L | 476呎 (2房)
 $1108万
 $23,270/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48364,7 +48364,7 @@
           <t>D | 609呎 (2房)
 $1979万
 $32,500/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -48380,7 +48380,7 @@
           <t>F | 384呎 (1房)
 $827万
 $21,525/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -48388,7 +48388,7 @@
           <t>G | 384呎 (1房)
 $827万
 $21,525/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -48396,7 +48396,7 @@
           <t>H | 250呎 (开放式)
 $585万
 $23,386/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -48404,7 +48404,7 @@
           <t>J | 392呎 (1房)
 $848万
 $21,621/呎
-(23年-06月-30日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -48412,7 +48412,7 @@
           <t>K | 388呎 (1房)
 $842万
 $21,709/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -48420,7 +48420,7 @@
           <t>L | 476呎 (2房)
 $1098万
 $23,071/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48435,7 +48435,7 @@
           <t>A | 936呎 (3房)
 $3373万
 $36,038/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -48475,7 +48475,7 @@
           <t>F | 384呎 (1房)
 $824万
 $21,464/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -48483,7 +48483,7 @@
           <t>G | 384呎 (1房)
 $824万
 $21,464/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -48491,7 +48491,7 @@
           <t>H | 250呎 (开放式)
 $561万
 $22,450/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -48499,7 +48499,7 @@
           <t>J | 392呎 (1房)
 $859万
 $21,916/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -48507,7 +48507,7 @@
           <t>K | 388呎 (1房)
 $840万
 $21,644/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -48515,7 +48515,7 @@
           <t>L | 476呎 (2房)
 $1095万
 $23,003/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48530,7 +48530,7 @@
           <t>A | 936呎 (3房)
 $3288万
 $35,128/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -48570,7 +48570,7 @@
           <t>F | 384呎 (1房)
 $822万
 $21,401/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -48578,7 +48578,7 @@
           <t>G | 384呎 (1房)
 $822万
 $21,401/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -48586,7 +48586,7 @@
           <t>H | 250呎 (开放式)
 $566万
 $22,633/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -48594,7 +48594,7 @@
           <t>J | 392呎 (1房)
 $866万
 $22,091/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -48602,7 +48602,7 @@
           <t>K | 388呎 (1房)
 $837万
 $21,581/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -48610,7 +48610,7 @@
           <t>L | 476呎 (2房)
 $1092万
 $22,937/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48625,7 +48625,7 @@
           <t>A | 936呎 (3房)
 $3280万
 $35,037/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -48649,7 +48649,7 @@
           <t>D | 609呎 (2房)
 $1973万
 $32,400/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -48665,7 +48665,7 @@
           <t>F | 384呎 (1房)
 $819万
 $21,340/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -48673,7 +48673,7 @@
           <t>G | 384呎 (1房)
 $819万
 $21,340/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -48681,7 +48681,7 @@
           <t>H | 250呎 (开放式)
 $564万
 $22,568/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -48689,7 +48689,7 @@
           <t>J | 392呎 (1房)
 $840万
 $21,430/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -48697,7 +48697,7 @@
           <t>K | 388呎 (1房)
 $835万
 $21,519/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -48705,7 +48705,7 @@
           <t>L | 476呎 (2房)
 $1107万
 $23,252/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -48720,7 +48720,7 @@
           <t>A | 936呎 (3房)
 $3293万
 $35,185/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -48760,7 +48760,7 @@
           <t>F | 384呎 (1房)
 $817万
 $21,277/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -48768,7 +48768,7 @@
           <t>G | 384呎 (1房)
 $817万
 $21,277/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -48776,7 +48776,7 @@
           <t>H | 250呎 (开放式)
 $556万
 $22,259/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -48784,7 +48784,7 @@
           <t>J | 392呎 (1房)
 $838万
 $21,368/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -48792,7 +48792,7 @@
           <t>K | 388呎 (1房)
 $856万
 $22,050/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -48800,7 +48800,7 @@
           <t>L | 476呎 (2房)
 $1116万
 $23,438/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48815,7 +48815,7 @@
           <t>A | 936呎 (3房)
 $3280万
 $35,037/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -48855,7 +48855,7 @@
           <t>F | 384呎 (1房)
 $812万
 $21,155/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -48863,7 +48863,7 @@
           <t>G | 384呎 (1房)
 $767万
 $19,979/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -48871,7 +48871,7 @@
           <t>H | 250呎 (开放式)
 $563万
 $22,502/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -48879,7 +48879,7 @@
           <t>J | 392呎 (1房)
 $833万
 $21,242/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -48887,7 +48887,7 @@
           <t>K | 388呎 (1房)
 $841万
 $21,684/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -48895,7 +48895,7 @@
           <t>L | 476呎 (2房)
 $1097万
 $23,050/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -48910,7 +48910,7 @@
           <t>A | 936呎 (3房)
 $3213万
 $34,327/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -48950,7 +48950,7 @@
           <t>F | 384呎 (1房)
 $810万
 $21,091/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -48958,7 +48958,7 @@
           <t>G | 384呎 (1房)
 $810万
 $21,091/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -48966,7 +48966,7 @@
           <t>H | 250呎 (开放式)
 $552万
 $22,068/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -48974,7 +48974,7 @@
           <t>J | 392呎 (1房)
 $844万
 $21,533/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -48982,7 +48982,7 @@
           <t>K | 388呎 (1房)
 $825万
 $21,264/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -48990,7 +48990,7 @@
           <t>L | 476呎 (2房)
 $1076万
 $22,604/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49005,7 +49005,7 @@
           <t>A | 936呎 (3房)
 $3195万
 $34,136/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -49045,7 +49045,7 @@
           <t>F | 384呎 (1房)
 $808万
 $21,030/呎
-(24年-01月-14日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -49053,7 +49053,7 @@
           <t>G | 384呎 (1房)
 $808万
 $21,030/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -49061,7 +49061,7 @@
           <t>H | 250呎 (开放式)
 $550万
 $22,007/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -49069,7 +49069,7 @@
           <t>J | 392呎 (1房)
 $828万
 $21,118/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -49077,7 +49077,7 @@
           <t>K | 388呎 (1房)
 $823万
 $21,201/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -49085,7 +49085,7 @@
           <t>L | 476呎 (2房)
 $1073万
 $22,538/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49100,7 +49100,7 @@
           <t>A | 936呎 (3房)
 $3176万
 $33,932/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -49140,7 +49140,7 @@
           <t>F | 384呎 (1房)
 $805万
 $20,967/呎
-(23年-11月-12日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -49148,7 +49148,7 @@
           <t>G | 384呎 (1房)
 $805万
 $20,967/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -49156,7 +49156,7 @@
           <t>H | 250呎 (开放式)
 $549万
 $21,942/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -49164,7 +49164,7 @@
           <t>J | 392呎 (1房)
 $825万
 $21,054/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -49172,7 +49172,7 @@
           <t>K | 388呎 (1房)
 $820万
 $21,138/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -49180,7 +49180,7 @@
           <t>L | 476呎 (2房)
 $1082万
 $22,721/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49195,7 +49195,7 @@
           <t>A | 936呎 (3房)
 $3167万
 $33,836/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -49235,7 +49235,7 @@
           <t>F | 384呎 (1房)
 $803万
 $20,906/呎
-(23年-08月-03日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -49243,7 +49243,7 @@
           <t>G | 384呎 (1房)
 $803万
 $20,906/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -49251,7 +49251,7 @@
           <t>H | 250呎 (开放式)
 $559万
 $22,363/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -49259,7 +49259,7 @@
           <t>J | 392呎 (1房)
 $823万
 $20,992/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -49267,7 +49267,7 @@
           <t>K | 388呎 (1房)
 $818万
 $21,073/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -49275,7 +49275,7 @@
           <t>L | 476呎 (2房)
 $1078万
 $22,654/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49290,7 +49290,7 @@
           <t>A | 936呎 (3房)
 $3205万
 $34,237/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -49330,7 +49330,7 @@
           <t>F | 384呎 (1房)
 $800万
 $20,845/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -49338,7 +49338,7 @@
           <t>G | 384呎 (1房)
 $800万
 $20,845/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -49346,7 +49346,7 @@
           <t>H | 250呎 (开放式)
 $545万
 $21,816/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -49354,7 +49354,7 @@
           <t>J | 392呎 (1房)
 $820万
 $20,930/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -49362,7 +49362,7 @@
           <t>K | 388呎 (1房)
 $815万
 $21,011/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -49370,7 +49370,7 @@
           <t>L | 476呎 (2房)
 $1087万
 $22,836/呎
-(23年-06月-30日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -49385,7 +49385,7 @@
           <t>A | 936呎 (3房)
 $3195万
 $34,136/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -49425,7 +49425,7 @@
           <t>F | 384呎 (1房)
 $798万
 $20,782/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -49433,7 +49433,7 @@
           <t>G | 384呎 (1房)
 $798万
 $20,782/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -49441,7 +49441,7 @@
           <t>H | 250呎 (开放式)
 $550万
 $21,993/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -49449,7 +49449,7 @@
           <t>J | 392呎 (1房)
 $832万
 $21,213/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -49457,7 +49457,7 @@
           <t>K | 388呎 (1房)
 $813万
 $20,948/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -49465,7 +49465,7 @@
           <t>L | 476呎 (2房)
 $1078万
 $22,642/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -49480,7 +49480,7 @@
           <t>A | 936呎 (3房)
 $3160万
 $33,761/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -49520,7 +49520,7 @@
           <t>F | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-08月-14日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -49528,7 +49528,7 @@
           <t>G | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -49536,7 +49536,7 @@
           <t>H | 250呎 (开放式)
 $548万
 $21,931/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -49544,7 +49544,7 @@
           <t>J | 392呎 (1房)
 $815万
 $20,803/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -49552,7 +49552,7 @@
           <t>K | 388呎 (1房)
 $810万
 $20,883/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -49560,7 +49560,7 @@
           <t>L | 476呎 (2房)
 $1057万
 $22,205/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49575,7 +49575,7 @@
           <t>A | 936呎 (3房)
 $3184万
 $34,015/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -49615,7 +49615,7 @@
           <t>F | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -49623,7 +49623,7 @@
           <t>G | 384呎 (1房)
 $805万
 $20,951/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -49631,7 +49631,7 @@
           <t>H | 250呎 (开放式)
 $557万
 $22,292/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -49639,7 +49639,7 @@
           <t>J | 392呎 (1房)
 $815万
 $20,803/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -49647,7 +49647,7 @@
           <t>K | 388呎 (1房)
 $810万
 $20,883/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -49655,7 +49655,7 @@
           <t>L | 476呎 (2房)
 $1057万
 $22,205/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49670,7 +49670,7 @@
           <t>A | 936呎 (3房)
 $3176万
 $33,936/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -49710,7 +49710,7 @@
           <t>F | 384呎 (1房)
 $793万
 $20,660/呎
-(24年-01月-24日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -49718,7 +49718,7 @@
           <t>G | 384呎 (1房)
 $793万
 $20,660/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -49726,7 +49726,7 @@
           <t>H | 250呎 (开放式)
 $547万
 $21,865/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -49734,7 +49734,7 @@
           <t>J | 392呎 (1房)
 $813万
 $20,739/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -49742,7 +49742,7 @@
           <t>K | 388呎 (1房)
 $808万
 $20,821/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -49750,7 +49750,7 @@
           <t>L | 476呎 (2房)
 $1054万
 $22,139/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49765,7 +49765,7 @@
           <t>A | 936呎 (3房)
 $3167万
 $33,836/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -49805,7 +49805,7 @@
           <t>F | 384呎 (1房)
 $804万
 $20,940/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -49813,7 +49813,7 @@
           <t>G | 384呎 (1房)
 $813万
 $21,169/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -49821,7 +49821,7 @@
           <t>H | 250呎 (开放式)
 $539万
 $21,560/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -49829,7 +49829,7 @@
           <t>J | 392呎 (1房)
 $811万
 $20,677/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -49837,7 +49837,7 @@
           <t>K | 388呎 (1房)
 $805万
 $20,756/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -49845,7 +49845,7 @@
           <t>L | 476呎 (2房)
 $1051万
 $22,073/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49860,7 +49860,7 @@
           <t>A | 936呎 (3房)
 $3158万
 $33,736/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -49900,7 +49900,7 @@
           <t>F | 384呎 (1房)
 $789万
 $20,536/呎
-(23年-08月-08日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -49908,7 +49908,7 @@
           <t>G | 384呎 (1房)
 $797万
 $20,764/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -49916,7 +49916,7 @@
           <t>H | 250呎 (开放式)
 $543万
 $21,738/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -49924,7 +49924,7 @@
           <t>J | 392呎 (1房)
 $808万
 $20,615/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -49932,7 +49932,7 @@
           <t>K | 388呎 (1房)
 $812万
 $20,923/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -49940,7 +49940,7 @@
           <t>L | 476呎 (2房)
 $1048万
 $22,007/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -49995,7 +49995,7 @@
           <t>F | 384呎 (1房)
 $786万
 $20,473/呎
-(23年-08月-06日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -50003,7 +50003,7 @@
           <t>G | 384呎 (1房)
 $799万
 $20,814/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -50011,7 +50011,7 @@
           <t>H | 250呎 (开放式)
 $545万
 $21,792/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -50019,7 +50019,7 @@
           <t>J | 392呎 (1房)
 $819万
 $20,893/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -50027,7 +50027,7 @@
           <t>K | 388呎 (1房)
 $800万
 $20,630/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -50035,7 +50035,7 @@
           <t>L | 476呎 (2房)
 $1044万
 $21,940/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50090,7 +50090,7 @@
           <t>F | 384呎 (1房)
 $797万
 $20,752/呎
-(24年-01月-30日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -50098,7 +50098,7 @@
           <t>G | 384呎 (1房)
 $784万
 $20,412/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -50106,7 +50106,7 @@
           <t>H | 250呎 (开放式)
 $534万
 $21,373/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -50114,7 +50114,7 @@
           <t>J | 392呎 (1房)
 $821万
 $20,944/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -50122,7 +50122,7 @@
           <t>K | 388呎 (1房)
 $807万
 $20,794/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -50130,7 +50130,7 @@
           <t>L | 476呎 (2房)
 $1041万
 $21,872/呎
-(23年-08月-03日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -50185,7 +50185,7 @@
           <t>F | 384呎 (1房)
 $790万
 $20,577/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -50193,7 +50193,7 @@
           <t>G | 384呎 (1房)
 $781万
 $20,351/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -50201,7 +50201,7 @@
           <t>H | 250呎 (开放式)
 $548万
 $21,900/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -50209,7 +50209,7 @@
           <t>J | 392呎 (1房)
 $801万
 $20,427/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -50217,7 +50217,7 @@
           <t>K | 388呎 (1房)
 $809万
 $20,844/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -50225,7 +50225,7 @@
           <t>L | 476呎 (2房)
 $1050万
 $22,048/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50280,7 +50280,7 @@
           <t>F | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -50288,7 +50288,7 @@
           <t>G | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -50296,7 +50296,7 @@
           <t>H | 250呎 (开放式)
 $531万
 $21,244/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -50304,7 +50304,7 @@
           <t>J | 392呎 (1房)
 $798万
 $20,362/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -50312,7 +50312,7 @@
           <t>K | 388呎 (1房)
 $793万
 $20,440/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -50320,7 +50320,7 @@
           <t>L | 476呎 (2房)
 $1035万
 $21,740/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50375,7 +50375,7 @@
           <t>F | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -50383,7 +50383,7 @@
           <t>G | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -50391,7 +50391,7 @@
           <t>H | 250呎 (开放式)
 $531万
 $21,240/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -50399,7 +50399,7 @@
           <t>J | 392呎 (1房)
 $798万
 $20,362/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -50407,7 +50407,7 @@
           <t>K | 388呎 (1房)
 $793万
 $20,440/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -50415,7 +50415,7 @@
           <t>L | 476呎 (2房)
 $1035万
 $21,740/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50470,7 +50470,7 @@
           <t>F | 384呎 (1房)
 $790万
 $20,564/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -50478,7 +50478,7 @@
           <t>G | 384呎 (1房)
 $777万
 $20,227/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -50486,7 +50486,7 @@
           <t>H | 250呎 (开放式)
 $530万
 $21,182/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -50494,7 +50494,7 @@
           <t>J | 392呎 (1房)
 $809万
 $20,639/呎
-(23年-08月-09日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -50502,7 +50502,7 @@
           <t>K | 388呎 (1房)
 $791万
 $20,375/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -50510,7 +50510,7 @@
           <t>L | 476呎 (2房)
 $1072万
 $22,517/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50565,7 +50565,7 @@
           <t>F | 384呎 (1房)
 $774万
 $20,163/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -50573,7 +50573,7 @@
           <t>G | 384呎 (1房)
 $791万
 $20,611/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -50581,7 +50581,7 @@
           <t>H | 250呎 (开放式)
 $528万
 $21,118/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -50589,7 +50589,7 @@
           <t>J | 392呎 (1房)
 $793万
 $20,239/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -50597,7 +50597,7 @@
           <t>K | 388呎 (1房)
 $788万
 $20,313/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -50605,7 +50605,7 @@
           <t>L | 476呎 (2房)
 $1046万
 $21,968/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -50660,7 +50660,7 @@
           <t>F | 384呎 (1房)
 $772万
 $20,102/呎
-(23年-08月-10日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -50668,7 +50668,7 @@
           <t>G | 384呎 (1房)
 $772万
 $20,102/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -50676,7 +50676,7 @@
           <t>H | 250呎 (开放式)
 $526万
 $21,056/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -50684,7 +50684,7 @@
           <t>J | 392呎 (1房)
 $791万
 $20,174/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -50692,7 +50692,7 @@
           <t>K | 388呎 (1房)
 $794万
 $20,475/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -50700,7 +50700,7 @@
           <t>L | 476呎 (2房)
 $1025万
 $21,539/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50755,7 +50755,7 @@
           <t>F | 384呎 (1房)
 $767万
 $19,978/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -50763,7 +50763,7 @@
           <t>G | 384呎 (1房)
 $767万
 $19,978/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -50771,7 +50771,7 @@
           <t>H | 250呎 (开放式)
 $523万
 $20,927/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -50779,7 +50779,7 @@
           <t>J | 392呎 (1房)
 $786万
 $20,048/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -50787,7 +50787,7 @@
           <t>K | 388呎 (1房)
 $737万
 $19,004/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -50795,7 +50795,7 @@
           <t>L | 476呎 (2房)
 $1019万
 $21,407/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -50850,7 +50850,7 @@
           <t>F | 384呎 (1房)
 $760万
 $19,788/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -50858,7 +50858,7 @@
           <t>G | 384呎 (1房)
 $781万
 $20,343/呎
-(23年-08月-09日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -50866,7 +50866,7 @@
           <t>H | 250呎 (开放式)
 $518万
 $20,729/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -50874,7 +50874,7 @@
           <t>J | 392呎 (1房)
 $735万
 $18,756/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -50882,7 +50882,7 @@
           <t>K | 388呎 (1房)
 $730万
 $18,825/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -50890,7 +50890,7 @@
           <t>L | 476呎 (2房)
 $1010万
 $21,209/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -51076,7 +51076,7 @@
           <t>A | 1204呎 (3房)
 $5422万
 $45,037/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -51100,7 +51100,7 @@
           <t>D | 250呎 (开放式)
 $582万
 $23,280/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -51108,7 +51108,7 @@
           <t>E | 390呎 (1房)
 $856万
 $21,939/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -51116,7 +51116,7 @@
           <t>F | 395呎 (1房)
 $867万
 $21,941/呎
-(24年-12月-17日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -51124,7 +51124,7 @@
           <t>G | 250呎 (开放式)
 $590万
 $23,604/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -51132,7 +51132,7 @@
           <t>H | 384呎 (1房)
 $852万
 $22,175/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -51140,7 +51140,7 @@
           <t>J | 604呎 (2房)
 $1380万
 $22,856/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr"/>
@@ -51182,7 +51182,7 @@
           <t>D | 609呎 (2房)
 $1870万
 $30,700/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -51198,7 +51198,7 @@
           <t>F | 564呎 (2房)
 $1747万
 $30,975/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -51206,7 +51206,7 @@
           <t>G | 250呎 (开放式)
 $595万
 $23,782/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -51214,7 +51214,7 @@
           <t>H | 390呎 (1房)
 $832万
 $21,321/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -51222,7 +51222,7 @@
           <t>J | 395呎 (1房)
 $805万
 $20,372/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -51230,7 +51230,7 @@
           <t>K | 250呎 (开放式)
 $563万
 $22,540/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -51238,7 +51238,7 @@
           <t>L | 384呎 (1房)
 $828万
 $21,551/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -51246,7 +51246,7 @@
           <t>M | 604呎 (2房)
 $1311万
 $21,703/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51261,7 +51261,7 @@
           <t>A | 678呎 (2房)
 $2271万
 $33,500/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -51285,7 +51285,7 @@
           <t>D | 609呎 (2房)
 $1849万
 $30,356/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -51301,7 +51301,7 @@
           <t>F | 564呎 (2房)
 $1727万
 $30,629/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -51309,7 +51309,7 @@
           <t>G | 250呎 (开放式)
 $590万
 $23,581/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -51317,7 +51317,7 @@
           <t>H | 390呎 (1房)
 $824万
 $21,138/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -51325,7 +51325,7 @@
           <t>J | 395呎 (1房)
 $798万
 $20,200/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -51333,7 +51333,7 @@
           <t>K | 250呎 (开放式)
 $568万
 $22,721/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -51341,7 +51341,7 @@
           <t>L | 384呎 (1房)
 $820万
 $21,366/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -51349,7 +51349,7 @@
           <t>M | 604呎 (2房)
 $1300万
 $21,518/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51364,7 +51364,7 @@
           <t>A | 678呎 (2房)
 $2258万
 $33,300/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -51388,7 +51388,7 @@
           <t>D | 609呎 (2房)
 $1859万
 $30,519/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -51404,7 +51404,7 @@
           <t>F | 564呎 (2房)
 $1746万
 $30,964/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -51412,7 +51412,7 @@
           <t>G | 250呎 (开放式)
 $588万
 $23,515/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -51420,7 +51420,7 @@
           <t>H | 390呎 (1房)
 $838万
 $21,498/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -51428,7 +51428,7 @@
           <t>J | 395呎 (1房)
 $833万
 $21,078/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -51436,7 +51436,7 @@
           <t>K | 250呎 (开放式)
 $566万
 $22,659/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -51444,7 +51444,7 @@
           <t>L | 384呎 (1房)
 $818万
 $21,302/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -51452,7 +51452,7 @@
           <t>M | 604呎 (2房)
 $1296万
 $21,455/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51467,7 +51467,7 @@
           <t>A | 678呎 (2房)
 $2281万
 $33,650/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -51475,7 +51475,7 @@
           <t>B | 474呎 (1房)
 $1456万
 $30,712/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -51491,7 +51491,7 @@
           <t>D | 609呎 (2房)
 $1828万
 $30,012/呎
-(23年-09月-14日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -51507,7 +51507,7 @@
           <t>F | 564呎 (2房)
 $1708万
 $30,284/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -51515,7 +51515,7 @@
           <t>G | 250呎 (开放式)
 $586万
 $23,450/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -51523,7 +51523,7 @@
           <t>H | 390呎 (1房)
 $820万
 $21,016/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -51531,7 +51531,7 @@
           <t>J | 395呎 (1房)
 $830万
 $21,019/呎
-(24年-07月-30日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -51539,7 +51539,7 @@
           <t>K | 250呎 (开放式)
 $556万
 $22,223/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -51547,7 +51547,7 @@
           <t>L | 384呎 (1房)
 $816万
 $21,241/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -51555,7 +51555,7 @@
           <t>M | 604呎 (2房)
 $1292万
 $21,394/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51570,7 +51570,7 @@
           <t>A | 678呎 (2房)
 $2195万
 $32,379/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -51578,7 +51578,7 @@
           <t>B | 474呎 (1房)
 $1447万
 $30,534/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -51594,7 +51594,7 @@
           <t>D | 609呎 (2房)
 $1817万
 $29,839/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -51610,7 +51610,7 @@
           <t>F | 564呎 (2房)
 $1717万
 $30,446/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -51618,7 +51618,7 @@
           <t>G | 250呎 (开放式)
 $585万
 $23,384/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -51626,7 +51626,7 @@
           <t>H | 390呎 (1房)
 $831万
 $21,303/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -51634,7 +51634,7 @@
           <t>J | 395呎 (1房)
 $828万
 $20,960/呎
-(24年-08月-15日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -51642,7 +51642,7 @@
           <t>K | 250呎 (开放式)
 $563万
 $22,531/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -51650,7 +51650,7 @@
           <t>L | 384呎 (1房)
 $813万
 $21,178/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -51658,7 +51658,7 @@
           <t>M | 603呎 (2房)
 $1288万
 $21,367/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51673,7 +51673,7 @@
           <t>A | 678呎 (2房)
 $2183万
 $32,193/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -51681,7 +51681,7 @@
           <t>B | 474呎 (1房)
 $1439万
 $30,357/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -51697,7 +51697,7 @@
           <t>D | 609呎 (2房)
 $1807万
 $29,667/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
@@ -51713,7 +51713,7 @@
           <t>F | 564呎 (2房)
 $1717万
 $30,438/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -51721,7 +51721,7 @@
           <t>G | 250呎 (开放式)
 $583万
 $23,310/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -51729,7 +51729,7 @@
           <t>H | 390呎 (1房)
 $837万
 $21,474/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -51737,7 +51737,7 @@
           <t>J | 395呎 (1房)
 $825万
 $20,898/呎
-(24年-07月-18日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -51745,7 +51745,7 @@
           <t>K | 250呎 (开放式)
 $562万
 $22,465/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -51753,7 +51753,7 @@
           <t>L | 384呎 (1房)
 $811万
 $21,117/呎
-(23年-09月-04日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -51761,7 +51761,7 @@
           <t>M | 604呎 (2房)
 $1299万
 $21,505/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -51776,7 +51776,7 @@
           <t>A | 678呎 (2房)
 $2170万
 $32,007/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -51800,7 +51800,7 @@
           <t>D | 609呎 (2房)
 $1796万
 $29,496/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -51816,7 +51816,7 @@
           <t>F | 564呎 (2房)
 $1679万
 $29,767/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -51824,7 +51824,7 @@
           <t>G | 250呎 (开放式)
 $560万
 $22,417/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -51832,7 +51832,7 @@
           <t>H | 390呎 (1房)
 $819万
 $21,002/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -51840,7 +51840,7 @@
           <t>J | 395呎 (1房)
 $834万
 $21,124/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -51848,7 +51848,7 @@
           <t>K | 250呎 (开放式)
 $549万
 $21,971/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -51856,7 +51856,7 @@
           <t>L | 384呎 (1房)
 $806万
 $20,993/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -51864,7 +51864,7 @@
           <t>M | 603呎 (2房)
 $1327万
 $22,004/呎
-(23年-07月-10日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -51879,7 +51879,7 @@
           <t>A | 678呎 (2房)
 $2157万
 $31,821/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -51903,7 +51903,7 @@
           <t>D | 609呎 (2房)
 $1786万
 $29,323/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -51919,7 +51919,7 @@
           <t>F | 564呎 (2房)
 $1669万
 $29,593/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -51927,7 +51927,7 @@
           <t>G | 250呎 (开放式)
 $559万
 $22,355/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -51935,7 +51935,7 @@
           <t>H | 390呎 (1房)
 $821万
 $21,057/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -51943,7 +51943,7 @@
           <t>J | 395呎 (1房)
 $827万
 $20,948/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -51951,7 +51951,7 @@
           <t>K | 250呎 (开放式)
 $557万
 $22,271/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -51959,7 +51959,7 @@
           <t>L | 384呎 (1房)
 $804万
 $20,932/呎
-(23年-08月-20日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -51967,7 +51967,7 @@
           <t>M | 604呎 (2房)
 $1274万
 $21,084/呎
-(23年-08月-10日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -51982,7 +51982,7 @@
           <t>A | 678呎 (2房)
 $2145万
 $31,635/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -52006,7 +52006,7 @@
           <t>D | 609呎 (2房)
 $1775万
 $29,152/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -52022,7 +52022,7 @@
           <t>F | 564呎 (2房)
 $1659万
 $29,421/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -52030,7 +52030,7 @@
           <t>G | 250呎 (开放式)
 $568万
 $22,736/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -52038,7 +52038,7 @@
           <t>H | 390呎 (1房)
 $805万
 $20,649/呎
-(23年-12月-28日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -52046,7 +52046,7 @@
           <t>J | 395呎 (1房)
 $830万
 $21,003/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -52054,7 +52054,7 @@
           <t>K | 250呎 (开放式)
 $555万
 $22,209/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -52062,7 +52062,7 @@
           <t>L | 384呎 (1房)
 $801万
 $20,869/呎
-(23年-08月-09日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -52070,7 +52070,7 @@
           <t>M | 604呎 (2房)
 $1291万
 $21,372/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -52109,7 +52109,7 @@
           <t>D | 609呎 (2房)
 $1765万
 $28,979/呎
-(24年-08月-05日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -52125,7 +52125,7 @@
           <t>F | 564呎 (2房)
 $1650万
 $29,248/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -52133,7 +52133,7 @@
           <t>G | 250呎 (开放式)
 $567万
 $22,666/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -52141,7 +52141,7 @@
           <t>H | 390呎 (1房)
 $803万
 $20,589/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -52149,7 +52149,7 @@
           <t>J | 395呎 (1房)
 $814万
 $20,597/呎
-(24年-05月-12日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -52157,7 +52157,7 @@
           <t>K | 250呎 (开放式)
 $554万
 $22,143/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -52165,7 +52165,7 @@
           <t>L | 384呎 (1房)
 $799万
 $20,808/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -52173,7 +52173,7 @@
           <t>M | 603呎 (2房)
 $1266万
 $20,996/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -52212,7 +52212,7 @@
           <t>D | 609呎 (2房)
 $1760万
 $28,893/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -52228,7 +52228,7 @@
           <t>F | 564呎 (2房)
 $1645万
 $29,162/呎
-(24年-12月-12日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -52236,7 +52236,7 @@
           <t>G | 250呎 (开放式)
 $554万
 $22,161/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -52244,7 +52244,7 @@
           <t>H | 390呎 (1房)
 $801万
 $20,529/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -52252,7 +52252,7 @@
           <t>J | 395呎 (1房)
 $811万
 $20,538/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -52260,7 +52260,7 @@
           <t>K | 250呎 (开放式)
 $552万
 $22,077/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -52268,7 +52268,7 @@
           <t>L | 384呎 (1房)
 $797万
 $20,747/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -52276,7 +52276,7 @@
           <t>M | 604呎 (2房)
 $1262万
 $20,898/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -52315,7 +52315,7 @@
           <t>D | 609呎 (2房)
 $1754万
 $28,807/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -52331,7 +52331,7 @@
           <t>F | 564呎 (2房)
 $1640万
 $29,076/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -52339,7 +52339,7 @@
           <t>G | 250呎 (开放式)
 $543万
 $21,733/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -52347,7 +52347,7 @@
           <t>H | 390呎 (1房)
 $798万
 $20,467/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -52355,7 +52355,7 @@
           <t>J | 395呎 (1房)
 $809万
 $20,479/呎
-(24年-07月-08日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -52363,7 +52363,7 @@
           <t>K | 250呎 (开放式)
 $541万
 $21,654/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -52371,7 +52371,7 @@
           <t>L | 384呎 (1房)
 $794万
 $20,684/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -52379,7 +52379,7 @@
           <t>M | 604呎 (2房)
 $1273万
 $21,069/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -52418,7 +52418,7 @@
           <t>D | 609呎 (2房)
 $1749万
 $28,720/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -52434,7 +52434,7 @@
           <t>F | 564呎 (2房)
 $1635万
 $28,990/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -52442,7 +52442,7 @@
           <t>G | 250呎 (开放式)
 $542万
 $21,672/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -52450,7 +52450,7 @@
           <t>H | 390呎 (1房)
 $796万
 $20,407/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -52458,7 +52458,7 @@
           <t>J | 395呎 (1房)
 $820万
 $20,758/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -52466,7 +52466,7 @@
           <t>K | 250呎 (开放式)
 $546万
 $21,829/呎
-(23年-10月-02日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -52474,7 +52474,7 @@
           <t>L | 384呎 (1房)
 $792万
 $20,623/呎
-(23年-09月-21日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -52482,7 +52482,7 @@
           <t>M | 604呎 (2房)
 $1290万
 $21,351/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
           <t>D | 609呎 (2房)
 $1744万
 $28,634/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -52537,7 +52537,7 @@
           <t>F | 564呎 (2房)
 $1630万
 $28,904/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -52545,7 +52545,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,607/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -52553,7 +52553,7 @@
           <t>H | 390呎 (1房)
 $793万
 $20,345/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -52561,7 +52561,7 @@
           <t>J | 395呎 (1房)
 $804万
 $20,358/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -52569,7 +52569,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,528/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -52577,7 +52577,7 @@
           <t>L | 384呎 (1房)
 $790万
 $20,562/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -52585,7 +52585,7 @@
           <t>M | 604呎 (2房)
 $1251万
 $20,713/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -52600,7 +52600,7 @@
           <t>A | 678呎 (2房)
 $2107万
 $31,078/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -52624,7 +52624,7 @@
           <t>D | 609呎 (2房)
 $1744万
 $28,634/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -52640,7 +52640,7 @@
           <t>F | 564呎 (2房)
 $1630万
 $28,904/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -52648,7 +52648,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,607/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -52656,7 +52656,7 @@
           <t>H | 390呎 (1房)
 $793万
 $20,345/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -52664,7 +52664,7 @@
           <t>J | 395呎 (1房)
 $804万
 $20,358/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -52672,7 +52672,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,528/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -52680,7 +52680,7 @@
           <t>L | 384呎 (1房)
 $803万
 $20,904/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -52688,7 +52688,7 @@
           <t>M | 603呎 (2房)
 $1251万
 $20,748/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
           <t>A | 678呎 (2房)
 $2101万
 $30,985/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -52727,7 +52727,7 @@
           <t>D | 609呎 (2房)
 $1739万
 $28,549/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -52743,7 +52743,7 @@
           <t>F | 564呎 (2房)
 $1625万
 $28,818/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -52751,7 +52751,7 @@
           <t>G | 250呎 (开放式)
 $554万
 $22,144/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -52759,7 +52759,7 @@
           <t>H | 390呎 (1房)
 $804万
 $20,623/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -52767,7 +52767,7 @@
           <t>J | 395呎 (1房)
 $811万
 $20,522/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -52775,7 +52775,7 @@
           <t>K | 250呎 (开放式)
 $557万
 $22,298/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -52783,7 +52783,7 @@
           <t>L | 384呎 (1房)
 $787万
 $20,498/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -52791,7 +52791,7 @@
           <t>M | 604呎 (2房)
 $1247万
 $20,651/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -52806,7 +52806,7 @@
           <t>A | 678呎 (2房)
 $2129万
 $31,407/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -52830,7 +52830,7 @@
           <t>D | 609呎 (2房)
 $1733万
 $28,463/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -52838,7 +52838,7 @@
           <t>E | 415呎 (1房)
 $1231万
 $29,672/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -52846,7 +52846,7 @@
           <t>F | 564呎 (2房)
 $1620万
 $28,731/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -52854,7 +52854,7 @@
           <t>G | 250呎 (开放式)
 $537万
 $21,481/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -52862,7 +52862,7 @@
           <t>H | 390呎 (1房)
 $789万
 $20,225/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -52870,7 +52870,7 @@
           <t>J | 395呎 (1房)
 $813万
 $20,575/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -52878,7 +52878,7 @@
           <t>K | 250呎 (开放式)
 $535万
 $21,398/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -52886,7 +52886,7 @@
           <t>L | 384呎 (1房)
 $785万
 $20,438/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -52894,7 +52894,7 @@
           <t>M | 604呎 (2房)
 $1244万
 $20,590/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -52933,7 +52933,7 @@
           <t>D | 609呎 (2房)
 $1728万
 $28,377/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -52949,7 +52949,7 @@
           <t>F | 564呎 (2房)
 $1616万
 $28,645/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -52957,7 +52957,7 @@
           <t>G | 250呎 (开放式)
 $535万
 $21,416/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -52965,7 +52965,7 @@
           <t>H | 390呎 (1房)
 $786万
 $20,162/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -52973,7 +52973,7 @@
           <t>J | 395呎 (1房)
 $797万
 $20,178/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -52981,7 +52981,7 @@
           <t>K | 250呎 (开放式)
 $533万
 $21,337/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -52989,7 +52989,7 @@
           <t>L | 384呎 (1房)
 $782万
 $20,374/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -52997,7 +52997,7 @@
           <t>M | 603呎 (2房)
 $1240万
 $20,561/呎
-(23年-08月-03日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53036,7 +53036,7 @@
           <t>D | 609呎 (2房)
 $1723万
 $28,290/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -53052,7 +53052,7 @@
           <t>F | 564呎 (2房)
 $1611万
 $28,559/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -53060,7 +53060,7 @@
           <t>G | 250呎 (开放式)
 $534万
 $21,355/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -53068,7 +53068,7 @@
           <t>H | 390呎 (1房)
 $784万
 $20,102/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -53076,7 +53076,7 @@
           <t>J | 395呎 (1房)
 $795万
 $20,117/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -53084,7 +53084,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,508/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -53092,7 +53092,7 @@
           <t>L | 384呎 (1房)
 $780万
 $20,313/呎
-(23年-12月-10日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -53100,7 +53100,7 @@
           <t>M | 603呎 (2房)
 $1270万
 $21,069/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53155,7 +53155,7 @@
           <t>F | 564呎 (2房)
 $1601万
 $28,387/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -53163,7 +53163,7 @@
           <t>G | 250呎 (开放式)
 $532万
 $21,290/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -53171,7 +53171,7 @@
           <t>H | 390呎 (1房)
 $782万
 $20,042/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -53179,7 +53179,7 @@
           <t>J | 395呎 (1房)
 $805万
 $20,392/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -53187,7 +53187,7 @@
           <t>K | 250呎 (开放式)
 $539万
 $21,564/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -53195,7 +53195,7 @@
           <t>L | 384呎 (1房)
 $778万
 $20,252/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -53203,7 +53203,7 @@
           <t>M | 603呎 (2房)
 $1232万
 $20,437/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53258,7 +53258,7 @@
           <t>F | 564呎 (2房)
 $1591万
 $28,213/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -53266,7 +53266,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,583/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -53274,7 +53274,7 @@
           <t>H | 390呎 (1房)
 $795万
 $20,379/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -53282,7 +53282,7 @@
           <t>J | 395呎 (1房)
 $803万
 $20,329/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -53290,7 +53290,7 @@
           <t>K | 250呎 (开放式)
 $529万
 $21,146/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -53298,7 +53298,7 @@
           <t>L | 384呎 (1房)
 $775万
 $20,189/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -53306,7 +53306,7 @@
           <t>M | 603呎 (2房)
 $1229万
 $20,376/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53369,7 +53369,7 @@
           <t>G | 250呎 (开放式)
 $529万
 $21,164/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -53377,7 +53377,7 @@
           <t>H | 390呎 (1房)
 $792万
 $20,319/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -53385,7 +53385,7 @@
           <t>J | 395呎 (1房)
 $801万
 $20,269/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -53393,7 +53393,7 @@
           <t>K | 250呎 (开放式)
 $527万
 $21,082/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -53401,7 +53401,7 @@
           <t>L | 384呎 (1房)
 $773万
 $20,128/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -53409,7 +53409,7 @@
           <t>M | 604呎 (2房)
 $1252万
 $20,730/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53472,7 +53472,7 @@
           <t>G | 250呎 (开放式)
 $538万
 $21,517/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -53480,7 +53480,7 @@
           <t>H | 390呎 (1房)
 $792万
 $20,319/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -53488,7 +53488,7 @@
           <t>J | 395呎 (1房)
 $788万
 $19,937/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -53496,7 +53496,7 @@
           <t>K | 250呎 (开放式)
 $527万
 $21,082/呎
-(23年-07月-10日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -53504,7 +53504,7 @@
           <t>L | 384呎 (1房)
 $773万
 $20,128/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -53512,7 +53512,7 @@
           <t>M | 603呎 (2房)
 $1225万
 $20,313/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -53575,7 +53575,7 @@
           <t>G | 250呎 (开放式)
 $536万
 $21,451/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -53583,7 +53583,7 @@
           <t>H | 390呎 (1房)
 $783万
 $20,078/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -53591,7 +53591,7 @@
           <t>J | 395呎 (1房)
 $785万
 $19,877/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -53599,7 +53599,7 @@
           <t>K | 250呎 (开放式)
 $526万
 $21,020/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -53607,7 +53607,7 @@
           <t>L | 384呎 (1房)
 $783万
 $20,399/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -53615,7 +53615,7 @@
           <t>M | 604呎 (2房)
 $1221万
 $20,219/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -53678,7 +53678,7 @@
           <t>G | 250呎 (开放式)
 $545万
 $21,817/呎
-(24年-05月-12日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -53686,7 +53686,7 @@
           <t>H | 390呎 (1房)
 $788万
 $20,195/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -53694,7 +53694,7 @@
           <t>J | 395呎 (1房)
 $796万
 $20,146/呎
-(24年-03月-03日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -53702,7 +53702,7 @@
           <t>K | 250呎 (开放式)
 $530万
 $21,188/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -53710,7 +53710,7 @@
           <t>L | 384呎 (1房)
 $768万
 $20,004/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -53718,7 +53718,7 @@
           <t>M | 604呎 (2房)
 $1217万
 $20,156/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -53781,7 +53781,7 @@
           <t>G | 250呎 (开放式)
 $535万
 $21,395/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -53789,7 +53789,7 @@
           <t>H | 390呎 (1房)
 $785万
 $20,132/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -53797,7 +53797,7 @@
           <t>J | 395呎 (1房)
 $793万
 $20,086/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -53805,7 +53805,7 @@
           <t>K | 250呎 (开放式)
 $522万
 $20,894/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -53813,7 +53813,7 @@
           <t>L | 384呎 (1房)
 $779万
 $20,275/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -53821,7 +53821,7 @@
           <t>M | 604呎 (2房)
 $1214万
 $20,095/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -53884,7 +53884,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,620/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -53892,7 +53892,7 @@
           <t>H | 390呎 (1房)
 $780万
 $20,008/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -53900,7 +53900,7 @@
           <t>J | 395呎 (1房)
 $776万
 $19,636/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -53908,7 +53908,7 @@
           <t>K | 250呎 (开放式)
 $528万
 $21,114/呎
-(23年-08月-16日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -53916,7 +53916,7 @@
           <t>L | 384呎 (1房)
 $774万
 $20,149/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -53924,7 +53924,7 @@
           <t>M | 604呎 (2房)
 $1206万
 $19,971/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -53987,7 +53987,7 @@
           <t>G | 250呎 (开放式)
 $525万
 $21,002/呎
-(24年-07月-02日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -53995,7 +53995,7 @@
           <t>H | 390呎 (1房)
 $773万
 $19,821/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -54003,7 +54003,7 @@
           <t>J | 395呎 (1房)
 $782万
 $19,808/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -54011,7 +54011,7 @@
           <t>K | 250呎 (开放式)
 $515万
 $20,592/呎
-(24年-01月-01日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -54019,7 +54019,7 @@
           <t>L | 384呎 (1房)
 $767万
 $19,985/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -54027,7 +54027,7 @@
           <t>M | 604呎 (2房)
 $1215万
 $20,118/呎
-(23年-08月-07日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -54165,7 +54165,7 @@
           <t>A | 649呎 (3房)
 $1444万
 $22,255/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -54173,7 +54173,7 @@
           <t>B | 649呎 (3房)
 $1440万
 $22,184/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -54181,7 +54181,7 @@
           <t>C | 304呎 (1房)
 $613万
 $20,172/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -54189,7 +54189,7 @@
           <t>D | 303呎 (1房)
 $609万
 $20,109/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54204,7 +54204,7 @@
           <t>A | 649呎 (3房)
 $1411万
 $21,736/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -54212,7 +54212,7 @@
           <t>B | 649呎 (3房)
 $1430万
 $22,028/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -54220,7 +54220,7 @@
           <t>C | 304呎 (1房)
 $610万
 $20,055/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -54228,7 +54228,7 @@
           <t>D | 304呎 (1房)
 $616万
 $20,253/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54243,7 +54243,7 @@
           <t>A | 649呎 (3房)
 $1394万
 $21,477/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -54251,7 +54251,7 @@
           <t>B | 649呎 (3房)
 $1428万
 $22,002/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -54259,7 +54259,7 @@
           <t>C | 304呎 (1房)
 $613万
 $20,155/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -54267,7 +54267,7 @@
           <t>D | 304呎 (1房)
 $609万
 $20,020/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54282,7 +54282,7 @@
           <t>A | 649呎 (3房)
 $1415万
 $21,807/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -54290,7 +54290,7 @@
           <t>B | 649呎 (3房)
 $1372万
 $21,148/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -54298,7 +54298,7 @@
           <t>C | 304呎 (1房)
 $610万
 $20,058/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -54306,7 +54306,7 @@
           <t>D | 303呎 (1房)
 $598万
 $19,744/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54318,10 +54318,10 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 627呎 (3房)
+          <t>A | 626呎 (3房)
 $1722万
-$27,456/呎
-(23年-06月-30日)</t>
+$27,500/呎
+(23年-06月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -54329,7 +54329,7 @@
           <t>B | 627呎 (3房)
 $1694万
 $27,010/呎
-(23年-07月-26日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -54337,7 +54337,7 @@
           <t>C | 282呎 (1房)
 $638万
 $22,634/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -54345,7 +54345,7 @@
           <t>D | 282呎 (1房)
 $644万
 $22,848/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54483,7 +54483,7 @@
           <t>A | 649呎 (3房)
 $1524万
 $23,488/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -54491,7 +54491,7 @@
           <t>B | 649呎 (3房)
 $1497万
 $23,069/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -54499,7 +54499,7 @@
           <t>C | 303呎 (1房)
 $617万
 $20,361/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -54507,7 +54507,7 @@
           <t>D | 303呎 (1房)
 $626万
 $20,664/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54522,7 +54522,7 @@
           <t>A | 649呎 (3房)
 $1481万
 $22,820/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -54530,7 +54530,7 @@
           <t>B | 649呎 (3房)
 $1462万
 $22,530/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -54538,7 +54538,7 @@
           <t>C | 303呎 (1房)
 $662万
 $21,861/呎
-(23年-08月-08日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -54546,7 +54546,7 @@
           <t>D | 303呎 (1房)
 $622万
 $20,540/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54561,7 +54561,7 @@
           <t>A | 648呎 (3房)
 $1440万
 $22,215/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -54569,7 +54569,7 @@
           <t>B | 649呎 (3房)
 $1445万
 $22,260/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -54577,7 +54577,7 @@
           <t>C | 303呎 (1房)
 $610万
 $20,124/呎
-(23年-06月-30日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -54585,7 +54585,7 @@
           <t>D | 303呎 (1房)
 $619万
 $20,415/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54600,7 +54600,7 @@
           <t>A | 649呎 (3房)
 $1422万
 $21,916/呎
-(23年-08月-03日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -54608,7 +54608,7 @@
           <t>B | 648呎 (3房)
 $1419万
 $21,904/呎
-(23年-06月-30日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -54616,7 +54616,7 @@
           <t>C | 303呎 (1房)
 $606万
 $20,005/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -54624,7 +54624,7 @@
           <t>D | 304呎 (1房)
 $615万
 $20,223/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54639,7 +54639,7 @@
           <t>A | 627呎 (3房)
 $1711万
 $27,289/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -54647,7 +54647,7 @@
           <t>B | 627呎 (3房)
 $1724万
 $27,498/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -54655,7 +54655,7 @@
           <t>C | 282呎 (1房)
 $656万
 $23,263/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -54663,7 +54663,7 @@
           <t>D | 282呎 (1房)
 $658万
 $23,339/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54801,7 +54801,7 @@
           <t>A | 648呎 (3房)
 $1521万
 $23,468/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -54809,7 +54809,7 @@
           <t>B | 648呎 (3房)
 $1494万
 $23,049/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -54817,7 +54817,7 @@
           <t>C | 303呎 (1房)
 $657万
 $21,671/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -54825,7 +54825,7 @@
           <t>D | 304呎 (1房)
 $664万
 $21,834/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -54840,7 +54840,7 @@
           <t>A | 648呎 (3房)
 $1491万
 $23,006/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -54848,7 +54848,7 @@
           <t>B | 649呎 (3房)
 $1480万
 $22,809/呎
-(23年-08月-06日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -54856,7 +54856,7 @@
           <t>C | 304呎 (1房)
 $660万
 $21,708/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -54864,7 +54864,7 @@
           <t>D | 303呎 (1房)
 $660万
 $21,775/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -54879,7 +54879,7 @@
           <t>A | 649呎 (3房)
 $1482万
 $22,836/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -54887,7 +54887,7 @@
           <t>B | 649呎 (3房)
 $1472万
 $22,673/呎
-(23年-08月-03日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -54895,7 +54895,7 @@
           <t>C | 304呎 (1房)
 $660万
 $21,698/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -54903,7 +54903,7 @@
           <t>D | 304呎 (1房)
 $674万
 $22,176/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
     </row>
@@ -54918,7 +54918,7 @@
           <t>A | 649呎 (3房)
 $1473万
 $22,700/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -54926,7 +54926,7 @@
           <t>B | 649呎 (3房)
 $1479万
 $22,788/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -54934,7 +54934,7 @@
           <t>C | 304呎 (1房)
 $645万
 $21,212/呎
-(23年-08月-06日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -54942,7 +54942,7 @@
           <t>D | 304呎 (1房)
 $652万
 $21,446/呎
-(23年-07月-10日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -54957,7 +54957,7 @@
           <t>A | 627呎 (3房)
 $1759万
 $28,046/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -54965,7 +54965,7 @@
           <t>B | 627呎 (3房)
 $1783万
 $28,433/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -54973,7 +54973,7 @@
           <t>C | 282呎 (1房)
 $681万
 $24,147/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -54981,7 +54981,7 @@
           <t>D | 282呎 (1房)
 $688万
 $24,415/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -55119,7 +55119,7 @@
           <t>A | 648呎 (3房)
 $1401万
 $21,615/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -55127,7 +55127,7 @@
           <t>B | 649呎 (3房)
 $1388万
 $21,386/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -55135,7 +55135,7 @@
           <t>C | 303呎 (1房)
 $625万
 $20,622/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -55143,7 +55143,7 @@
           <t>D | 303呎 (1房)
 $628万
 $20,740/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -55158,7 +55158,7 @@
           <t>A | 648呎 (3房)
 $1381万
 $21,309/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -55166,7 +55166,7 @@
           <t>B | 649呎 (3房)
 $1391万
 $21,432/呎
-(23年-06月-30日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -55174,7 +55174,7 @@
           <t>C | 304呎 (1房)
 $611万
 $20,096/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -55182,7 +55182,7 @@
           <t>D | 303呎 (1房)
 $1391万
 $45,905/呎
-(23年-07月-27日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -55197,7 +55197,7 @@
           <t>A | 648呎 (3房)
 $1380万
 $21,299/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -55205,7 +55205,7 @@
           <t>B | 649呎 (3房)
 $1390万
 $21,420/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -55213,7 +55213,7 @@
           <t>C | 304呎 (1房)
 $617万
 $20,308/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -55221,7 +55221,7 @@
           <t>D | 304呎 (1房)
 $611万
 $20,093/呎
-(23年-07月-25日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -55236,7 +55236,7 @@
           <t>A | 649呎 (3房)
 $1372万
 $21,141/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -55244,7 +55244,7 @@
           <t>B | 648呎 (3房)
 $1359万
 $20,975/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -55252,7 +55252,7 @@
           <t>C | 304呎 (1房)
 $610万
 $20,074/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -55260,7 +55260,7 @@
           <t>D | 304呎 (1房)
 $607万
 $19,972/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -55275,7 +55275,7 @@
           <t>A | 627呎 (3房)
 $1682万
 $26,821/呎
-(23年-07月-23日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -55283,7 +55283,7 @@
           <t>B | 626呎 (3房)
 $1685万
 $26,924/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -55291,7 +55291,7 @@
           <t>C | 282呎 (1房)
 $661万
 $23,433/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -55299,7 +55299,7 @@
           <t>D | 282呎 (1房)
 $672万
 $23,827/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -10,10 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N742"/>
+  <dimension ref="A1:N722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -43045,7 +43044,7 @@
     <row r="663">
       <c r="A663" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B663" s="3" t="inlineStr">
@@ -43073,14 +43072,14 @@
       </c>
       <c r="G663" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="H663" s="5" t="n">
-        <v>6093000</v>
+        <v>6261300</v>
       </c>
       <c r="I663" s="5" t="n">
-        <v>20109</v>
+        <v>20664</v>
       </c>
       <c r="J663" s="3" t="inlineStr">
         <is>
@@ -43088,10 +43087,10 @@
         </is>
       </c>
       <c r="K663" s="5" t="n">
-        <v>6093000</v>
+        <v>6261300</v>
       </c>
       <c r="L663" s="5" t="n">
-        <v>20109</v>
+        <v>20664</v>
       </c>
       <c r="M663" s="3" t="inlineStr">
         <is>
@@ -43107,7 +43106,7 @@
     <row r="664">
       <c r="A664" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B664" s="3" t="inlineStr">
@@ -43126,7 +43125,7 @@
         </is>
       </c>
       <c r="E664" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F664" s="3" t="inlineStr">
         <is>
@@ -43135,14 +43134,14 @@
       </c>
       <c r="G664" s="3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="H664" s="5" t="n">
-        <v>6132300</v>
+        <v>6169500</v>
       </c>
       <c r="I664" s="5" t="n">
-        <v>20172</v>
+        <v>20361</v>
       </c>
       <c r="J664" s="3" t="inlineStr">
         <is>
@@ -43150,10 +43149,10 @@
         </is>
       </c>
       <c r="K664" s="5" t="n">
-        <v>6132300</v>
+        <v>6169500</v>
       </c>
       <c r="L664" s="5" t="n">
-        <v>20172</v>
+        <v>20361</v>
       </c>
       <c r="M664" s="3" t="inlineStr">
         <is>
@@ -43169,7 +43168,7 @@
     <row r="665">
       <c r="A665" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B665" s="3" t="inlineStr">
@@ -43197,14 +43196,14 @@
       </c>
       <c r="G665" s="3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H665" s="5" t="n">
-        <v>14397300</v>
+        <v>14972100</v>
       </c>
       <c r="I665" s="5" t="n">
-        <v>22184</v>
+        <v>23069</v>
       </c>
       <c r="J665" s="3" t="inlineStr">
         <is>
@@ -43212,10 +43211,10 @@
         </is>
       </c>
       <c r="K665" s="5" t="n">
-        <v>14397300</v>
+        <v>14972100</v>
       </c>
       <c r="L665" s="5" t="n">
-        <v>22184</v>
+        <v>23069</v>
       </c>
       <c r="M665" s="3" t="inlineStr">
         <is>
@@ -43231,7 +43230,7 @@
     <row r="666">
       <c r="A666" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B666" s="3" t="inlineStr">
@@ -43259,14 +43258,14 @@
       </c>
       <c r="G666" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H666" s="5" t="n">
-        <v>14443200</v>
+        <v>15243400</v>
       </c>
       <c r="I666" s="5" t="n">
-        <v>22255</v>
+        <v>23488</v>
       </c>
       <c r="J666" s="3" t="inlineStr">
         <is>
@@ -43274,10 +43273,10 @@
         </is>
       </c>
       <c r="K666" s="5" t="n">
-        <v>14443200</v>
+        <v>15243400</v>
       </c>
       <c r="L666" s="5" t="n">
-        <v>22255</v>
+        <v>23488</v>
       </c>
       <c r="M666" s="3" t="inlineStr">
         <is>
@@ -43293,7 +43292,7 @@
     <row r="667">
       <c r="A667" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B667" s="3" t="inlineStr">
@@ -43312,7 +43311,7 @@
         </is>
       </c>
       <c r="E667" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
@@ -43321,14 +43320,14 @@
       </c>
       <c r="G667" s="3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H667" s="5" t="n">
-        <v>6157000</v>
+        <v>6223500</v>
       </c>
       <c r="I667" s="5" t="n">
-        <v>20253</v>
+        <v>20540</v>
       </c>
       <c r="J667" s="3" t="inlineStr">
         <is>
@@ -43336,10 +43335,10 @@
         </is>
       </c>
       <c r="K667" s="5" t="n">
-        <v>6157000</v>
+        <v>6223500</v>
       </c>
       <c r="L667" s="5" t="n">
-        <v>20253</v>
+        <v>20540</v>
       </c>
       <c r="M667" s="3" t="inlineStr">
         <is>
@@ -43355,7 +43354,7 @@
     <row r="668">
       <c r="A668" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B668" s="3" t="inlineStr">
@@ -43374,7 +43373,7 @@
         </is>
       </c>
       <c r="E668" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F668" s="3" t="inlineStr">
         <is>
@@ -43383,14 +43382,14 @@
       </c>
       <c r="G668" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H668" s="5" t="n">
-        <v>6096600</v>
+        <v>6624000</v>
       </c>
       <c r="I668" s="5" t="n">
-        <v>20055</v>
+        <v>21861</v>
       </c>
       <c r="J668" s="3" t="inlineStr">
         <is>
@@ -43398,10 +43397,10 @@
         </is>
       </c>
       <c r="K668" s="5" t="n">
-        <v>6096600</v>
+        <v>6624000</v>
       </c>
       <c r="L668" s="5" t="n">
-        <v>20055</v>
+        <v>21861</v>
       </c>
       <c r="M668" s="3" t="inlineStr">
         <is>
@@ -43417,7 +43416,7 @@
     <row r="669">
       <c r="A669" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B669" s="3" t="inlineStr">
@@ -43445,14 +43444,14 @@
       </c>
       <c r="G669" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H669" s="5" t="n">
-        <v>14295900</v>
+        <v>14621700</v>
       </c>
       <c r="I669" s="5" t="n">
-        <v>22028</v>
+        <v>22530</v>
       </c>
       <c r="J669" s="3" t="inlineStr">
         <is>
@@ -43460,10 +43459,10 @@
         </is>
       </c>
       <c r="K669" s="5" t="n">
-        <v>14295900</v>
+        <v>14621700</v>
       </c>
       <c r="L669" s="5" t="n">
-        <v>22028</v>
+        <v>22530</v>
       </c>
       <c r="M669" s="3" t="inlineStr">
         <is>
@@ -43479,7 +43478,7 @@
     <row r="670">
       <c r="A670" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B670" s="3" t="inlineStr">
@@ -43507,14 +43506,14 @@
       </c>
       <c r="G670" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H670" s="5" t="n">
-        <v>14106600</v>
+        <v>14810100</v>
       </c>
       <c r="I670" s="5" t="n">
-        <v>21736</v>
+        <v>22820</v>
       </c>
       <c r="J670" s="3" t="inlineStr">
         <is>
@@ -43522,10 +43521,10 @@
         </is>
       </c>
       <c r="K670" s="5" t="n">
-        <v>14106600</v>
+        <v>14810100</v>
       </c>
       <c r="L670" s="5" t="n">
-        <v>21736</v>
+        <v>22820</v>
       </c>
       <c r="M670" s="3" t="inlineStr">
         <is>
@@ -43541,7 +43540,7 @@
     <row r="671">
       <c r="A671" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B671" s="3" t="inlineStr">
@@ -43560,7 +43559,7 @@
         </is>
       </c>
       <c r="E671" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F671" s="3" t="inlineStr">
         <is>
@@ -43569,14 +43568,14 @@
       </c>
       <c r="G671" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H671" s="5" t="n">
-        <v>6086000</v>
+        <v>6185700</v>
       </c>
       <c r="I671" s="5" t="n">
-        <v>20020</v>
+        <v>20415</v>
       </c>
       <c r="J671" s="3" t="inlineStr">
         <is>
@@ -43584,10 +43583,10 @@
         </is>
       </c>
       <c r="K671" s="5" t="n">
-        <v>6086000</v>
+        <v>6185700</v>
       </c>
       <c r="L671" s="5" t="n">
-        <v>20020</v>
+        <v>20415</v>
       </c>
       <c r="M671" s="3" t="inlineStr">
         <is>
@@ -43603,7 +43602,7 @@
     <row r="672">
       <c r="A672" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B672" s="3" t="inlineStr">
@@ -43622,7 +43621,7 @@
         </is>
       </c>
       <c r="E672" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F672" s="3" t="inlineStr">
         <is>
@@ -43631,14 +43630,14 @@
       </c>
       <c r="G672" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H672" s="5" t="n">
-        <v>6127200</v>
+        <v>6097500</v>
       </c>
       <c r="I672" s="5" t="n">
-        <v>20155</v>
+        <v>20124</v>
       </c>
       <c r="J672" s="3" t="inlineStr">
         <is>
@@ -43646,10 +43645,10 @@
         </is>
       </c>
       <c r="K672" s="5" t="n">
-        <v>6127200</v>
+        <v>6097500</v>
       </c>
       <c r="L672" s="5" t="n">
-        <v>20155</v>
+        <v>20124</v>
       </c>
       <c r="M672" s="3" t="inlineStr">
         <is>
@@ -43665,7 +43664,7 @@
     <row r="673">
       <c r="A673" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B673" s="3" t="inlineStr">
@@ -43697,10 +43696,10 @@
         </is>
       </c>
       <c r="H673" s="5" t="n">
-        <v>14279200</v>
+        <v>14446900</v>
       </c>
       <c r="I673" s="5" t="n">
-        <v>22002</v>
+        <v>22260</v>
       </c>
       <c r="J673" s="3" t="inlineStr">
         <is>
@@ -43708,10 +43707,10 @@
         </is>
       </c>
       <c r="K673" s="5" t="n">
-        <v>14279200</v>
+        <v>14446900</v>
       </c>
       <c r="L673" s="5" t="n">
-        <v>22002</v>
+        <v>22260</v>
       </c>
       <c r="M673" s="3" t="inlineStr">
         <is>
@@ -43727,7 +43726,7 @@
     <row r="674">
       <c r="A674" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B674" s="3" t="inlineStr">
@@ -43746,7 +43745,7 @@
         </is>
       </c>
       <c r="E674" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F674" s="3" t="inlineStr">
         <is>
@@ -43755,14 +43754,14 @@
       </c>
       <c r="G674" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H674" s="5" t="n">
-        <v>13938300</v>
+        <v>14395500</v>
       </c>
       <c r="I674" s="5" t="n">
-        <v>21477</v>
+        <v>22215</v>
       </c>
       <c r="J674" s="3" t="inlineStr">
         <is>
@@ -43770,10 +43769,10 @@
         </is>
       </c>
       <c r="K674" s="5" t="n">
-        <v>13938300</v>
+        <v>14395500</v>
       </c>
       <c r="L674" s="5" t="n">
-        <v>21477</v>
+        <v>22215</v>
       </c>
       <c r="M674" s="3" t="inlineStr">
         <is>
@@ -43789,7 +43788,7 @@
     <row r="675">
       <c r="A675" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B675" s="3" t="inlineStr">
@@ -43808,7 +43807,7 @@
         </is>
       </c>
       <c r="E675" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F675" s="3" t="inlineStr">
         <is>
@@ -43817,14 +43816,14 @@
       </c>
       <c r="G675" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H675" s="5" t="n">
-        <v>5982300</v>
+        <v>6147900</v>
       </c>
       <c r="I675" s="5" t="n">
-        <v>19744</v>
+        <v>20223</v>
       </c>
       <c r="J675" s="3" t="inlineStr">
         <is>
@@ -43832,10 +43831,10 @@
         </is>
       </c>
       <c r="K675" s="5" t="n">
-        <v>5982300</v>
+        <v>6147900</v>
       </c>
       <c r="L675" s="5" t="n">
-        <v>19744</v>
+        <v>20223</v>
       </c>
       <c r="M675" s="3" t="inlineStr">
         <is>
@@ -43851,7 +43850,7 @@
     <row r="676">
       <c r="A676" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B676" s="3" t="inlineStr">
@@ -43870,7 +43869,7 @@
         </is>
       </c>
       <c r="E676" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F676" s="3" t="inlineStr">
         <is>
@@ -43879,14 +43878,14 @@
       </c>
       <c r="G676" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H676" s="5" t="n">
-        <v>6097600</v>
+        <v>6061500</v>
       </c>
       <c r="I676" s="5" t="n">
-        <v>20058</v>
+        <v>20005</v>
       </c>
       <c r="J676" s="3" t="inlineStr">
         <is>
@@ -43894,10 +43893,10 @@
         </is>
       </c>
       <c r="K676" s="5" t="n">
-        <v>6097600</v>
+        <v>6061500</v>
       </c>
       <c r="L676" s="5" t="n">
-        <v>20058</v>
+        <v>20005</v>
       </c>
       <c r="M676" s="3" t="inlineStr">
         <is>
@@ -43913,7 +43912,7 @@
     <row r="677">
       <c r="A677" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B677" s="3" t="inlineStr">
@@ -43932,7 +43931,7 @@
         </is>
       </c>
       <c r="E677" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F677" s="3" t="inlineStr">
         <is>
@@ -43941,14 +43940,14 @@
       </c>
       <c r="G677" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H677" s="5" t="n">
-        <v>13725000</v>
+        <v>14194100</v>
       </c>
       <c r="I677" s="5" t="n">
-        <v>21148</v>
+        <v>21904</v>
       </c>
       <c r="J677" s="3" t="inlineStr">
         <is>
@@ -43956,10 +43955,10 @@
         </is>
       </c>
       <c r="K677" s="5" t="n">
-        <v>13725000</v>
+        <v>14194100</v>
       </c>
       <c r="L677" s="5" t="n">
-        <v>21148</v>
+        <v>21904</v>
       </c>
       <c r="M677" s="3" t="inlineStr">
         <is>
@@ -43975,7 +43974,7 @@
     <row r="678">
       <c r="A678" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B678" s="3" t="inlineStr">
@@ -44003,14 +44002,14 @@
       </c>
       <c r="G678" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H678" s="5" t="n">
-        <v>14152500</v>
+        <v>14223600</v>
       </c>
       <c r="I678" s="5" t="n">
-        <v>21807</v>
+        <v>21916</v>
       </c>
       <c r="J678" s="3" t="inlineStr">
         <is>
@@ -44018,10 +44017,10 @@
         </is>
       </c>
       <c r="K678" s="5" t="n">
-        <v>14152500</v>
+        <v>14223600</v>
       </c>
       <c r="L678" s="5" t="n">
-        <v>21807</v>
+        <v>21916</v>
       </c>
       <c r="M678" s="3" t="inlineStr">
         <is>
@@ -44037,7 +44036,7 @@
     <row r="679">
       <c r="A679" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B679" s="3" t="inlineStr">
@@ -44065,14 +44064,14 @@
       </c>
       <c r="G679" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H679" s="5" t="n">
-        <v>6443100</v>
+        <v>6581500</v>
       </c>
       <c r="I679" s="5" t="n">
-        <v>22848</v>
+        <v>23339</v>
       </c>
       <c r="J679" s="3" t="inlineStr">
         <is>
@@ -44080,10 +44079,10 @@
         </is>
       </c>
       <c r="K679" s="5" t="n">
-        <v>6443100</v>
+        <v>6581500</v>
       </c>
       <c r="L679" s="5" t="n">
-        <v>22848</v>
+        <v>23339</v>
       </c>
       <c r="M679" s="3" t="inlineStr">
         <is>
@@ -44099,7 +44098,7 @@
     <row r="680">
       <c r="A680" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B680" s="3" t="inlineStr">
@@ -44131,10 +44130,10 @@
         </is>
       </c>
       <c r="H680" s="5" t="n">
-        <v>6382800</v>
+        <v>6560100</v>
       </c>
       <c r="I680" s="5" t="n">
-        <v>22634</v>
+        <v>23263</v>
       </c>
       <c r="J680" s="3" t="inlineStr">
         <is>
@@ -44142,10 +44141,10 @@
         </is>
       </c>
       <c r="K680" s="5" t="n">
-        <v>6382800</v>
+        <v>6560100</v>
       </c>
       <c r="L680" s="5" t="n">
-        <v>22634</v>
+        <v>23263</v>
       </c>
       <c r="M680" s="3" t="inlineStr">
         <is>
@@ -44161,7 +44160,7 @@
     <row r="681">
       <c r="A681" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B681" s="3" t="inlineStr">
@@ -44189,14 +44188,14 @@
       </c>
       <c r="G681" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H681" s="5" t="n">
-        <v>16935300</v>
+        <v>17241300</v>
       </c>
       <c r="I681" s="5" t="n">
-        <v>27010</v>
+        <v>27498</v>
       </c>
       <c r="J681" s="3" t="inlineStr">
         <is>
@@ -44204,10 +44203,10 @@
         </is>
       </c>
       <c r="K681" s="5" t="n">
-        <v>16935300</v>
+        <v>17241300</v>
       </c>
       <c r="L681" s="5" t="n">
-        <v>27010</v>
+        <v>27498</v>
       </c>
       <c r="M681" s="3" t="inlineStr">
         <is>
@@ -44223,7 +44222,7 @@
     <row r="682">
       <c r="A682" s="3" t="inlineStr">
         <is>
-          <t>低座A座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B682" s="3" t="inlineStr">
@@ -44242,7 +44241,7 @@
         </is>
       </c>
       <c r="E682" s="4" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F682" s="3" t="inlineStr">
         <is>
@@ -44251,14 +44250,14 @@
       </c>
       <c r="G682" s="3" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H682" s="5" t="n">
-        <v>17215200</v>
+        <v>17109900</v>
       </c>
       <c r="I682" s="5" t="n">
-        <v>27500</v>
+        <v>27289</v>
       </c>
       <c r="J682" s="3" t="inlineStr">
         <is>
@@ -44266,10 +44265,10 @@
         </is>
       </c>
       <c r="K682" s="5" t="n">
-        <v>17215200</v>
+        <v>17109900</v>
       </c>
       <c r="L682" s="5" t="n">
-        <v>27500</v>
+        <v>27289</v>
       </c>
       <c r="M682" s="3" t="inlineStr">
         <is>
@@ -44285,7 +44284,7 @@
     <row r="683">
       <c r="A683" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B683" s="3" t="inlineStr">
@@ -44304,7 +44303,7 @@
         </is>
       </c>
       <c r="E683" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F683" s="3" t="inlineStr">
         <is>
@@ -44313,14 +44312,14 @@
       </c>
       <c r="G683" s="3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H683" s="5" t="n">
-        <v>6261300</v>
+        <v>6637500</v>
       </c>
       <c r="I683" s="5" t="n">
-        <v>20664</v>
+        <v>21834</v>
       </c>
       <c r="J683" s="3" t="inlineStr">
         <is>
@@ -44328,10 +44327,10 @@
         </is>
       </c>
       <c r="K683" s="5" t="n">
-        <v>6261300</v>
+        <v>6637500</v>
       </c>
       <c r="L683" s="5" t="n">
-        <v>20664</v>
+        <v>21834</v>
       </c>
       <c r="M683" s="3" t="inlineStr">
         <is>
@@ -44347,7 +44346,7 @@
     <row r="684">
       <c r="A684" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B684" s="3" t="inlineStr">
@@ -44375,14 +44374,14 @@
       </c>
       <c r="G684" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H684" s="5" t="n">
-        <v>6169500</v>
+        <v>6566400</v>
       </c>
       <c r="I684" s="5" t="n">
-        <v>20361</v>
+        <v>21671</v>
       </c>
       <c r="J684" s="3" t="inlineStr">
         <is>
@@ -44390,10 +44389,10 @@
         </is>
       </c>
       <c r="K684" s="5" t="n">
-        <v>6169500</v>
+        <v>6566400</v>
       </c>
       <c r="L684" s="5" t="n">
-        <v>20361</v>
+        <v>21671</v>
       </c>
       <c r="M684" s="3" t="inlineStr">
         <is>
@@ -44409,7 +44408,7 @@
     <row r="685">
       <c r="A685" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B685" s="3" t="inlineStr">
@@ -44428,7 +44427,7 @@
         </is>
       </c>
       <c r="E685" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F685" s="3" t="inlineStr">
         <is>
@@ -44437,14 +44436,14 @@
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H685" s="5" t="n">
-        <v>14972100</v>
+        <v>14935500</v>
       </c>
       <c r="I685" s="5" t="n">
-        <v>23069</v>
+        <v>23049</v>
       </c>
       <c r="J685" s="3" t="inlineStr">
         <is>
@@ -44452,10 +44451,10 @@
         </is>
       </c>
       <c r="K685" s="5" t="n">
-        <v>14972100</v>
+        <v>14935500</v>
       </c>
       <c r="L685" s="5" t="n">
-        <v>23069</v>
+        <v>23049</v>
       </c>
       <c r="M685" s="3" t="inlineStr">
         <is>
@@ -44471,7 +44470,7 @@
     <row r="686">
       <c r="A686" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B686" s="3" t="inlineStr">
@@ -44490,7 +44489,7 @@
         </is>
       </c>
       <c r="E686" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F686" s="3" t="inlineStr">
         <is>
@@ -44499,14 +44498,14 @@
       </c>
       <c r="G686" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="H686" s="5" t="n">
-        <v>15243400</v>
+        <v>15207000</v>
       </c>
       <c r="I686" s="5" t="n">
-        <v>23488</v>
+        <v>23468</v>
       </c>
       <c r="J686" s="3" t="inlineStr">
         <is>
@@ -44514,10 +44513,10 @@
         </is>
       </c>
       <c r="K686" s="5" t="n">
-        <v>15243400</v>
+        <v>15207000</v>
       </c>
       <c r="L686" s="5" t="n">
-        <v>23488</v>
+        <v>23468</v>
       </c>
       <c r="M686" s="3" t="inlineStr">
         <is>
@@ -44533,7 +44532,7 @@
     <row r="687">
       <c r="A687" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B687" s="3" t="inlineStr">
@@ -44561,14 +44560,14 @@
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H687" s="5" t="n">
-        <v>6223500</v>
+        <v>6597900</v>
       </c>
       <c r="I687" s="5" t="n">
-        <v>20540</v>
+        <v>21775</v>
       </c>
       <c r="J687" s="3" t="inlineStr">
         <is>
@@ -44576,10 +44575,10 @@
         </is>
       </c>
       <c r="K687" s="5" t="n">
-        <v>6223500</v>
+        <v>6597900</v>
       </c>
       <c r="L687" s="5" t="n">
-        <v>20540</v>
+        <v>21775</v>
       </c>
       <c r="M687" s="3" t="inlineStr">
         <is>
@@ -44595,7 +44594,7 @@
     <row r="688">
       <c r="A688" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B688" s="3" t="inlineStr">
@@ -44614,7 +44613,7 @@
         </is>
       </c>
       <c r="E688" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F688" s="3" t="inlineStr">
         <is>
@@ -44623,14 +44622,14 @@
       </c>
       <c r="G688" s="3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H688" s="5" t="n">
-        <v>6624000</v>
+        <v>6599300</v>
       </c>
       <c r="I688" s="5" t="n">
-        <v>21861</v>
+        <v>21708</v>
       </c>
       <c r="J688" s="3" t="inlineStr">
         <is>
@@ -44638,10 +44637,10 @@
         </is>
       </c>
       <c r="K688" s="5" t="n">
-        <v>6624000</v>
+        <v>6599300</v>
       </c>
       <c r="L688" s="5" t="n">
-        <v>21861</v>
+        <v>21708</v>
       </c>
       <c r="M688" s="3" t="inlineStr">
         <is>
@@ -44657,7 +44656,7 @@
     <row r="689">
       <c r="A689" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B689" s="3" t="inlineStr">
@@ -44685,14 +44684,14 @@
       </c>
       <c r="G689" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="H689" s="5" t="n">
-        <v>14621700</v>
+        <v>14803200</v>
       </c>
       <c r="I689" s="5" t="n">
-        <v>22530</v>
+        <v>22809</v>
       </c>
       <c r="J689" s="3" t="inlineStr">
         <is>
@@ -44700,10 +44699,10 @@
         </is>
       </c>
       <c r="K689" s="5" t="n">
-        <v>14621700</v>
+        <v>14803200</v>
       </c>
       <c r="L689" s="5" t="n">
-        <v>22530</v>
+        <v>22809</v>
       </c>
       <c r="M689" s="3" t="inlineStr">
         <is>
@@ -44719,7 +44718,7 @@
     <row r="690">
       <c r="A690" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B690" s="3" t="inlineStr">
@@ -44738,7 +44737,7 @@
         </is>
       </c>
       <c r="E690" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F690" s="3" t="inlineStr">
         <is>
@@ -44747,14 +44746,14 @@
       </c>
       <c r="G690" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H690" s="5" t="n">
-        <v>14810100</v>
+        <v>14907600</v>
       </c>
       <c r="I690" s="5" t="n">
-        <v>22820</v>
+        <v>23006</v>
       </c>
       <c r="J690" s="3" t="inlineStr">
         <is>
@@ -44762,10 +44761,10 @@
         </is>
       </c>
       <c r="K690" s="5" t="n">
-        <v>14810100</v>
+        <v>14907600</v>
       </c>
       <c r="L690" s="5" t="n">
-        <v>22820</v>
+        <v>23006</v>
       </c>
       <c r="M690" s="3" t="inlineStr">
         <is>
@@ -44781,7 +44780,7 @@
     <row r="691">
       <c r="A691" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B691" s="3" t="inlineStr">
@@ -44800,7 +44799,7 @@
         </is>
       </c>
       <c r="E691" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F691" s="3" t="inlineStr">
         <is>
@@ -44809,14 +44808,14 @@
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H691" s="5" t="n">
-        <v>6185700</v>
+        <v>6741400</v>
       </c>
       <c r="I691" s="5" t="n">
-        <v>20415</v>
+        <v>22176</v>
       </c>
       <c r="J691" s="3" t="inlineStr">
         <is>
@@ -44824,10 +44823,10 @@
         </is>
       </c>
       <c r="K691" s="5" t="n">
-        <v>6185700</v>
+        <v>6741400</v>
       </c>
       <c r="L691" s="5" t="n">
-        <v>20415</v>
+        <v>22176</v>
       </c>
       <c r="M691" s="3" t="inlineStr">
         <is>
@@ -44843,7 +44842,7 @@
     <row r="692">
       <c r="A692" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B692" s="3" t="inlineStr">
@@ -44862,7 +44861,7 @@
         </is>
       </c>
       <c r="E692" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F692" s="3" t="inlineStr">
         <is>
@@ -44871,14 +44870,14 @@
       </c>
       <c r="G692" s="3" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H692" s="5" t="n">
-        <v>6097500</v>
+        <v>6596200</v>
       </c>
       <c r="I692" s="5" t="n">
-        <v>20124</v>
+        <v>21698</v>
       </c>
       <c r="J692" s="3" t="inlineStr">
         <is>
@@ -44886,10 +44885,10 @@
         </is>
       </c>
       <c r="K692" s="5" t="n">
-        <v>6097500</v>
+        <v>6596200</v>
       </c>
       <c r="L692" s="5" t="n">
-        <v>20124</v>
+        <v>21698</v>
       </c>
       <c r="M692" s="3" t="inlineStr">
         <is>
@@ -44905,7 +44904,7 @@
     <row r="693">
       <c r="A693" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B693" s="3" t="inlineStr">
@@ -44933,14 +44932,14 @@
       </c>
       <c r="G693" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H693" s="5" t="n">
-        <v>14446900</v>
+        <v>14715000</v>
       </c>
       <c r="I693" s="5" t="n">
-        <v>22260</v>
+        <v>22673</v>
       </c>
       <c r="J693" s="3" t="inlineStr">
         <is>
@@ -44948,10 +44947,10 @@
         </is>
       </c>
       <c r="K693" s="5" t="n">
-        <v>14446900</v>
+        <v>14715000</v>
       </c>
       <c r="L693" s="5" t="n">
-        <v>22260</v>
+        <v>22673</v>
       </c>
       <c r="M693" s="3" t="inlineStr">
         <is>
@@ -44967,7 +44966,7 @@
     <row r="694">
       <c r="A694" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B694" s="3" t="inlineStr">
@@ -44986,7 +44985,7 @@
         </is>
       </c>
       <c r="E694" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F694" s="3" t="inlineStr">
         <is>
@@ -44995,14 +44994,14 @@
       </c>
       <c r="G694" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H694" s="5" t="n">
-        <v>14395500</v>
+        <v>14820300</v>
       </c>
       <c r="I694" s="5" t="n">
-        <v>22215</v>
+        <v>22836</v>
       </c>
       <c r="J694" s="3" t="inlineStr">
         <is>
@@ -45010,10 +45009,10 @@
         </is>
       </c>
       <c r="K694" s="5" t="n">
-        <v>14395500</v>
+        <v>14820300</v>
       </c>
       <c r="L694" s="5" t="n">
-        <v>22215</v>
+        <v>22836</v>
       </c>
       <c r="M694" s="3" t="inlineStr">
         <is>
@@ -45029,7 +45028,7 @@
     <row r="695">
       <c r="A695" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B695" s="3" t="inlineStr">
@@ -45057,14 +45056,14 @@
       </c>
       <c r="G695" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="H695" s="5" t="n">
-        <v>6147900</v>
+        <v>6519600</v>
       </c>
       <c r="I695" s="5" t="n">
-        <v>20223</v>
+        <v>21446</v>
       </c>
       <c r="J695" s="3" t="inlineStr">
         <is>
@@ -45072,10 +45071,10 @@
         </is>
       </c>
       <c r="K695" s="5" t="n">
-        <v>6147900</v>
+        <v>6519600</v>
       </c>
       <c r="L695" s="5" t="n">
-        <v>20223</v>
+        <v>21446</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -45091,7 +45090,7 @@
     <row r="696">
       <c r="A696" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B696" s="3" t="inlineStr">
@@ -45110,7 +45109,7 @@
         </is>
       </c>
       <c r="E696" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
@@ -45119,14 +45118,14 @@
       </c>
       <c r="G696" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="H696" s="5" t="n">
-        <v>6061500</v>
+        <v>6448500</v>
       </c>
       <c r="I696" s="5" t="n">
-        <v>20005</v>
+        <v>21212</v>
       </c>
       <c r="J696" s="3" t="inlineStr">
         <is>
@@ -45134,10 +45133,10 @@
         </is>
       </c>
       <c r="K696" s="5" t="n">
-        <v>6061500</v>
+        <v>6448500</v>
       </c>
       <c r="L696" s="5" t="n">
-        <v>20005</v>
+        <v>21212</v>
       </c>
       <c r="M696" s="3" t="inlineStr">
         <is>
@@ -45153,7 +45152,7 @@
     <row r="697">
       <c r="A697" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B697" s="3" t="inlineStr">
@@ -45172,7 +45171,7 @@
         </is>
       </c>
       <c r="E697" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F697" s="3" t="inlineStr">
         <is>
@@ -45181,14 +45180,14 @@
       </c>
       <c r="G697" s="3" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="H697" s="5" t="n">
-        <v>14194100</v>
+        <v>14789300</v>
       </c>
       <c r="I697" s="5" t="n">
-        <v>21904</v>
+        <v>22788</v>
       </c>
       <c r="J697" s="3" t="inlineStr">
         <is>
@@ -45196,10 +45195,10 @@
         </is>
       </c>
       <c r="K697" s="5" t="n">
-        <v>14194100</v>
+        <v>14789300</v>
       </c>
       <c r="L697" s="5" t="n">
-        <v>21904</v>
+        <v>22788</v>
       </c>
       <c r="M697" s="3" t="inlineStr">
         <is>
@@ -45215,7 +45214,7 @@
     <row r="698">
       <c r="A698" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B698" s="3" t="inlineStr">
@@ -45243,14 +45242,14 @@
       </c>
       <c r="G698" s="3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H698" s="5" t="n">
-        <v>14223600</v>
+        <v>14732100</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>21916</v>
+        <v>22700</v>
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
@@ -45258,10 +45257,10 @@
         </is>
       </c>
       <c r="K698" s="5" t="n">
-        <v>14223600</v>
+        <v>14732100</v>
       </c>
       <c r="L698" s="5" t="n">
-        <v>21916</v>
+        <v>22700</v>
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
@@ -45277,7 +45276,7 @@
     <row r="699">
       <c r="A699" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B699" s="3" t="inlineStr">
@@ -45305,14 +45304,14 @@
       </c>
       <c r="G699" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="H699" s="5" t="n">
-        <v>6581500</v>
+        <v>6885000</v>
       </c>
       <c r="I699" s="5" t="n">
-        <v>23339</v>
+        <v>24415</v>
       </c>
       <c r="J699" s="3" t="inlineStr">
         <is>
@@ -45320,10 +45319,10 @@
         </is>
       </c>
       <c r="K699" s="5" t="n">
-        <v>6581500</v>
+        <v>6885000</v>
       </c>
       <c r="L699" s="5" t="n">
-        <v>23339</v>
+        <v>24415</v>
       </c>
       <c r="M699" s="3" t="inlineStr">
         <is>
@@ -45339,7 +45338,7 @@
     <row r="700">
       <c r="A700" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B700" s="3" t="inlineStr">
@@ -45367,14 +45366,14 @@
       </c>
       <c r="G700" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H700" s="5" t="n">
-        <v>6560100</v>
+        <v>6809400</v>
       </c>
       <c r="I700" s="5" t="n">
-        <v>23263</v>
+        <v>24147</v>
       </c>
       <c r="J700" s="3" t="inlineStr">
         <is>
@@ -45382,10 +45381,10 @@
         </is>
       </c>
       <c r="K700" s="5" t="n">
-        <v>6560100</v>
+        <v>6809400</v>
       </c>
       <c r="L700" s="5" t="n">
-        <v>23263</v>
+        <v>24147</v>
       </c>
       <c r="M700" s="3" t="inlineStr">
         <is>
@@ -45401,7 +45400,7 @@
     <row r="701">
       <c r="A701" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B701" s="3" t="inlineStr">
@@ -45429,14 +45428,14 @@
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
-        <v>17241300</v>
+        <v>17827800</v>
       </c>
       <c r="I701" s="5" t="n">
-        <v>27498</v>
+        <v>28433</v>
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
@@ -45444,10 +45443,10 @@
         </is>
       </c>
       <c r="K701" s="5" t="n">
-        <v>17241300</v>
+        <v>17827800</v>
       </c>
       <c r="L701" s="5" t="n">
-        <v>27498</v>
+        <v>28433</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
@@ -45463,7 +45462,7 @@
     <row r="702">
       <c r="A702" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座C座</t>
         </is>
       </c>
       <c r="B702" s="3" t="inlineStr">
@@ -45491,14 +45490,14 @@
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H702" s="5" t="n">
-        <v>17109900</v>
+        <v>17585100</v>
       </c>
       <c r="I702" s="5" t="n">
-        <v>27289</v>
+        <v>28046</v>
       </c>
       <c r="J702" s="3" t="inlineStr">
         <is>
@@ -45506,10 +45505,10 @@
         </is>
       </c>
       <c r="K702" s="5" t="n">
-        <v>17109900</v>
+        <v>17585100</v>
       </c>
       <c r="L702" s="5" t="n">
-        <v>27289</v>
+        <v>28046</v>
       </c>
       <c r="M702" s="3" t="inlineStr">
         <is>
@@ -45525,7 +45524,7 @@
     <row r="703">
       <c r="A703" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B703" s="3" t="inlineStr">
@@ -45544,7 +45543,7 @@
         </is>
       </c>
       <c r="E703" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
@@ -45553,14 +45552,14 @@
       </c>
       <c r="G703" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H703" s="5" t="n">
-        <v>6637500</v>
+        <v>6284200</v>
       </c>
       <c r="I703" s="5" t="n">
-        <v>21834</v>
+        <v>20740</v>
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
@@ -45568,10 +45567,10 @@
         </is>
       </c>
       <c r="K703" s="5" t="n">
-        <v>6637500</v>
+        <v>6284200</v>
       </c>
       <c r="L703" s="5" t="n">
-        <v>21834</v>
+        <v>20740</v>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
@@ -45587,7 +45586,7 @@
     <row r="704">
       <c r="A704" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B704" s="3" t="inlineStr">
@@ -45615,14 +45614,14 @@
       </c>
       <c r="G704" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H704" s="5" t="n">
-        <v>6566400</v>
+        <v>6248500</v>
       </c>
       <c r="I704" s="5" t="n">
-        <v>21671</v>
+        <v>20622</v>
       </c>
       <c r="J704" s="3" t="inlineStr">
         <is>
@@ -45630,10 +45629,10 @@
         </is>
       </c>
       <c r="K704" s="5" t="n">
-        <v>6566400</v>
+        <v>6248500</v>
       </c>
       <c r="L704" s="5" t="n">
-        <v>21671</v>
+        <v>20622</v>
       </c>
       <c r="M704" s="3" t="inlineStr">
         <is>
@@ -45649,7 +45648,7 @@
     <row r="705">
       <c r="A705" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B705" s="3" t="inlineStr">
@@ -45668,7 +45667,7 @@
         </is>
       </c>
       <c r="E705" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F705" s="3" t="inlineStr">
         <is>
@@ -45677,14 +45676,14 @@
       </c>
       <c r="G705" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H705" s="5" t="n">
-        <v>14935500</v>
+        <v>13879800</v>
       </c>
       <c r="I705" s="5" t="n">
-        <v>23049</v>
+        <v>21386</v>
       </c>
       <c r="J705" s="3" t="inlineStr">
         <is>
@@ -45692,10 +45691,10 @@
         </is>
       </c>
       <c r="K705" s="5" t="n">
-        <v>14935500</v>
+        <v>13879800</v>
       </c>
       <c r="L705" s="5" t="n">
-        <v>23049</v>
+        <v>21386</v>
       </c>
       <c r="M705" s="3" t="inlineStr">
         <is>
@@ -45711,7 +45710,7 @@
     <row r="706">
       <c r="A706" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B706" s="3" t="inlineStr">
@@ -45739,14 +45738,14 @@
       </c>
       <c r="G706" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H706" s="5" t="n">
-        <v>15207000</v>
+        <v>14006800</v>
       </c>
       <c r="I706" s="5" t="n">
-        <v>23468</v>
+        <v>21615</v>
       </c>
       <c r="J706" s="3" t="inlineStr">
         <is>
@@ -45754,10 +45753,10 @@
         </is>
       </c>
       <c r="K706" s="5" t="n">
-        <v>15207000</v>
+        <v>14006800</v>
       </c>
       <c r="L706" s="5" t="n">
-        <v>23468</v>
+        <v>21615</v>
       </c>
       <c r="M706" s="3" t="inlineStr">
         <is>
@@ -45773,7 +45772,7 @@
     <row r="707">
       <c r="A707" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B707" s="3" t="inlineStr">
@@ -45801,14 +45800,14 @@
       </c>
       <c r="G707" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="H707" s="5" t="n">
-        <v>6597900</v>
+        <v>13909300</v>
       </c>
       <c r="I707" s="5" t="n">
-        <v>21775</v>
+        <v>45905</v>
       </c>
       <c r="J707" s="3" t="inlineStr">
         <is>
@@ -45816,10 +45815,10 @@
         </is>
       </c>
       <c r="K707" s="5" t="n">
-        <v>6597900</v>
+        <v>13909300</v>
       </c>
       <c r="L707" s="5" t="n">
-        <v>21775</v>
+        <v>45905</v>
       </c>
       <c r="M707" s="3" t="inlineStr">
         <is>
@@ -45835,7 +45834,7 @@
     <row r="708">
       <c r="A708" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B708" s="3" t="inlineStr">
@@ -45863,14 +45862,14 @@
       </c>
       <c r="G708" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H708" s="5" t="n">
-        <v>6599300</v>
+        <v>6109200</v>
       </c>
       <c r="I708" s="5" t="n">
-        <v>21708</v>
+        <v>20096</v>
       </c>
       <c r="J708" s="3" t="inlineStr">
         <is>
@@ -45878,10 +45877,10 @@
         </is>
       </c>
       <c r="K708" s="5" t="n">
-        <v>6599300</v>
+        <v>6109200</v>
       </c>
       <c r="L708" s="5" t="n">
-        <v>21708</v>
+        <v>20096</v>
       </c>
       <c r="M708" s="3" t="inlineStr">
         <is>
@@ -45897,7 +45896,7 @@
     <row r="709">
       <c r="A709" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B709" s="3" t="inlineStr">
@@ -45925,14 +45924,14 @@
       </c>
       <c r="G709" s="3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H709" s="5" t="n">
-        <v>14803200</v>
+        <v>13909300</v>
       </c>
       <c r="I709" s="5" t="n">
-        <v>22809</v>
+        <v>21432</v>
       </c>
       <c r="J709" s="3" t="inlineStr">
         <is>
@@ -45940,10 +45939,10 @@
         </is>
       </c>
       <c r="K709" s="5" t="n">
-        <v>14803200</v>
+        <v>13909300</v>
       </c>
       <c r="L709" s="5" t="n">
-        <v>22809</v>
+        <v>21432</v>
       </c>
       <c r="M709" s="3" t="inlineStr">
         <is>
@@ -45959,7 +45958,7 @@
     <row r="710">
       <c r="A710" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B710" s="3" t="inlineStr">
@@ -45987,14 +45986,14 @@
       </c>
       <c r="G710" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="H710" s="5" t="n">
-        <v>14907600</v>
+        <v>13808300</v>
       </c>
       <c r="I710" s="5" t="n">
-        <v>23006</v>
+        <v>21309</v>
       </c>
       <c r="J710" s="3" t="inlineStr">
         <is>
@@ -46002,10 +46001,10 @@
         </is>
       </c>
       <c r="K710" s="5" t="n">
-        <v>14907600</v>
+        <v>13808300</v>
       </c>
       <c r="L710" s="5" t="n">
-        <v>23006</v>
+        <v>21309</v>
       </c>
       <c r="M710" s="3" t="inlineStr">
         <is>
@@ -46021,7 +46020,7 @@
     <row r="711">
       <c r="A711" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B711" s="3" t="inlineStr">
@@ -46049,14 +46048,14 @@
       </c>
       <c r="G711" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H711" s="5" t="n">
-        <v>6741400</v>
+        <v>6108300</v>
       </c>
       <c r="I711" s="5" t="n">
-        <v>22176</v>
+        <v>20093</v>
       </c>
       <c r="J711" s="3" t="inlineStr">
         <is>
@@ -46064,10 +46063,10 @@
         </is>
       </c>
       <c r="K711" s="5" t="n">
-        <v>6741400</v>
+        <v>6108300</v>
       </c>
       <c r="L711" s="5" t="n">
-        <v>22176</v>
+        <v>20093</v>
       </c>
       <c r="M711" s="3" t="inlineStr">
         <is>
@@ -46083,7 +46082,7 @@
     <row r="712">
       <c r="A712" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B712" s="3" t="inlineStr">
@@ -46111,14 +46110,14 @@
       </c>
       <c r="G712" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H712" s="5" t="n">
-        <v>6596200</v>
+        <v>6173500</v>
       </c>
       <c r="I712" s="5" t="n">
-        <v>21698</v>
+        <v>20308</v>
       </c>
       <c r="J712" s="3" t="inlineStr">
         <is>
@@ -46126,10 +46125,10 @@
         </is>
       </c>
       <c r="K712" s="5" t="n">
-        <v>6596200</v>
+        <v>6173500</v>
       </c>
       <c r="L712" s="5" t="n">
-        <v>21698</v>
+        <v>20308</v>
       </c>
       <c r="M712" s="3" t="inlineStr">
         <is>
@@ -46145,7 +46144,7 @@
     <row r="713">
       <c r="A713" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B713" s="3" t="inlineStr">
@@ -46173,14 +46172,14 @@
       </c>
       <c r="G713" s="3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H713" s="5" t="n">
-        <v>14715000</v>
+        <v>13901500</v>
       </c>
       <c r="I713" s="5" t="n">
-        <v>22673</v>
+        <v>21420</v>
       </c>
       <c r="J713" s="3" t="inlineStr">
         <is>
@@ -46188,10 +46187,10 @@
         </is>
       </c>
       <c r="K713" s="5" t="n">
-        <v>14715000</v>
+        <v>13901500</v>
       </c>
       <c r="L713" s="5" t="n">
-        <v>22673</v>
+        <v>21420</v>
       </c>
       <c r="M713" s="3" t="inlineStr">
         <is>
@@ -46207,7 +46206,7 @@
     <row r="714">
       <c r="A714" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B714" s="3" t="inlineStr">
@@ -46226,7 +46225,7 @@
         </is>
       </c>
       <c r="E714" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F714" s="3" t="inlineStr">
         <is>
@@ -46235,14 +46234,14 @@
       </c>
       <c r="G714" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H714" s="5" t="n">
-        <v>14820300</v>
+        <v>13801800</v>
       </c>
       <c r="I714" s="5" t="n">
-        <v>22836</v>
+        <v>21299</v>
       </c>
       <c r="J714" s="3" t="inlineStr">
         <is>
@@ -46250,10 +46249,10 @@
         </is>
       </c>
       <c r="K714" s="5" t="n">
-        <v>14820300</v>
+        <v>13801800</v>
       </c>
       <c r="L714" s="5" t="n">
-        <v>22836</v>
+        <v>21299</v>
       </c>
       <c r="M714" s="3" t="inlineStr">
         <is>
@@ -46269,7 +46268,7 @@
     <row r="715">
       <c r="A715" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B715" s="3" t="inlineStr">
@@ -46297,14 +46296,14 @@
       </c>
       <c r="G715" s="3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H715" s="5" t="n">
-        <v>6519600</v>
+        <v>6071400</v>
       </c>
       <c r="I715" s="5" t="n">
-        <v>21446</v>
+        <v>19972</v>
       </c>
       <c r="J715" s="3" t="inlineStr">
         <is>
@@ -46312,10 +46311,10 @@
         </is>
       </c>
       <c r="K715" s="5" t="n">
-        <v>6519600</v>
+        <v>6071400</v>
       </c>
       <c r="L715" s="5" t="n">
-        <v>21446</v>
+        <v>19972</v>
       </c>
       <c r="M715" s="3" t="inlineStr">
         <is>
@@ -46331,7 +46330,7 @@
     <row r="716">
       <c r="A716" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B716" s="3" t="inlineStr">
@@ -46359,14 +46358,14 @@
       </c>
       <c r="G716" s="3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H716" s="5" t="n">
-        <v>6448500</v>
+        <v>6102400</v>
       </c>
       <c r="I716" s="5" t="n">
-        <v>21212</v>
+        <v>20074</v>
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
@@ -46374,10 +46373,10 @@
         </is>
       </c>
       <c r="K716" s="5" t="n">
-        <v>6448500</v>
+        <v>6102400</v>
       </c>
       <c r="L716" s="5" t="n">
-        <v>21212</v>
+        <v>20074</v>
       </c>
       <c r="M716" s="3" t="inlineStr">
         <is>
@@ -46393,7 +46392,7 @@
     <row r="717">
       <c r="A717" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B717" s="3" t="inlineStr">
@@ -46412,7 +46411,7 @@
         </is>
       </c>
       <c r="E717" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
@@ -46421,14 +46420,14 @@
       </c>
       <c r="G717" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H717" s="5" t="n">
-        <v>14789300</v>
+        <v>13591800</v>
       </c>
       <c r="I717" s="5" t="n">
-        <v>22788</v>
+        <v>20975</v>
       </c>
       <c r="J717" s="3" t="inlineStr">
         <is>
@@ -46436,10 +46435,10 @@
         </is>
       </c>
       <c r="K717" s="5" t="n">
-        <v>14789300</v>
+        <v>13591800</v>
       </c>
       <c r="L717" s="5" t="n">
-        <v>22788</v>
+        <v>20975</v>
       </c>
       <c r="M717" s="3" t="inlineStr">
         <is>
@@ -46455,7 +46454,7 @@
     <row r="718">
       <c r="A718" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B718" s="3" t="inlineStr">
@@ -46483,14 +46482,14 @@
       </c>
       <c r="G718" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H718" s="5" t="n">
-        <v>14732100</v>
+        <v>13720400</v>
       </c>
       <c r="I718" s="5" t="n">
-        <v>22700</v>
+        <v>21141</v>
       </c>
       <c r="J718" s="3" t="inlineStr">
         <is>
@@ -46498,10 +46497,10 @@
         </is>
       </c>
       <c r="K718" s="5" t="n">
-        <v>14732100</v>
+        <v>13720400</v>
       </c>
       <c r="L718" s="5" t="n">
-        <v>22700</v>
+        <v>21141</v>
       </c>
       <c r="M718" s="3" t="inlineStr">
         <is>
@@ -46517,7 +46516,7 @@
     <row r="719">
       <c r="A719" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B719" s="3" t="inlineStr">
@@ -46545,14 +46544,14 @@
       </c>
       <c r="G719" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H719" s="5" t="n">
-        <v>6885000</v>
+        <v>6719200</v>
       </c>
       <c r="I719" s="5" t="n">
-        <v>24415</v>
+        <v>23827</v>
       </c>
       <c r="J719" s="3" t="inlineStr">
         <is>
@@ -46560,10 +46559,10 @@
         </is>
       </c>
       <c r="K719" s="5" t="n">
-        <v>6885000</v>
+        <v>6719200</v>
       </c>
       <c r="L719" s="5" t="n">
-        <v>24415</v>
+        <v>23827</v>
       </c>
       <c r="M719" s="3" t="inlineStr">
         <is>
@@ -46579,7 +46578,7 @@
     <row r="720">
       <c r="A720" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B720" s="3" t="inlineStr">
@@ -46607,14 +46606,14 @@
       </c>
       <c r="G720" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H720" s="5" t="n">
-        <v>6809400</v>
+        <v>6608100</v>
       </c>
       <c r="I720" s="5" t="n">
-        <v>24147</v>
+        <v>23433</v>
       </c>
       <c r="J720" s="3" t="inlineStr">
         <is>
@@ -46622,10 +46621,10 @@
         </is>
       </c>
       <c r="K720" s="5" t="n">
-        <v>6809400</v>
+        <v>6608100</v>
       </c>
       <c r="L720" s="5" t="n">
-        <v>24147</v>
+        <v>23433</v>
       </c>
       <c r="M720" s="3" t="inlineStr">
         <is>
@@ -46641,7 +46640,7 @@
     <row r="721">
       <c r="A721" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B721" s="3" t="inlineStr">
@@ -46660,7 +46659,7 @@
         </is>
       </c>
       <c r="E721" s="4" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F721" s="3" t="inlineStr">
         <is>
@@ -46669,14 +46668,14 @@
       </c>
       <c r="G721" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H721" s="5" t="n">
-        <v>17827800</v>
+        <v>16854300</v>
       </c>
       <c r="I721" s="5" t="n">
-        <v>28433</v>
+        <v>26924</v>
       </c>
       <c r="J721" s="3" t="inlineStr">
         <is>
@@ -46684,10 +46683,10 @@
         </is>
       </c>
       <c r="K721" s="5" t="n">
-        <v>17827800</v>
+        <v>16854300</v>
       </c>
       <c r="L721" s="5" t="n">
-        <v>28433</v>
+        <v>26924</v>
       </c>
       <c r="M721" s="3" t="inlineStr">
         <is>
@@ -46703,7 +46702,7 @@
     <row r="722">
       <c r="A722" s="3" t="inlineStr">
         <is>
-          <t>低座C座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B722" s="3" t="inlineStr">
@@ -46731,14 +46730,14 @@
       </c>
       <c r="G722" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="H722" s="5" t="n">
-        <v>17585100</v>
+        <v>16816700</v>
       </c>
       <c r="I722" s="5" t="n">
-        <v>28046</v>
+        <v>26821</v>
       </c>
       <c r="J722" s="3" t="inlineStr">
         <is>
@@ -46746,10 +46745,10 @@
         </is>
       </c>
       <c r="K722" s="5" t="n">
-        <v>17585100</v>
+        <v>16816700</v>
       </c>
       <c r="L722" s="5" t="n">
-        <v>28046</v>
+        <v>26821</v>
       </c>
       <c r="M722" s="3" t="inlineStr">
         <is>
@@ -46757,1246 +46756,6 @@
         </is>
       </c>
       <c r="N722" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B723" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C723" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D723" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E723" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F723" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G723" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H723" s="5" t="n">
-        <v>6284200</v>
-      </c>
-      <c r="I723" s="5" t="n">
-        <v>20740</v>
-      </c>
-      <c r="J723" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K723" s="5" t="n">
-        <v>6284200</v>
-      </c>
-      <c r="L723" s="5" t="n">
-        <v>20740</v>
-      </c>
-      <c r="M723" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N723" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B724" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C724" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D724" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E724" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F724" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G724" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H724" s="5" t="n">
-        <v>6248500</v>
-      </c>
-      <c r="I724" s="5" t="n">
-        <v>20622</v>
-      </c>
-      <c r="J724" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K724" s="5" t="n">
-        <v>6248500</v>
-      </c>
-      <c r="L724" s="5" t="n">
-        <v>20622</v>
-      </c>
-      <c r="M724" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N724" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B725" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C725" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D725" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E725" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F725" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G725" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H725" s="5" t="n">
-        <v>13879800</v>
-      </c>
-      <c r="I725" s="5" t="n">
-        <v>21386</v>
-      </c>
-      <c r="J725" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K725" s="5" t="n">
-        <v>13879800</v>
-      </c>
-      <c r="L725" s="5" t="n">
-        <v>21386</v>
-      </c>
-      <c r="M725" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N725" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B726" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C726" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D726" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E726" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F726" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G726" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H726" s="5" t="n">
-        <v>14006800</v>
-      </c>
-      <c r="I726" s="5" t="n">
-        <v>21615</v>
-      </c>
-      <c r="J726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K726" s="5" t="n">
-        <v>14006800</v>
-      </c>
-      <c r="L726" s="5" t="n">
-        <v>21615</v>
-      </c>
-      <c r="M726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N726" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B727" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C727" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D727" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E727" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F727" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G727" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="H727" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="I727" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="J727" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K727" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="L727" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="M727" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N727" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B728" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C728" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D728" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E728" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F728" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G728" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H728" s="5" t="n">
-        <v>6109200</v>
-      </c>
-      <c r="I728" s="5" t="n">
-        <v>20096</v>
-      </c>
-      <c r="J728" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K728" s="5" t="n">
-        <v>6109200</v>
-      </c>
-      <c r="L728" s="5" t="n">
-        <v>20096</v>
-      </c>
-      <c r="M728" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N728" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B729" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C729" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D729" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E729" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F729" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G729" s="3" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="H729" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="I729" s="5" t="n">
-        <v>21432</v>
-      </c>
-      <c r="J729" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K729" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="L729" s="5" t="n">
-        <v>21432</v>
-      </c>
-      <c r="M729" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N729" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B730" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C730" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D730" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E730" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F730" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G730" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="H730" s="5" t="n">
-        <v>13808300</v>
-      </c>
-      <c r="I730" s="5" t="n">
-        <v>21309</v>
-      </c>
-      <c r="J730" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K730" s="5" t="n">
-        <v>13808300</v>
-      </c>
-      <c r="L730" s="5" t="n">
-        <v>21309</v>
-      </c>
-      <c r="M730" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N730" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B731" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D731" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E731" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F731" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G731" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="H731" s="5" t="n">
-        <v>6108300</v>
-      </c>
-      <c r="I731" s="5" t="n">
-        <v>20093</v>
-      </c>
-      <c r="J731" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K731" s="5" t="n">
-        <v>6108300</v>
-      </c>
-      <c r="L731" s="5" t="n">
-        <v>20093</v>
-      </c>
-      <c r="M731" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N731" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B732" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C732" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D732" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E732" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F732" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G732" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H732" s="5" t="n">
-        <v>6173500</v>
-      </c>
-      <c r="I732" s="5" t="n">
-        <v>20308</v>
-      </c>
-      <c r="J732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K732" s="5" t="n">
-        <v>6173500</v>
-      </c>
-      <c r="L732" s="5" t="n">
-        <v>20308</v>
-      </c>
-      <c r="M732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N732" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B733" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C733" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D733" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E733" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F733" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G733" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H733" s="5" t="n">
-        <v>13901500</v>
-      </c>
-      <c r="I733" s="5" t="n">
-        <v>21420</v>
-      </c>
-      <c r="J733" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K733" s="5" t="n">
-        <v>13901500</v>
-      </c>
-      <c r="L733" s="5" t="n">
-        <v>21420</v>
-      </c>
-      <c r="M733" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N733" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B734" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C734" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D734" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E734" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F734" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G734" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H734" s="5" t="n">
-        <v>13801800</v>
-      </c>
-      <c r="I734" s="5" t="n">
-        <v>21299</v>
-      </c>
-      <c r="J734" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K734" s="5" t="n">
-        <v>13801800</v>
-      </c>
-      <c r="L734" s="5" t="n">
-        <v>21299</v>
-      </c>
-      <c r="M734" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N734" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B735" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C735" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D735" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E735" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F735" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G735" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H735" s="5" t="n">
-        <v>6071400</v>
-      </c>
-      <c r="I735" s="5" t="n">
-        <v>19972</v>
-      </c>
-      <c r="J735" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K735" s="5" t="n">
-        <v>6071400</v>
-      </c>
-      <c r="L735" s="5" t="n">
-        <v>19972</v>
-      </c>
-      <c r="M735" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N735" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B736" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C736" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D736" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E736" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F736" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G736" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H736" s="5" t="n">
-        <v>6102400</v>
-      </c>
-      <c r="I736" s="5" t="n">
-        <v>20074</v>
-      </c>
-      <c r="J736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K736" s="5" t="n">
-        <v>6102400</v>
-      </c>
-      <c r="L736" s="5" t="n">
-        <v>20074</v>
-      </c>
-      <c r="M736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N736" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B737" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C737" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D737" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E737" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F737" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G737" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="H737" s="5" t="n">
-        <v>13591800</v>
-      </c>
-      <c r="I737" s="5" t="n">
-        <v>20975</v>
-      </c>
-      <c r="J737" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K737" s="5" t="n">
-        <v>13591800</v>
-      </c>
-      <c r="L737" s="5" t="n">
-        <v>20975</v>
-      </c>
-      <c r="M737" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N737" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B738" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C738" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D738" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E738" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F738" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G738" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="H738" s="5" t="n">
-        <v>13720400</v>
-      </c>
-      <c r="I738" s="5" t="n">
-        <v>21141</v>
-      </c>
-      <c r="J738" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K738" s="5" t="n">
-        <v>13720400</v>
-      </c>
-      <c r="L738" s="5" t="n">
-        <v>21141</v>
-      </c>
-      <c r="M738" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N738" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B739" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C739" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D739" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E739" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F739" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G739" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H739" s="5" t="n">
-        <v>6719200</v>
-      </c>
-      <c r="I739" s="5" t="n">
-        <v>23827</v>
-      </c>
-      <c r="J739" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K739" s="5" t="n">
-        <v>6719200</v>
-      </c>
-      <c r="L739" s="5" t="n">
-        <v>23827</v>
-      </c>
-      <c r="M739" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N739" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B740" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C740" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D740" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E740" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F740" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G740" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H740" s="5" t="n">
-        <v>6608100</v>
-      </c>
-      <c r="I740" s="5" t="n">
-        <v>23433</v>
-      </c>
-      <c r="J740" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K740" s="5" t="n">
-        <v>6608100</v>
-      </c>
-      <c r="L740" s="5" t="n">
-        <v>23433</v>
-      </c>
-      <c r="M740" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N740" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B741" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C741" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D741" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E741" s="4" t="n">
-        <v>626</v>
-      </c>
-      <c r="F741" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G741" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H741" s="5" t="n">
-        <v>16854300</v>
-      </c>
-      <c r="I741" s="5" t="n">
-        <v>26924</v>
-      </c>
-      <c r="J741" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K741" s="5" t="n">
-        <v>16854300</v>
-      </c>
-      <c r="L741" s="5" t="n">
-        <v>26924</v>
-      </c>
-      <c r="M741" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N741" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B742" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C742" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D742" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E742" s="4" t="n">
-        <v>627</v>
-      </c>
-      <c r="F742" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G742" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="H742" s="5" t="n">
-        <v>16816700</v>
-      </c>
-      <c r="I742" s="5" t="n">
-        <v>26821</v>
-      </c>
-      <c r="J742" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K742" s="5" t="n">
-        <v>16816700</v>
-      </c>
-      <c r="L742" s="5" t="n">
-        <v>26821</v>
-      </c>
-      <c r="M742" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N742" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -48194,7 +46953,7 @@
           <t>C | 384呎 (1房)
 $858万
 $22,341/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -48202,7 +46961,7 @@
           <t>D | 384呎 (1房)
 $858万
 $22,341/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -48210,7 +46969,7 @@
           <t>E | 250呎 (开放式)
 $584万
 $23,361/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -48218,7 +46977,7 @@
           <t>F | 392呎 (1房)
 $895万
 $22,836/呎
-(25年-03月)</t>
+(25年-03月-09日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -48226,7 +46985,7 @@
           <t>G | 391呎 (1房)
 $881万
 $22,535/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr"/>
@@ -48269,7 +47028,7 @@
           <t>D | 609呎 (2房)
 $2028万
 $33,300/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -48285,7 +47044,7 @@
           <t>F | 384呎 (1房)
 $834万
 $21,710/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -48293,7 +47052,7 @@
           <t>G | 384呎 (1房)
 $848万
 $22,072/呎
-(23年-11月)</t>
+(23年-11月-07日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -48301,7 +47060,7 @@
           <t>H | 250呎 (开放式)
 $568万
 $22,702/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -48309,7 +47068,7 @@
           <t>J | 392呎 (1房)
 $855万
 $21,809/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -48317,7 +47076,7 @@
           <t>K | 388呎 (1房)
 $869万
 $22,386/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -48325,7 +47084,7 @@
           <t>L | 476呎 (2房)
 $1108万
 $23,270/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -48364,7 +47123,7 @@
           <t>D | 609呎 (2房)
 $1979万
 $32,500/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -48380,7 +47139,7 @@
           <t>F | 384呎 (1房)
 $827万
 $21,525/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -48388,7 +47147,7 @@
           <t>G | 384呎 (1房)
 $827万
 $21,525/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -48396,7 +47155,7 @@
           <t>H | 250呎 (开放式)
 $585万
 $23,386/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -48404,7 +47163,7 @@
           <t>J | 392呎 (1房)
 $848万
 $21,621/呎
-(23年-06月)</t>
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -48412,7 +47171,7 @@
           <t>K | 388呎 (1房)
 $842万
 $21,709/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -48420,7 +47179,7 @@
           <t>L | 476呎 (2房)
 $1098万
 $23,071/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -48435,7 +47194,7 @@
           <t>A | 936呎 (3房)
 $3373万
 $36,038/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -48475,7 +47234,7 @@
           <t>F | 384呎 (1房)
 $824万
 $21,464/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -48483,7 +47242,7 @@
           <t>G | 384呎 (1房)
 $824万
 $21,464/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -48491,7 +47250,7 @@
           <t>H | 250呎 (开放式)
 $561万
 $22,450/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -48499,7 +47258,7 @@
           <t>J | 392呎 (1房)
 $859万
 $21,916/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -48507,7 +47266,7 @@
           <t>K | 388呎 (1房)
 $840万
 $21,644/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -48515,7 +47274,7 @@
           <t>L | 476呎 (2房)
 $1095万
 $23,003/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -48530,7 +47289,7 @@
           <t>A | 936呎 (3房)
 $3288万
 $35,128/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -48570,7 +47329,7 @@
           <t>F | 384呎 (1房)
 $822万
 $21,401/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -48578,7 +47337,7 @@
           <t>G | 384呎 (1房)
 $822万
 $21,401/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -48586,7 +47345,7 @@
           <t>H | 250呎 (开放式)
 $566万
 $22,633/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -48594,7 +47353,7 @@
           <t>J | 392呎 (1房)
 $866万
 $22,091/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -48602,7 +47361,7 @@
           <t>K | 388呎 (1房)
 $837万
 $21,581/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -48610,7 +47369,7 @@
           <t>L | 476呎 (2房)
 $1092万
 $22,937/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -48625,7 +47384,7 @@
           <t>A | 936呎 (3房)
 $3280万
 $35,037/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -48649,7 +47408,7 @@
           <t>D | 609呎 (2房)
 $1973万
 $32,400/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -48665,7 +47424,7 @@
           <t>F | 384呎 (1房)
 $819万
 $21,340/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -48673,7 +47432,7 @@
           <t>G | 384呎 (1房)
 $819万
 $21,340/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -48681,7 +47440,7 @@
           <t>H | 250呎 (开放式)
 $564万
 $22,568/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -48689,7 +47448,7 @@
           <t>J | 392呎 (1房)
 $840万
 $21,430/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -48697,7 +47456,7 @@
           <t>K | 388呎 (1房)
 $835万
 $21,519/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -48705,7 +47464,7 @@
           <t>L | 476呎 (2房)
 $1107万
 $23,252/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -48720,7 +47479,7 @@
           <t>A | 936呎 (3房)
 $3293万
 $35,185/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -48760,7 +47519,7 @@
           <t>F | 384呎 (1房)
 $817万
 $21,277/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -48768,7 +47527,7 @@
           <t>G | 384呎 (1房)
 $817万
 $21,277/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -48776,7 +47535,7 @@
           <t>H | 250呎 (开放式)
 $556万
 $22,259/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -48784,7 +47543,7 @@
           <t>J | 392呎 (1房)
 $838万
 $21,368/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -48792,7 +47551,7 @@
           <t>K | 388呎 (1房)
 $856万
 $22,050/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -48800,7 +47559,7 @@
           <t>L | 476呎 (2房)
 $1116万
 $23,438/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -48815,7 +47574,7 @@
           <t>A | 936呎 (3房)
 $3280万
 $35,037/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -48855,7 +47614,7 @@
           <t>F | 384呎 (1房)
 $812万
 $21,155/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -48863,7 +47622,7 @@
           <t>G | 384呎 (1房)
 $767万
 $19,979/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -48871,7 +47630,7 @@
           <t>H | 250呎 (开放式)
 $563万
 $22,502/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -48879,7 +47638,7 @@
           <t>J | 392呎 (1房)
 $833万
 $21,242/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -48887,7 +47646,7 @@
           <t>K | 388呎 (1房)
 $841万
 $21,684/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -48895,7 +47654,7 @@
           <t>L | 476呎 (2房)
 $1097万
 $23,050/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -48910,7 +47669,7 @@
           <t>A | 936呎 (3房)
 $3213万
 $34,327/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -48950,7 +47709,7 @@
           <t>F | 384呎 (1房)
 $810万
 $21,091/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -48958,7 +47717,7 @@
           <t>G | 384呎 (1房)
 $810万
 $21,091/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -48966,7 +47725,7 @@
           <t>H | 250呎 (开放式)
 $552万
 $22,068/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -48974,7 +47733,7 @@
           <t>J | 392呎 (1房)
 $844万
 $21,533/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -48982,7 +47741,7 @@
           <t>K | 388呎 (1房)
 $825万
 $21,264/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -48990,7 +47749,7 @@
           <t>L | 476呎 (2房)
 $1076万
 $22,604/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -49005,7 +47764,7 @@
           <t>A | 936呎 (3房)
 $3195万
 $34,136/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -49045,7 +47804,7 @@
           <t>F | 384呎 (1房)
 $808万
 $21,030/呎
-(24年-01月)</t>
+(24年-01月-14日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -49053,7 +47812,7 @@
           <t>G | 384呎 (1房)
 $808万
 $21,030/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -49061,7 +47820,7 @@
           <t>H | 250呎 (开放式)
 $550万
 $22,007/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -49069,7 +47828,7 @@
           <t>J | 392呎 (1房)
 $828万
 $21,118/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -49077,7 +47836,7 @@
           <t>K | 388呎 (1房)
 $823万
 $21,201/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -49085,7 +47844,7 @@
           <t>L | 476呎 (2房)
 $1073万
 $22,538/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -49100,7 +47859,7 @@
           <t>A | 936呎 (3房)
 $3176万
 $33,932/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -49140,7 +47899,7 @@
           <t>F | 384呎 (1房)
 $805万
 $20,967/呎
-(23年-11月)</t>
+(23年-11月-12日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -49148,7 +47907,7 @@
           <t>G | 384呎 (1房)
 $805万
 $20,967/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -49156,7 +47915,7 @@
           <t>H | 250呎 (开放式)
 $549万
 $21,942/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -49164,7 +47923,7 @@
           <t>J | 392呎 (1房)
 $825万
 $21,054/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -49172,7 +47931,7 @@
           <t>K | 388呎 (1房)
 $820万
 $21,138/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -49180,7 +47939,7 @@
           <t>L | 476呎 (2房)
 $1082万
 $22,721/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -49195,7 +47954,7 @@
           <t>A | 936呎 (3房)
 $3167万
 $33,836/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -49235,7 +47994,7 @@
           <t>F | 384呎 (1房)
 $803万
 $20,906/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -49243,7 +48002,7 @@
           <t>G | 384呎 (1房)
 $803万
 $20,906/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -49251,7 +48010,7 @@
           <t>H | 250呎 (开放式)
 $559万
 $22,363/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -49259,7 +48018,7 @@
           <t>J | 392呎 (1房)
 $823万
 $20,992/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -49267,7 +48026,7 @@
           <t>K | 388呎 (1房)
 $818万
 $21,073/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -49275,7 +48034,7 @@
           <t>L | 476呎 (2房)
 $1078万
 $22,654/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -49290,7 +48049,7 @@
           <t>A | 936呎 (3房)
 $3205万
 $34,237/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -49330,7 +48089,7 @@
           <t>F | 384呎 (1房)
 $800万
 $20,845/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -49338,7 +48097,7 @@
           <t>G | 384呎 (1房)
 $800万
 $20,845/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -49346,7 +48105,7 @@
           <t>H | 250呎 (开放式)
 $545万
 $21,816/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -49354,7 +48113,7 @@
           <t>J | 392呎 (1房)
 $820万
 $20,930/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -49362,7 +48121,7 @@
           <t>K | 388呎 (1房)
 $815万
 $21,011/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -49370,7 +48129,7 @@
           <t>L | 476呎 (2房)
 $1087万
 $22,836/呎
-(23年-06月)</t>
+(23年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -49385,7 +48144,7 @@
           <t>A | 936呎 (3房)
 $3195万
 $34,136/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -49425,7 +48184,7 @@
           <t>F | 384呎 (1房)
 $798万
 $20,782/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -49433,7 +48192,7 @@
           <t>G | 384呎 (1房)
 $798万
 $20,782/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -49441,7 +48200,7 @@
           <t>H | 250呎 (开放式)
 $550万
 $21,993/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -49449,7 +48208,7 @@
           <t>J | 392呎 (1房)
 $832万
 $21,213/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -49457,7 +48216,7 @@
           <t>K | 388呎 (1房)
 $813万
 $20,948/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -49465,7 +48224,7 @@
           <t>L | 476呎 (2房)
 $1078万
 $22,642/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -49480,7 +48239,7 @@
           <t>A | 936呎 (3房)
 $3160万
 $33,761/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -49520,7 +48279,7 @@
           <t>F | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-08月)</t>
+(23年-08月-14日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -49528,7 +48287,7 @@
           <t>G | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -49536,7 +48295,7 @@
           <t>H | 250呎 (开放式)
 $548万
 $21,931/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -49544,7 +48303,7 @@
           <t>J | 392呎 (1房)
 $815万
 $20,803/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -49552,7 +48311,7 @@
           <t>K | 388呎 (1房)
 $810万
 $20,883/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -49560,7 +48319,7 @@
           <t>L | 476呎 (2房)
 $1057万
 $22,205/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -49575,7 +48334,7 @@
           <t>A | 936呎 (3房)
 $3184万
 $34,015/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -49615,7 +48374,7 @@
           <t>F | 384呎 (1房)
 $796万
 $20,721/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -49623,7 +48382,7 @@
           <t>G | 384呎 (1房)
 $805万
 $20,951/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -49631,7 +48390,7 @@
           <t>H | 250呎 (开放式)
 $557万
 $22,292/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -49639,7 +48398,7 @@
           <t>J | 392呎 (1房)
 $815万
 $20,803/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -49647,7 +48406,7 @@
           <t>K | 388呎 (1房)
 $810万
 $20,883/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -49655,7 +48414,7 @@
           <t>L | 476呎 (2房)
 $1057万
 $22,205/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -49670,7 +48429,7 @@
           <t>A | 936呎 (3房)
 $3176万
 $33,936/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -49710,7 +48469,7 @@
           <t>F | 384呎 (1房)
 $793万
 $20,660/呎
-(24年-01月)</t>
+(24年-01月-24日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -49718,7 +48477,7 @@
           <t>G | 384呎 (1房)
 $793万
 $20,660/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -49726,7 +48485,7 @@
           <t>H | 250呎 (开放式)
 $547万
 $21,865/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -49734,7 +48493,7 @@
           <t>J | 392呎 (1房)
 $813万
 $20,739/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -49742,7 +48501,7 @@
           <t>K | 388呎 (1房)
 $808万
 $20,821/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -49750,7 +48509,7 @@
           <t>L | 476呎 (2房)
 $1054万
 $22,139/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -49765,7 +48524,7 @@
           <t>A | 936呎 (3房)
 $3167万
 $33,836/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -49805,7 +48564,7 @@
           <t>F | 384呎 (1房)
 $804万
 $20,940/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -49813,7 +48572,7 @@
           <t>G | 384呎 (1房)
 $813万
 $21,169/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -49821,7 +48580,7 @@
           <t>H | 250呎 (开放式)
 $539万
 $21,560/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -49829,7 +48588,7 @@
           <t>J | 392呎 (1房)
 $811万
 $20,677/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -49837,7 +48596,7 @@
           <t>K | 388呎 (1房)
 $805万
 $20,756/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -49845,7 +48604,7 @@
           <t>L | 476呎 (2房)
 $1051万
 $22,073/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -49860,7 +48619,7 @@
           <t>A | 936呎 (3房)
 $3158万
 $33,736/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -49900,7 +48659,7 @@
           <t>F | 384呎 (1房)
 $789万
 $20,536/呎
-(23年-08月)</t>
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -49908,7 +48667,7 @@
           <t>G | 384呎 (1房)
 $797万
 $20,764/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -49916,7 +48675,7 @@
           <t>H | 250呎 (开放式)
 $543万
 $21,738/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -49924,7 +48683,7 @@
           <t>J | 392呎 (1房)
 $808万
 $20,615/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -49932,7 +48691,7 @@
           <t>K | 388呎 (1房)
 $812万
 $20,923/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -49940,7 +48699,7 @@
           <t>L | 476呎 (2房)
 $1048万
 $22,007/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -49995,7 +48754,7 @@
           <t>F | 384呎 (1房)
 $786万
 $20,473/呎
-(23年-08月)</t>
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -50003,7 +48762,7 @@
           <t>G | 384呎 (1房)
 $799万
 $20,814/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -50011,7 +48770,7 @@
           <t>H | 250呎 (开放式)
 $545万
 $21,792/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -50019,7 +48778,7 @@
           <t>J | 392呎 (1房)
 $819万
 $20,893/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -50027,7 +48786,7 @@
           <t>K | 388呎 (1房)
 $800万
 $20,630/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -50035,7 +48794,7 @@
           <t>L | 476呎 (2房)
 $1044万
 $21,940/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -50090,7 +48849,7 @@
           <t>F | 384呎 (1房)
 $797万
 $20,752/呎
-(24年-01月)</t>
+(24年-01月-30日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -50098,7 +48857,7 @@
           <t>G | 384呎 (1房)
 $784万
 $20,412/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -50106,7 +48865,7 @@
           <t>H | 250呎 (开放式)
 $534万
 $21,373/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -50114,7 +48873,7 @@
           <t>J | 392呎 (1房)
 $821万
 $20,944/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -50122,7 +48881,7 @@
           <t>K | 388呎 (1房)
 $807万
 $20,794/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -50130,7 +48889,7 @@
           <t>L | 476呎 (2房)
 $1041万
 $21,872/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -50185,7 +48944,7 @@
           <t>F | 384呎 (1房)
 $790万
 $20,577/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -50193,7 +48952,7 @@
           <t>G | 384呎 (1房)
 $781万
 $20,351/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -50201,7 +48960,7 @@
           <t>H | 250呎 (开放式)
 $548万
 $21,900/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -50209,7 +48968,7 @@
           <t>J | 392呎 (1房)
 $801万
 $20,427/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -50217,7 +48976,7 @@
           <t>K | 388呎 (1房)
 $809万
 $20,844/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -50225,7 +48984,7 @@
           <t>L | 476呎 (2房)
 $1050万
 $22,048/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -50280,7 +49039,7 @@
           <t>F | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -50288,7 +49047,7 @@
           <t>G | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -50296,7 +49055,7 @@
           <t>H | 250呎 (开放式)
 $531万
 $21,244/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -50304,7 +49063,7 @@
           <t>J | 392呎 (1房)
 $798万
 $20,362/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -50312,7 +49071,7 @@
           <t>K | 388呎 (1房)
 $793万
 $20,440/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -50320,7 +49079,7 @@
           <t>L | 476呎 (2房)
 $1035万
 $21,740/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -50375,7 +49134,7 @@
           <t>F | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -50383,7 +49142,7 @@
           <t>G | 384呎 (1房)
 $779万
 $20,288/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -50391,7 +49150,7 @@
           <t>H | 250呎 (开放式)
 $531万
 $21,240/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -50399,7 +49158,7 @@
           <t>J | 392呎 (1房)
 $798万
 $20,362/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -50407,7 +49166,7 @@
           <t>K | 388呎 (1房)
 $793万
 $20,440/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -50415,7 +49174,7 @@
           <t>L | 476呎 (2房)
 $1035万
 $21,740/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -50470,7 +49229,7 @@
           <t>F | 384呎 (1房)
 $790万
 $20,564/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -50478,7 +49237,7 @@
           <t>G | 384呎 (1房)
 $777万
 $20,227/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -50486,7 +49245,7 @@
           <t>H | 250呎 (开放式)
 $530万
 $21,182/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -50494,7 +49253,7 @@
           <t>J | 392呎 (1房)
 $809万
 $20,639/呎
-(23年-08月)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -50502,7 +49261,7 @@
           <t>K | 388呎 (1房)
 $791万
 $20,375/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -50510,7 +49269,7 @@
           <t>L | 476呎 (2房)
 $1072万
 $22,517/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -50565,7 +49324,7 @@
           <t>F | 384呎 (1房)
 $774万
 $20,163/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -50573,7 +49332,7 @@
           <t>G | 384呎 (1房)
 $791万
 $20,611/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -50581,7 +49340,7 @@
           <t>H | 250呎 (开放式)
 $528万
 $21,118/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -50589,7 +49348,7 @@
           <t>J | 392呎 (1房)
 $793万
 $20,239/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -50597,7 +49356,7 @@
           <t>K | 388呎 (1房)
 $788万
 $20,313/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -50605,7 +49364,7 @@
           <t>L | 476呎 (2房)
 $1046万
 $21,968/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -50660,7 +49419,7 @@
           <t>F | 384呎 (1房)
 $772万
 $20,102/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -50668,7 +49427,7 @@
           <t>G | 384呎 (1房)
 $772万
 $20,102/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -50676,7 +49435,7 @@
           <t>H | 250呎 (开放式)
 $526万
 $21,056/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -50684,7 +49443,7 @@
           <t>J | 392呎 (1房)
 $791万
 $20,174/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -50692,7 +49451,7 @@
           <t>K | 388呎 (1房)
 $794万
 $20,475/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -50700,7 +49459,7 @@
           <t>L | 476呎 (2房)
 $1025万
 $21,539/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -50755,7 +49514,7 @@
           <t>F | 384呎 (1房)
 $767万
 $19,978/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -50763,7 +49522,7 @@
           <t>G | 384呎 (1房)
 $767万
 $19,978/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -50771,7 +49530,7 @@
           <t>H | 250呎 (开放式)
 $523万
 $20,927/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -50779,7 +49538,7 @@
           <t>J | 392呎 (1房)
 $786万
 $20,048/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -50787,7 +49546,7 @@
           <t>K | 388呎 (1房)
 $737万
 $19,004/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -50795,7 +49554,7 @@
           <t>L | 476呎 (2房)
 $1019万
 $21,407/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -50850,7 +49609,7 @@
           <t>F | 384呎 (1房)
 $760万
 $19,788/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -50858,7 +49617,7 @@
           <t>G | 384呎 (1房)
 $781万
 $20,343/呎
-(23年-08月)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -50866,7 +49625,7 @@
           <t>H | 250呎 (开放式)
 $518万
 $20,729/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -50874,7 +49633,7 @@
           <t>J | 392呎 (1房)
 $735万
 $18,756/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -50882,7 +49641,7 @@
           <t>K | 388呎 (1房)
 $730万
 $18,825/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -50890,7 +49649,7 @@
           <t>L | 476呎 (2房)
 $1010万
 $21,209/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -51076,7 +49835,7 @@
           <t>A | 1204呎 (3房)
 $5422万
 $45,037/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -51100,7 +49859,7 @@
           <t>D | 250呎 (开放式)
 $582万
 $23,280/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -51108,7 +49867,7 @@
           <t>E | 390呎 (1房)
 $856万
 $21,939/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -51116,7 +49875,7 @@
           <t>F | 395呎 (1房)
 $867万
 $21,941/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -51124,7 +49883,7 @@
           <t>G | 250呎 (开放式)
 $590万
 $23,604/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -51132,7 +49891,7 @@
           <t>H | 384呎 (1房)
 $852万
 $22,175/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -51140,7 +49899,7 @@
           <t>J | 604呎 (2房)
 $1380万
 $22,856/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr"/>
@@ -51182,7 +49941,7 @@
           <t>D | 609呎 (2房)
 $1870万
 $30,700/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -51198,7 +49957,7 @@
           <t>F | 564呎 (2房)
 $1747万
 $30,975/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -51206,7 +49965,7 @@
           <t>G | 250呎 (开放式)
 $595万
 $23,782/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -51214,7 +49973,7 @@
           <t>H | 390呎 (1房)
 $832万
 $21,321/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -51222,7 +49981,7 @@
           <t>J | 395呎 (1房)
 $805万
 $20,372/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -51230,7 +49989,7 @@
           <t>K | 250呎 (开放式)
 $563万
 $22,540/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -51238,7 +49997,7 @@
           <t>L | 384呎 (1房)
 $828万
 $21,551/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -51246,7 +50005,7 @@
           <t>M | 604呎 (2房)
 $1311万
 $21,703/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -51261,7 +50020,7 @@
           <t>A | 678呎 (2房)
 $2271万
 $33,500/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -51285,7 +50044,7 @@
           <t>D | 609呎 (2房)
 $1849万
 $30,356/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -51301,7 +50060,7 @@
           <t>F | 564呎 (2房)
 $1727万
 $30,629/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -51309,7 +50068,7 @@
           <t>G | 250呎 (开放式)
 $590万
 $23,581/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -51317,7 +50076,7 @@
           <t>H | 390呎 (1房)
 $824万
 $21,138/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -51325,7 +50084,7 @@
           <t>J | 395呎 (1房)
 $798万
 $20,200/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -51333,7 +50092,7 @@
           <t>K | 250呎 (开放式)
 $568万
 $22,721/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -51341,7 +50100,7 @@
           <t>L | 384呎 (1房)
 $820万
 $21,366/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -51349,7 +50108,7 @@
           <t>M | 604呎 (2房)
 $1300万
 $21,518/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -51364,7 +50123,7 @@
           <t>A | 678呎 (2房)
 $2258万
 $33,300/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -51388,7 +50147,7 @@
           <t>D | 609呎 (2房)
 $1859万
 $30,519/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -51404,7 +50163,7 @@
           <t>F | 564呎 (2房)
 $1746万
 $30,964/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -51412,7 +50171,7 @@
           <t>G | 250呎 (开放式)
 $588万
 $23,515/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -51420,7 +50179,7 @@
           <t>H | 390呎 (1房)
 $838万
 $21,498/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -51428,7 +50187,7 @@
           <t>J | 395呎 (1房)
 $833万
 $21,078/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -51436,7 +50195,7 @@
           <t>K | 250呎 (开放式)
 $566万
 $22,659/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -51444,7 +50203,7 @@
           <t>L | 384呎 (1房)
 $818万
 $21,302/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -51452,7 +50211,7 @@
           <t>M | 604呎 (2房)
 $1296万
 $21,455/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -51467,7 +50226,7 @@
           <t>A | 678呎 (2房)
 $2281万
 $33,650/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -51475,7 +50234,7 @@
           <t>B | 474呎 (1房)
 $1456万
 $30,712/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -51491,7 +50250,7 @@
           <t>D | 609呎 (2房)
 $1828万
 $30,012/呎
-(23年-09月)</t>
+(23年-09月-14日)</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -51507,7 +50266,7 @@
           <t>F | 564呎 (2房)
 $1708万
 $30,284/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -51515,7 +50274,7 @@
           <t>G | 250呎 (开放式)
 $586万
 $23,450/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -51523,7 +50282,7 @@
           <t>H | 390呎 (1房)
 $820万
 $21,016/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -51531,7 +50290,7 @@
           <t>J | 395呎 (1房)
 $830万
 $21,019/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -51539,7 +50298,7 @@
           <t>K | 250呎 (开放式)
 $556万
 $22,223/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -51547,7 +50306,7 @@
           <t>L | 384呎 (1房)
 $816万
 $21,241/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -51555,7 +50314,7 @@
           <t>M | 604呎 (2房)
 $1292万
 $21,394/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -51570,7 +50329,7 @@
           <t>A | 678呎 (2房)
 $2195万
 $32,379/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -51578,7 +50337,7 @@
           <t>B | 474呎 (1房)
 $1447万
 $30,534/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -51594,7 +50353,7 @@
           <t>D | 609呎 (2房)
 $1817万
 $29,839/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -51610,7 +50369,7 @@
           <t>F | 564呎 (2房)
 $1717万
 $30,446/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -51618,7 +50377,7 @@
           <t>G | 250呎 (开放式)
 $585万
 $23,384/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -51626,7 +50385,7 @@
           <t>H | 390呎 (1房)
 $831万
 $21,303/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -51634,7 +50393,7 @@
           <t>J | 395呎 (1房)
 $828万
 $20,960/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -51642,7 +50401,7 @@
           <t>K | 250呎 (开放式)
 $563万
 $22,531/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -51650,7 +50409,7 @@
           <t>L | 384呎 (1房)
 $813万
 $21,178/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -51658,7 +50417,7 @@
           <t>M | 603呎 (2房)
 $1288万
 $21,367/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -51673,7 +50432,7 @@
           <t>A | 678呎 (2房)
 $2183万
 $32,193/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -51681,7 +50440,7 @@
           <t>B | 474呎 (1房)
 $1439万
 $30,357/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -51697,7 +50456,7 @@
           <t>D | 609呎 (2房)
 $1807万
 $29,667/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
@@ -51713,7 +50472,7 @@
           <t>F | 564呎 (2房)
 $1717万
 $30,438/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -51721,7 +50480,7 @@
           <t>G | 250呎 (开放式)
 $583万
 $23,310/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -51729,7 +50488,7 @@
           <t>H | 390呎 (1房)
 $837万
 $21,474/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -51737,7 +50496,7 @@
           <t>J | 395呎 (1房)
 $825万
 $20,898/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -51745,7 +50504,7 @@
           <t>K | 250呎 (开放式)
 $562万
 $22,465/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -51753,7 +50512,7 @@
           <t>L | 384呎 (1房)
 $811万
 $21,117/呎
-(23年-09月)</t>
+(23年-09月-04日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -51761,7 +50520,7 @@
           <t>M | 604呎 (2房)
 $1299万
 $21,505/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -51776,7 +50535,7 @@
           <t>A | 678呎 (2房)
 $2170万
 $32,007/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -51800,7 +50559,7 @@
           <t>D | 609呎 (2房)
 $1796万
 $29,496/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -51816,7 +50575,7 @@
           <t>F | 564呎 (2房)
 $1679万
 $29,767/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -51824,7 +50583,7 @@
           <t>G | 250呎 (开放式)
 $560万
 $22,417/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -51832,7 +50591,7 @@
           <t>H | 390呎 (1房)
 $819万
 $21,002/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -51840,7 +50599,7 @@
           <t>J | 395呎 (1房)
 $834万
 $21,124/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -51848,7 +50607,7 @@
           <t>K | 250呎 (开放式)
 $549万
 $21,971/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -51856,7 +50615,7 @@
           <t>L | 384呎 (1房)
 $806万
 $20,993/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -51864,7 +50623,7 @@
           <t>M | 603呎 (2房)
 $1327万
 $22,004/呎
-(23年-07月)</t>
+(23年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -51879,7 +50638,7 @@
           <t>A | 678呎 (2房)
 $2157万
 $31,821/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -51903,7 +50662,7 @@
           <t>D | 609呎 (2房)
 $1786万
 $29,323/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -51919,7 +50678,7 @@
           <t>F | 564呎 (2房)
 $1669万
 $29,593/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -51927,7 +50686,7 @@
           <t>G | 250呎 (开放式)
 $559万
 $22,355/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -51935,7 +50694,7 @@
           <t>H | 390呎 (1房)
 $821万
 $21,057/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -51943,7 +50702,7 @@
           <t>J | 395呎 (1房)
 $827万
 $20,948/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -51951,7 +50710,7 @@
           <t>K | 250呎 (开放式)
 $557万
 $22,271/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -51959,7 +50718,7 @@
           <t>L | 384呎 (1房)
 $804万
 $20,932/呎
-(23年-08月)</t>
+(23年-08月-20日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -51967,7 +50726,7 @@
           <t>M | 604呎 (2房)
 $1274万
 $21,084/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -51982,7 +50741,7 @@
           <t>A | 678呎 (2房)
 $2145万
 $31,635/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -52006,7 +50765,7 @@
           <t>D | 609呎 (2房)
 $1775万
 $29,152/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -52022,7 +50781,7 @@
           <t>F | 564呎 (2房)
 $1659万
 $29,421/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -52030,7 +50789,7 @@
           <t>G | 250呎 (开放式)
 $568万
 $22,736/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -52038,7 +50797,7 @@
           <t>H | 390呎 (1房)
 $805万
 $20,649/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -52046,7 +50805,7 @@
           <t>J | 395呎 (1房)
 $830万
 $21,003/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -52054,7 +50813,7 @@
           <t>K | 250呎 (开放式)
 $555万
 $22,209/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -52062,7 +50821,7 @@
           <t>L | 384呎 (1房)
 $801万
 $20,869/呎
-(23年-08月)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -52070,7 +50829,7 @@
           <t>M | 604呎 (2房)
 $1291万
 $21,372/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -52109,7 +50868,7 @@
           <t>D | 609呎 (2房)
 $1765万
 $28,979/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -52125,7 +50884,7 @@
           <t>F | 564呎 (2房)
 $1650万
 $29,248/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -52133,7 +50892,7 @@
           <t>G | 250呎 (开放式)
 $567万
 $22,666/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -52141,7 +50900,7 @@
           <t>H | 390呎 (1房)
 $803万
 $20,589/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -52149,7 +50908,7 @@
           <t>J | 395呎 (1房)
 $814万
 $20,597/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -52157,7 +50916,7 @@
           <t>K | 250呎 (开放式)
 $554万
 $22,143/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -52165,7 +50924,7 @@
           <t>L | 384呎 (1房)
 $799万
 $20,808/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -52173,7 +50932,7 @@
           <t>M | 603呎 (2房)
 $1266万
 $20,996/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -52212,7 +50971,7 @@
           <t>D | 609呎 (2房)
 $1760万
 $28,893/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -52228,7 +50987,7 @@
           <t>F | 564呎 (2房)
 $1645万
 $29,162/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -52236,7 +50995,7 @@
           <t>G | 250呎 (开放式)
 $554万
 $22,161/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -52244,7 +51003,7 @@
           <t>H | 390呎 (1房)
 $801万
 $20,529/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -52252,7 +51011,7 @@
           <t>J | 395呎 (1房)
 $811万
 $20,538/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -52260,7 +51019,7 @@
           <t>K | 250呎 (开放式)
 $552万
 $22,077/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -52268,7 +51027,7 @@
           <t>L | 384呎 (1房)
 $797万
 $20,747/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -52276,7 +51035,7 @@
           <t>M | 604呎 (2房)
 $1262万
 $20,898/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -52315,7 +51074,7 @@
           <t>D | 609呎 (2房)
 $1754万
 $28,807/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -52331,7 +51090,7 @@
           <t>F | 564呎 (2房)
 $1640万
 $29,076/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -52339,7 +51098,7 @@
           <t>G | 250呎 (开放式)
 $543万
 $21,733/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -52347,7 +51106,7 @@
           <t>H | 390呎 (1房)
 $798万
 $20,467/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -52355,7 +51114,7 @@
           <t>J | 395呎 (1房)
 $809万
 $20,479/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -52363,7 +51122,7 @@
           <t>K | 250呎 (开放式)
 $541万
 $21,654/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -52371,7 +51130,7 @@
           <t>L | 384呎 (1房)
 $794万
 $20,684/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -52379,7 +51138,7 @@
           <t>M | 604呎 (2房)
 $1273万
 $21,069/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -52418,7 +51177,7 @@
           <t>D | 609呎 (2房)
 $1749万
 $28,720/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -52434,7 +51193,7 @@
           <t>F | 564呎 (2房)
 $1635万
 $28,990/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -52442,7 +51201,7 @@
           <t>G | 250呎 (开放式)
 $542万
 $21,672/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -52450,7 +51209,7 @@
           <t>H | 390呎 (1房)
 $796万
 $20,407/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -52458,7 +51217,7 @@
           <t>J | 395呎 (1房)
 $820万
 $20,758/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -52466,7 +51225,7 @@
           <t>K | 250呎 (开放式)
 $546万
 $21,829/呎
-(23年-10月)</t>
+(23年-10月-02日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -52474,7 +51233,7 @@
           <t>L | 384呎 (1房)
 $792万
 $20,623/呎
-(23年-09月)</t>
+(23年-09月-21日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -52482,7 +51241,7 @@
           <t>M | 604呎 (2房)
 $1290万
 $21,351/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -52521,7 +51280,7 @@
           <t>D | 609呎 (2房)
 $1744万
 $28,634/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -52537,7 +51296,7 @@
           <t>F | 564呎 (2房)
 $1630万
 $28,904/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -52545,7 +51304,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,607/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -52553,7 +51312,7 @@
           <t>H | 390呎 (1房)
 $793万
 $20,345/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -52561,7 +51320,7 @@
           <t>J | 395呎 (1房)
 $804万
 $20,358/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -52569,7 +51328,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,528/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -52577,7 +51336,7 @@
           <t>L | 384呎 (1房)
 $790万
 $20,562/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -52585,7 +51344,7 @@
           <t>M | 604呎 (2房)
 $1251万
 $20,713/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -52600,7 +51359,7 @@
           <t>A | 678呎 (2房)
 $2107万
 $31,078/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -52624,7 +51383,7 @@
           <t>D | 609呎 (2房)
 $1744万
 $28,634/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -52640,7 +51399,7 @@
           <t>F | 564呎 (2房)
 $1630万
 $28,904/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -52648,7 +51407,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,607/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -52656,7 +51415,7 @@
           <t>H | 390呎 (1房)
 $793万
 $20,345/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -52664,7 +51423,7 @@
           <t>J | 395呎 (1房)
 $804万
 $20,358/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -52672,7 +51431,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,528/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -52680,7 +51439,7 @@
           <t>L | 384呎 (1房)
 $803万
 $20,904/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -52688,7 +51447,7 @@
           <t>M | 603呎 (2房)
 $1251万
 $20,748/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -52703,7 +51462,7 @@
           <t>A | 678呎 (2房)
 $2101万
 $30,985/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -52727,7 +51486,7 @@
           <t>D | 609呎 (2房)
 $1739万
 $28,549/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -52743,7 +51502,7 @@
           <t>F | 564呎 (2房)
 $1625万
 $28,818/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -52751,7 +51510,7 @@
           <t>G | 250呎 (开放式)
 $554万
 $22,144/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -52759,7 +51518,7 @@
           <t>H | 390呎 (1房)
 $804万
 $20,623/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -52767,7 +51526,7 @@
           <t>J | 395呎 (1房)
 $811万
 $20,522/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -52775,7 +51534,7 @@
           <t>K | 250呎 (开放式)
 $557万
 $22,298/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -52783,7 +51542,7 @@
           <t>L | 384呎 (1房)
 $787万
 $20,498/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -52791,7 +51550,7 @@
           <t>M | 604呎 (2房)
 $1247万
 $20,651/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -52806,7 +51565,7 @@
           <t>A | 678呎 (2房)
 $2129万
 $31,407/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -52830,7 +51589,7 @@
           <t>D | 609呎 (2房)
 $1733万
 $28,463/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -52838,7 +51597,7 @@
           <t>E | 415呎 (1房)
 $1231万
 $29,672/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -52846,7 +51605,7 @@
           <t>F | 564呎 (2房)
 $1620万
 $28,731/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -52854,7 +51613,7 @@
           <t>G | 250呎 (开放式)
 $537万
 $21,481/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -52862,7 +51621,7 @@
           <t>H | 390呎 (1房)
 $789万
 $20,225/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -52870,7 +51629,7 @@
           <t>J | 395呎 (1房)
 $813万
 $20,575/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -52878,7 +51637,7 @@
           <t>K | 250呎 (开放式)
 $535万
 $21,398/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -52886,7 +51645,7 @@
           <t>L | 384呎 (1房)
 $785万
 $20,438/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -52894,7 +51653,7 @@
           <t>M | 604呎 (2房)
 $1244万
 $20,590/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -52933,7 +51692,7 @@
           <t>D | 609呎 (2房)
 $1728万
 $28,377/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -52949,7 +51708,7 @@
           <t>F | 564呎 (2房)
 $1616万
 $28,645/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -52957,7 +51716,7 @@
           <t>G | 250呎 (开放式)
 $535万
 $21,416/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -52965,7 +51724,7 @@
           <t>H | 390呎 (1房)
 $786万
 $20,162/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -52973,7 +51732,7 @@
           <t>J | 395呎 (1房)
 $797万
 $20,178/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -52981,7 +51740,7 @@
           <t>K | 250呎 (开放式)
 $533万
 $21,337/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -52989,7 +51748,7 @@
           <t>L | 384呎 (1房)
 $782万
 $20,374/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -52997,7 +51756,7 @@
           <t>M | 603呎 (2房)
 $1240万
 $20,561/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -53036,7 +51795,7 @@
           <t>D | 609呎 (2房)
 $1723万
 $28,290/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -53052,7 +51811,7 @@
           <t>F | 564呎 (2房)
 $1611万
 $28,559/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -53060,7 +51819,7 @@
           <t>G | 250呎 (开放式)
 $534万
 $21,355/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -53068,7 +51827,7 @@
           <t>H | 390呎 (1房)
 $784万
 $20,102/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -53076,7 +51835,7 @@
           <t>J | 395呎 (1房)
 $795万
 $20,117/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -53084,7 +51843,7 @@
           <t>K | 250呎 (开放式)
 $538万
 $21,508/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -53092,7 +51851,7 @@
           <t>L | 384呎 (1房)
 $780万
 $20,313/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -53100,7 +51859,7 @@
           <t>M | 603呎 (2房)
 $1270万
 $21,069/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -53155,7 +51914,7 @@
           <t>F | 564呎 (2房)
 $1601万
 $28,387/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -53163,7 +51922,7 @@
           <t>G | 250呎 (开放式)
 $532万
 $21,290/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -53171,7 +51930,7 @@
           <t>H | 390呎 (1房)
 $782万
 $20,042/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -53179,7 +51938,7 @@
           <t>J | 395呎 (1房)
 $805万
 $20,392/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -53187,7 +51946,7 @@
           <t>K | 250呎 (开放式)
 $539万
 $21,564/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -53195,7 +51954,7 @@
           <t>L | 384呎 (1房)
 $778万
 $20,252/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -53203,7 +51962,7 @@
           <t>M | 603呎 (2房)
 $1232万
 $20,437/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -53258,7 +52017,7 @@
           <t>F | 564呎 (2房)
 $1591万
 $28,213/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -53266,7 +52025,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,583/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -53274,7 +52033,7 @@
           <t>H | 390呎 (1房)
 $795万
 $20,379/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -53282,7 +52041,7 @@
           <t>J | 395呎 (1房)
 $803万
 $20,329/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -53290,7 +52049,7 @@
           <t>K | 250呎 (开放式)
 $529万
 $21,146/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -53298,7 +52057,7 @@
           <t>L | 384呎 (1房)
 $775万
 $20,189/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -53306,7 +52065,7 @@
           <t>M | 603呎 (2房)
 $1229万
 $20,376/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -53369,7 +52128,7 @@
           <t>G | 250呎 (开放式)
 $529万
 $21,164/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -53377,7 +52136,7 @@
           <t>H | 390呎 (1房)
 $792万
 $20,319/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -53385,7 +52144,7 @@
           <t>J | 395呎 (1房)
 $801万
 $20,269/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -53393,7 +52152,7 @@
           <t>K | 250呎 (开放式)
 $527万
 $21,082/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -53401,7 +52160,7 @@
           <t>L | 384呎 (1房)
 $773万
 $20,128/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -53409,7 +52168,7 @@
           <t>M | 604呎 (2房)
 $1252万
 $20,730/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -53472,7 +52231,7 @@
           <t>G | 250呎 (开放式)
 $538万
 $21,517/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -53480,7 +52239,7 @@
           <t>H | 390呎 (1房)
 $792万
 $20,319/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -53488,7 +52247,7 @@
           <t>J | 395呎 (1房)
 $788万
 $19,937/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -53496,7 +52255,7 @@
           <t>K | 250呎 (开放式)
 $527万
 $21,082/呎
-(23年-07月)</t>
+(23年-07月-10日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -53504,7 +52263,7 @@
           <t>L | 384呎 (1房)
 $773万
 $20,128/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -53512,7 +52271,7 @@
           <t>M | 603呎 (2房)
 $1225万
 $20,313/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -53575,7 +52334,7 @@
           <t>G | 250呎 (开放式)
 $536万
 $21,451/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -53583,7 +52342,7 @@
           <t>H | 390呎 (1房)
 $783万
 $20,078/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -53591,7 +52350,7 @@
           <t>J | 395呎 (1房)
 $785万
 $19,877/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -53599,7 +52358,7 @@
           <t>K | 250呎 (开放式)
 $526万
 $21,020/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -53607,7 +52366,7 @@
           <t>L | 384呎 (1房)
 $783万
 $20,399/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -53615,7 +52374,7 @@
           <t>M | 604呎 (2房)
 $1221万
 $20,219/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -53678,7 +52437,7 @@
           <t>G | 250呎 (开放式)
 $545万
 $21,817/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -53686,7 +52445,7 @@
           <t>H | 390呎 (1房)
 $788万
 $20,195/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -53694,7 +52453,7 @@
           <t>J | 395呎 (1房)
 $796万
 $20,146/呎
-(24年-03月)</t>
+(24年-03月-03日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -53702,7 +52461,7 @@
           <t>K | 250呎 (开放式)
 $530万
 $21,188/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -53710,7 +52469,7 @@
           <t>L | 384呎 (1房)
 $768万
 $20,004/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -53718,7 +52477,7 @@
           <t>M | 604呎 (2房)
 $1217万
 $20,156/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -53781,7 +52540,7 @@
           <t>G | 250呎 (开放式)
 $535万
 $21,395/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -53789,7 +52548,7 @@
           <t>H | 390呎 (1房)
 $785万
 $20,132/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -53797,7 +52556,7 @@
           <t>J | 395呎 (1房)
 $793万
 $20,086/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -53805,7 +52564,7 @@
           <t>K | 250呎 (开放式)
 $522万
 $20,894/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -53813,7 +52572,7 @@
           <t>L | 384呎 (1房)
 $779万
 $20,275/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -53821,7 +52580,7 @@
           <t>M | 604呎 (2房)
 $1214万
 $20,095/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -53884,7 +52643,7 @@
           <t>G | 250呎 (开放式)
 $540万
 $21,620/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -53892,7 +52651,7 @@
           <t>H | 390呎 (1房)
 $780万
 $20,008/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -53900,7 +52659,7 @@
           <t>J | 395呎 (1房)
 $776万
 $19,636/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -53908,7 +52667,7 @@
           <t>K | 250呎 (开放式)
 $528万
 $21,114/呎
-(23年-08月)</t>
+(23年-08月-16日)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -53916,7 +52675,7 @@
           <t>L | 384呎 (1房)
 $774万
 $20,149/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -53924,7 +52683,7 @@
           <t>M | 604呎 (2房)
 $1206万
 $19,971/呎
-(23年-07月)</t>
+(23年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -53987,7 +52746,7 @@
           <t>G | 250呎 (开放式)
 $525万
 $21,002/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -53995,7 +52754,7 @@
           <t>H | 390呎 (1房)
 $773万
 $19,821/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -54003,7 +52762,7 @@
           <t>J | 395呎 (1房)
 $782万
 $19,808/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -54011,7 +52770,7 @@
           <t>K | 250呎 (开放式)
 $515万
 $20,592/呎
-(24年-01月)</t>
+(24年-01月-01日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -54019,7 +52778,7 @@
           <t>L | 384呎 (1房)
 $767万
 $19,985/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -54027,7 +52786,7 @@
           <t>M | 604呎 (2房)
 $1215万
 $20,118/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -54059,7 +52818,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>低座A座 销控网格图</t>
+          <t>低座B座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -54163,33 +52922,33 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 649呎 (3房)
-$1444万
-$22,255/呎
-(23年-07月)</t>
+$1524万
+$23,488/呎
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 649呎 (3房)
-$1440万
-$22,184/呎
-(23年-07月)</t>
+$1497万
+$23,069/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
-$613万
-$20,172/呎
-(23年-07月)</t>
+          <t>C | 303呎 (1房)
+$617万
+$20,361/呎
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 303呎 (1房)
-$609万
-$20,109/呎
-(23年-07月)</t>
+$626万
+$20,664/呎
+(23年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -54202,33 +52961,33 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 649呎 (3房)
-$1411万
-$21,736/呎
-(23年-08月)</t>
+$1481万
+$22,820/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 649呎 (3房)
-$1430万
-$22,028/呎
-(23年-07月)</t>
+$1462万
+$22,530/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
-$610万
-$20,055/呎
-(23年-07月)</t>
+          <t>C | 303呎 (1房)
+$662万
+$21,861/呎
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
-$616万
-$20,253/呎
-(23年-07月)</t>
+          <t>D | 303呎 (1房)
+$622万
+$20,540/呎
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -54240,34 +52999,34 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 649呎 (3房)
-$1394万
-$21,477/呎
-(23年-07月)</t>
+          <t>A | 648呎 (3房)
+$1440万
+$22,215/呎
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 649呎 (3房)
-$1428万
-$22,002/呎
-(23年-07月)</t>
+$1445万
+$22,260/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
-$613万
-$20,155/呎
-(23年-07月)</t>
+          <t>C | 303呎 (1房)
+$610万
+$20,124/呎
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
-$609万
-$20,020/呎
-(23年-07月)</t>
+          <t>D | 303呎 (1房)
+$619万
+$20,415/呎
+(23年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -54280,33 +53039,33 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 649呎 (3房)
-$1415万
-$21,807/呎
-(23年-07月)</t>
+$1422万
+$21,916/呎
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 649呎 (3房)
-$1372万
-$21,148/呎
-(23年-07月)</t>
+          <t>B | 648呎 (3房)
+$1419万
+$21,904/呎
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
-$610万
-$20,058/呎
-(23年-07月)</t>
+          <t>C | 303呎 (1房)
+$606万
+$20,005/呎
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 303呎 (1房)
-$598万
-$19,744/呎
-(23年-07月)</t>
+          <t>D | 304呎 (1房)
+$615万
+$20,223/呎
+(23年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -54318,34 +53077,34 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 626呎 (3房)
-$1722万
-$27,500/呎
-(23年-06月)</t>
+          <t>A | 627呎 (3房)
+$1711万
+$27,289/呎
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1694万
-$27,010/呎
-(23年-07月)</t>
+$1724万
+$27,498/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 282呎 (1房)
-$638万
-$22,634/呎
-(23年-07月)</t>
+$656万
+$23,263/呎
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 282呎 (1房)
-$644万
-$22,848/呎
-(23年-07月)</t>
+$658万
+$23,339/呎
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -54377,7 +53136,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>低座B座 销控网格图</t>
+          <t>低座C座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -54480,34 +53239,34 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 649呎 (3房)
-$1524万
-$23,488/呎
-(23年-07月)</t>
+          <t>A | 648呎 (3房)
+$1521万
+$23,468/呎
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 649呎 (3房)
-$1497万
-$23,069/呎
-(23年-07月)</t>
+          <t>B | 648呎 (3房)
+$1494万
+$23,049/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 303呎 (1房)
-$617万
-$20,361/呎
-(23年-07月)</t>
+$657万
+$21,671/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 303呎 (1房)
-$626万
-$20,664/呎
-(23年-07月)</t>
+          <t>D | 304呎 (1房)
+$664万
+$21,834/呎
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -54519,34 +53278,34 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 649呎 (3房)
-$1481万
-$22,820/呎
-(23年-07月)</t>
+          <t>A | 648呎 (3房)
+$1491万
+$23,006/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 649呎 (3房)
-$1462万
-$22,530/呎
-(23年-07月)</t>
+$1480万
+$22,809/呎
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 303呎 (1房)
-$662万
-$21,861/呎
-(23年-08月)</t>
+          <t>C | 304呎 (1房)
+$660万
+$21,708/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 303呎 (1房)
-$622万
-$20,540/呎
-(23年-07月)</t>
+$660万
+$21,775/呎
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -54558,34 +53317,34 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
-$1440万
-$22,215/呎
-(23年-07月)</t>
+          <t>A | 649呎 (3房)
+$1482万
+$22,836/呎
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 649呎 (3房)
-$1445万
-$22,260/呎
-(23年-07月)</t>
+$1472万
+$22,673/呎
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 303呎 (1房)
-$610万
-$20,124/呎
-(23年-06月)</t>
+          <t>C | 304呎 (1房)
+$660万
+$21,698/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 303呎 (1房)
-$619万
-$20,415/呎
-(23年-07月)</t>
+          <t>D | 304呎 (1房)
+$674万
+$22,176/呎
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -54598,33 +53357,33 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 649呎 (3房)
-$1422万
-$21,916/呎
-(23年-08月)</t>
+$1473万
+$22,700/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 648呎 (3房)
-$1419万
-$21,904/呎
-(23年-06月)</t>
+          <t>B | 649呎 (3房)
+$1479万
+$22,788/呎
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 303呎 (1房)
-$606万
-$20,005/呎
-(23年-07月)</t>
+          <t>C | 304呎 (1房)
+$645万
+$21,212/呎
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 304呎 (1房)
-$615万
-$20,223/呎
-(23年-07月)</t>
+$652万
+$21,446/呎
+(23年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -54637,33 +53396,33 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 627呎 (3房)
-$1711万
-$27,289/呎
-(23年-07月)</t>
+$1759万
+$28,046/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1724万
-$27,498/呎
-(23年-07月)</t>
+$1783万
+$28,433/呎
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 282呎 (1房)
-$656万
-$23,263/呎
-(23年-07月)</t>
+$681万
+$24,147/呎
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 282呎 (1房)
-$658万
-$23,339/呎
-(23年-07月)</t>
+$688万
+$24,415/呎
+(23年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -54695,324 +53454,6 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>低座C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 648呎 (3房)
-$1521万
-$23,468/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 648呎 (3房)
-$1494万
-$23,049/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$657万
-$21,671/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$664万
-$21,834/呎
-(23年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 648呎 (3房)
-$1491万
-$23,006/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1480万
-$22,809/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$660万
-$21,708/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 303呎 (1房)
-$660万
-$21,775/呎
-(23年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1482万
-$22,836/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1472万
-$22,673/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$660万
-$21,698/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$674万
-$22,176/呎
-(23年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1473万
-$22,700/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1479万
-$22,788/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$645万
-$21,212/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$652万
-$21,446/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 627呎 (3房)
-$1759万
-$28,046/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 627呎 (3房)
-$1783万
-$28,433/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$681万
-$24,147/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 282呎 (1房)
-$688万
-$24,415/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
           <t>低座D座 销控网格图</t>
         </is>
       </c>
@@ -55119,7 +53560,7 @@
           <t>A | 648呎 (3房)
 $1401万
 $21,615/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -55127,7 +53568,7 @@
           <t>B | 649呎 (3房)
 $1388万
 $21,386/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -55135,7 +53576,7 @@
           <t>C | 303呎 (1房)
 $625万
 $20,622/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -55143,7 +53584,7 @@
           <t>D | 303呎 (1房)
 $628万
 $20,740/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -55158,7 +53599,7 @@
           <t>A | 648呎 (3房)
 $1381万
 $21,309/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -55166,7 +53607,7 @@
           <t>B | 649呎 (3房)
 $1391万
 $21,432/呎
-(23年-06月)</t>
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -55174,7 +53615,7 @@
           <t>C | 304呎 (1房)
 $611万
 $20,096/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -55182,7 +53623,7 @@
           <t>D | 303呎 (1房)
 $1391万
 $45,905/呎
-(23年-07月)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -55197,7 +53638,7 @@
           <t>A | 648呎 (3房)
 $1380万
 $21,299/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -55205,7 +53646,7 @@
           <t>B | 649呎 (3房)
 $1390万
 $21,420/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -55213,7 +53654,7 @@
           <t>C | 304呎 (1房)
 $617万
 $20,308/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -55221,7 +53662,7 @@
           <t>D | 304呎 (1房)
 $611万
 $20,093/呎
-(23年-07月)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -55236,7 +53677,7 @@
           <t>A | 649呎 (3房)
 $1372万
 $21,141/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -55244,7 +53685,7 @@
           <t>B | 648呎 (3房)
 $1359万
 $20,975/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -55252,7 +53693,7 @@
           <t>C | 304呎 (1房)
 $610万
 $20,074/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -55260,7 +53701,7 @@
           <t>D | 304呎 (1房)
 $607万
 $19,972/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -55275,7 +53716,7 @@
           <t>A | 627呎 (3房)
 $1682万
 $26,821/呎
-(23年-07月)</t>
+(23年-07月-23日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -55283,7 +53724,7 @@
           <t>B | 626呎 (3房)
 $1685万
 $26,924/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -55291,7 +53732,7 @@
           <t>C | 282呎 (1房)
 $661万
 $23,433/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -55299,7 +53740,7 @@
           <t>D | 282呎 (1房)
 $672万
 $23,827/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
     </row>
